--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -1714,31 +1714,30 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr"/>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>Hensoldt</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
         <is>
           <t>Projektleiter Software Defined Defence (SDD) (w/m/d)</t>
         </is>
       </c>
-      <c r="E39" s="2" t="n">
+      <c r="E39" t="n">
         <v>3</v>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>...equisition ID: 3422 Location: Fürstenfeldbruck, DE, 82256 Company: ESG Elekt...</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Projektleiter-Software-Defined-Defence-%28SDD%29-%28wmd%29-82256/1352828255/</t>
         </is>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1214,54 +1214,55 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Hensoldt</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Projektleiter TLB und Informationssicherheit P-8A (w/m/d)</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>...equisition ID: 4852 Location: Fürstenfeldbruck, DE, 82256 Wurster Nordseeküs...</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Projektleiter-TLB-und-Informationssicherheit-P-8A-%28wmd%29-82256/1361632455/</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>Isar Aerospace</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
         <is>
           <t>Project Manager Commercial (m/f/d)</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>5</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Ottobrunn, Bavaria, Germany; Parsdorf, Bavaria, Germany</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4949469101</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Munich Re</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Project Manager - SAP SuccessFactors (m/f/d)*</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -1269,29 +1270,29 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>...AP SuccessFactors (m/f/d)* in Munich at Munich Re Skip to main con...</t>
+          <t>Ottobrunn, Bavaria, Germany; Parsdorf, Bavaria, Germany</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://careers.munichre.com/en/job/munich/project-manager-sap-successfactors-m-f-d/3342/44462004480</t>
+          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4949469101</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" t="inlineStr">
         <is>
-          <t>Michael Page Switzerland</t>
+          <t>Munich Re</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Zurich</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>IT Project Manager</t>
+          <t>Project Manager - SAP SuccessFactors (m/f/d)*</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -1299,47 +1300,42 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
+          <t>...AP SuccessFactors (m/f/d)* in Munich at Munich Re Skip to main con...</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://careers.munichre.com/en/job/munich/project-manager-sap-successfactors-m-f-d/3342/44462004480</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Michael Page Switzerland</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>IT Project Manager</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>5</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
           <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>https://www.michaelpage.ch/job-detail/it-project-manager/ref/jn-092026-7100459</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Celonis</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Customer Engagement Program Manager - Scale Team</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>4</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Munich, Germany</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/7823007003?gh_jid=7823007003</t>
         </is>
       </c>
     </row>
@@ -1361,7 +1357,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Customer Success Program Manager - Scale Team</t>
+          <t>Customer Engagement Program Manager - Scale Team</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -1374,14 +1370,14 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/7823005003?gh_jid=7823005003</t>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7823007003?gh_jid=7823007003</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1396,7 +1392,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Lead Project Manager</t>
+          <t>Customer Success Program Manager - Scale Team</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -1409,24 +1405,29 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/7683452003?gh_jid=7683452003</t>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7823005003?gh_jid=7823005003</t>
         </is>
       </c>
     </row>
     <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ETH Zurich</t>
+          <t>Celonis</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Zurich</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Projektleiter:in IT (w/m/d) 60%-100%, Zürich, befristet 08.09.2026                 |                 Informatikdienste</t>
+          <t>Lead Project Manager</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -1434,19 +1435,19 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>...eiter:in IT (w/m/d) 60%-100%, Zürich, befristet print Drucken An d...</t>
+          <t>Munich, Germany</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://jobs.ethz.ch/job/view/JOPG_ethz_Mv6A7zxfE2ogt3097w</t>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7683452003?gh_jid=7683452003</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" t="inlineStr">
         <is>
-          <t>Michael Page Switzerland</t>
+          <t>ETH Zurich</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1456,7 +1457,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>IT Project Manager / Product Owner</t>
+          <t>Projektleiter:in IT (w/m/d) 60%-100%, Zürich, befristet 08.09.2026                 |                 Informatikdienste</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -1464,29 +1465,29 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+          <t>...eiter:in IT (w/m/d) 60%-100%, Zürich, befristet print Drucken An d...</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.michaelpage.ch/job-detail/it-project-manager-product-owner/ref/jn-072026-7053211</t>
+          <t>https://jobs.ethz.ch/job/view/JOPG_ethz_Mv6A7zxfE2ogt3097w</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" t="inlineStr">
         <is>
-          <t>Michael Page Germany</t>
+          <t>Michael Page Switzerland</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>Zurich</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Projektmanager SAP Einführung (gn)</t>
+          <t>IT Project Manager / Product Owner</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -1494,29 +1495,29 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.michaelpage.de/job-detail/projektmanager-sap-einf%C3%BChrung-gn/ref/jn-072026-7074884</t>
+          <t>https://www.michaelpage.ch/job-detail/it-project-manager-product-owner/ref/jn-072026-7053211</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" t="inlineStr">
         <is>
-          <t>Hensoldt</t>
+          <t>Michael Page Germany</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Zurich</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Projektleiter ILS/IPS (w/m/d)</t>
+          <t>Projektmanager SAP Einführung (gn)</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -1524,19 +1525,19 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>...für Produkte und Projekte des zugehörigen Programmbereichs Ange...</t>
+          <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://jobs.hensoldt.net/job/Ulm-Projektleiter-ILSIPS-%28wmd%29-89077/1363566455/</t>
+          <t>https://www.michaelpage.de/job-detail/projektmanager-sap-einf%C3%BChrung-gn/ref/jn-072026-7074884</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="B33" t="inlineStr">
         <is>
-          <t>Bundesamt fur Informatik BIT</t>
+          <t>Hensoldt</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1546,7 +1547,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Projektleiter/-in für grosskalibrige Munition Bundesamt für Rüstung armasuisse Bern | 100%</t>
+          <t>Projektleiter ILS/IPS (w/m/d)</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -1554,29 +1555,29 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>...hschulabschluss (Bachelor) vorzugsweise in Elektrotechnik oder...</t>
+          <t>...für Produkte und Projekte des zugehörigen Programmbereichs Ange...</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://jobs.admin.ch/offene-stellen/projektleiter-in-fuer-grosskalibrige-munition/54119111-a980-43d3-8597-e9fd348e9a01</t>
+          <t>https://jobs.hensoldt.net/job/Ulm-Projektleiter-ILSIPS-%28wmd%29-89077/1363566455/</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="B34" t="inlineStr">
         <is>
-          <t>GAF Geospatial GmbH</t>
+          <t>Bundesamt fur Informatik BIT</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>Zurich</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Junior Project Manager – Software Development and Operations</t>
+          <t>Projektleiter/-in für grosskalibrige Munition Bundesamt für Rüstung armasuisse Bern | 100%</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -1584,19 +1585,19 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>...r team at our headquarters in Munich , we are looking for a motiva...</t>
+          <t>...hschulabschluss (Bachelor) vorzugsweise in Elektrotechnik oder...</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://careers.gaf.de/junior-project-manager-software-development-and-operations/</t>
+          <t>https://jobs.admin.ch/offene-stellen/projektleiter-in-fuer-grosskalibrige-munition/54119111-a980-43d3-8597-e9fd348e9a01</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="B35" t="inlineStr">
         <is>
-          <t>Aeromaritime Systembau GmbH</t>
+          <t>GAF Geospatial GmbH</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1606,67 +1607,68 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Project Manager (m/f/d)</t>
+          <t>Junior Project Manager – Software Development and Operations</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>...ement Location: Neufahrn near Freising, Germany Start Date: As soon...</t>
+          <t>...r team at our headquarters in Munich , we are looking for a motiva...</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://aeromaritimegroup.com/jobs/project-manager-m-f-d/</t>
+          <t>https://careers.gaf.de/junior-project-manager-software-development-and-operations/</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Michael Page Switzerland</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Zurich</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Project Manager</t>
-        </is>
-      </c>
-      <c r="E36" t="n">
-        <v>3</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>https://www.michaelpage.ch/jobs/project-manager</t>
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Hensoldt</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Project Lead Police Helicopters (w/m/d)</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>...equisition ID: 5556 Location: Fürstenfeldbruck, DE, 82256 Company: ESG Elekt...</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Project-Lead-Police-Helicopters-%28wmd%29-82256/1361623855/</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="B37" t="inlineStr">
         <is>
-          <t>Michael Page Switzerland</t>
+          <t>Aeromaritime Systembau GmbH</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Zurich</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>IT Project Manager - FR / GE</t>
+          <t>Project Manager (m/f/d)</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -1674,12 +1676,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+          <t>...ement Location: Neufahrn near Freising, Germany Start Date: As soon...</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.michaelpage.ch/fr/job-detail/it-project-manager-fr-ge/ref/jn-062026-7044696?lang=en</t>
+          <t>https://aeromaritimegroup.com/jobs/project-manager-m-f-d/</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1698,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Senior Hands-On IT Project Manager - Integration</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -1709,24 +1711,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.michaelpage.ch/job-detail/senior-hands-it-project-manager-integration/ref/jn-052026-7008447</t>
+          <t>https://www.michaelpage.ch/jobs/project-manager</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="B39" t="inlineStr">
         <is>
-          <t>Hensoldt</t>
+          <t>Michael Page Switzerland</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>Zurich</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Projektleiter Software Defined Defence (SDD) (w/m/d)</t>
+          <t>IT Project Manager - FR / GE</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -1734,10 +1736,70 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.ch/fr/job-detail/it-project-manager-fr-ge/ref/jn-062026-7044696?lang=en</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Michael Page Switzerland</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Senior Hands-On IT Project Manager - Integration</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>3</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.ch/job-detail/senior-hands-it-project-manager-integration/ref/jn-052026-7008447</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Hensoldt</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Projektleiter Software Defined Defence (SDD) (w/m/d)</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>3</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
           <t>...equisition ID: 3422 Location: Fürstenfeldbruck, DE, 82256 Company: ESG Elekt...</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Projektleiter-Software-Defined-Defence-%28SDD%29-%28wmd%29-82256/1352828255/</t>
         </is>
@@ -1754,7 +1816,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1804,120 +1866,213 @@
       </c>
     </row>
     <row r="2">
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Siemens Energy</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Basel</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Project Manager (f/m/d) – Service &amp; Repair (Gas Turbine Components)</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>5</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>...gungssicherheit. Steuerung globaler Lieferketten einschließlich...</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>https://jobs.siemens-energy.com/en_US/jobs/FolderDetail/Project-Manager-f-m-d-Service-Repair-Gas-Turbine-Components/303134</t>
+      <c r="A2" s="3" t="inlineStr"/>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Bundesamt fur Informatik BIT</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Bern</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Projektleiter/-in Bundesamt für Rüstung armasuisse Bern | 80 - 100%</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>...desamt für Rüstung armasuisse Bern (und Homeoffice) | 80-100% Ei...</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>https://jobs.admin.ch/offene-stellen/projektleiter-in/9a84a100-ca7d-474a-84d9-ffbe3eb167ed</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="B3" t="inlineStr">
         <is>
+          <t>Siemens Energy</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Basel</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Project Manager (f/m/d) – Service &amp; Repair (Gas Turbine Components)</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>...gungssicherheit. Steuerung globaler Lieferketten einschließlich...</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>https://jobs.siemens-energy.com/en_US/jobs/FolderDetail/Project-Manager-f-m-d-Service-Repair-Gas-Turbine-Components/303134</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr"/>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Hensoldt</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Bern</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Angebots- und Projektmanager EW Systems (w/m/d)</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>...Angebots- und Projektmanager übernehmen Sie die Verantwortung fü...</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>https://jobs.hensoldt.net/job/Ulm-Angebots-und-Projektmanager-EW-Systems-%28wmd%29-89077/1361578255/</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Hensoldt</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Bern</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Angebots- und Projektmanager EW Systems (w/m/d)</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>...gplattformen. In Ihrer Rolle übernehmen Sie die Verantwortung fü...</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>https://jobs.hensoldt.net/job/Ulm-Angebots-und-Projektmanager-EW-Systems-%28wmd%29-89077/1364864055/</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
           <t>ILF Beratende Ingenieure GmbH</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Bern</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>Projektleiter:in im Bereich Infrastruktur</t>
         </is>
       </c>
-      <c r="E3" t="n">
+      <c r="E6" t="n">
         <v>3</v>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>...Kabelinfrastrukturprojekten) übernehmen. Sie werden mit der Leit...</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>https://www.ilf.com/job/?id=2876</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="B4" t="inlineStr">
+    <row r="7">
+      <c r="B7" t="inlineStr">
         <is>
           <t>ILF Beratende Ingenieure GmbH</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Bern</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Projektleiter:in im Bereich Infrastruktur</t>
         </is>
       </c>
-      <c r="E4" t="n">
+      <c r="E7" t="n">
         <v>3</v>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>...Kabelinfrastrukturprojekten) übernehmen. Sie werden mit der Leit...</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>https://www.ilf.com/job/?id=2999</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="B5" t="inlineStr">
+    <row r="8">
+      <c r="B8" t="inlineStr">
         <is>
           <t>ILF Beratende Ingenieure GmbH</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Bern</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Projektmanager:in Verkehr</t>
         </is>
       </c>
-      <c r="E5" t="n">
+      <c r="E8" t="n">
         <v>3</v>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>...städtische Verkehrssysteme) übernehmen. Sie werden mit der Leit...</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>https://www.ilf.com/job/?id=2771</t>
         </is>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G41"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1214,85 +1214,85 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr"/>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>Hensoldt</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
         <is>
           <t>Projektleiter TLB und Informationssicherheit P-8A (w/m/d)</t>
         </is>
       </c>
-      <c r="E23" s="2" t="n">
+      <c r="E23" t="n">
         <v>6</v>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>...equisition ID: 4852 Location: Fürstenfeldbruck, DE, 82256 Wurster Nordseeküs...</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Projektleiter-TLB-und-Informationssicherheit-P-8A-%28wmd%29-82256/1361632455/</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Germany</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Projektleiter (m/w/d) Defence</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.de/job-detail/projektleiter-mwd-defence/ref/jn-092026-7105457</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>Isar Aerospace</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
         <is>
           <t>Project Manager Commercial (m/f/d)</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>5</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Ottobrunn, Bavaria, Germany; Parsdorf, Bavaria, Germany</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4949469101</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Munich Re</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Project Manager - SAP SuccessFactors (m/f/d)*</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -1300,29 +1300,29 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>...AP SuccessFactors (m/f/d)* in Munich at Munich Re Skip to main con...</t>
+          <t>Ottobrunn, Bavaria, Germany; Parsdorf, Bavaria, Germany</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://careers.munichre.com/en/job/munich/project-manager-sap-successfactors-m-f-d/3342/44462004480</t>
+          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4949469101</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="B26" t="inlineStr">
         <is>
-          <t>Michael Page Switzerland</t>
+          <t>Munich Re</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Zurich</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>IT Project Manager</t>
+          <t>Project Manager - SAP SuccessFactors (m/f/d)*</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -1330,47 +1330,42 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
+          <t>...AP SuccessFactors (m/f/d)* in Munich at Munich Re Skip to main con...</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://careers.munichre.com/en/job/munich/project-manager-sap-successfactors-m-f-d/3342/44462004480</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Michael Page Switzerland</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>IT Project Manager</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>5</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
           <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>https://www.michaelpage.ch/job-detail/it-project-manager/ref/jn-092026-7100459</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Celonis</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Customer Engagement Program Manager - Scale Team</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>4</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Munich, Germany</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/7823007003?gh_jid=7823007003</t>
         </is>
       </c>
     </row>
@@ -1392,7 +1387,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Customer Success Program Manager - Scale Team</t>
+          <t>Customer Engagement Program Manager - Scale Team</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -1405,14 +1400,14 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/7823005003?gh_jid=7823005003</t>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7823007003?gh_jid=7823007003</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1427,7 +1422,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Lead Project Manager</t>
+          <t>Customer Success Program Manager - Scale Team</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -1440,24 +1435,29 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/7683452003?gh_jid=7683452003</t>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7823005003?gh_jid=7823005003</t>
         </is>
       </c>
     </row>
     <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ETH Zurich</t>
+          <t>Celonis</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Zurich</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Projektleiter:in IT (w/m/d) 60%-100%, Zürich, befristet 08.09.2026                 |                 Informatikdienste</t>
+          <t>Lead Project Manager</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -1465,19 +1465,19 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>...eiter:in IT (w/m/d) 60%-100%, Zürich, befristet print Drucken An d...</t>
+          <t>Munich, Germany</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://jobs.ethz.ch/job/view/JOPG_ethz_Mv6A7zxfE2ogt3097w</t>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7683452003?gh_jid=7683452003</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" t="inlineStr">
         <is>
-          <t>Michael Page Switzerland</t>
+          <t>ETH Zurich</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>IT Project Manager / Product Owner</t>
+          <t>Projektleiter:in IT (w/m/d) 60%-100%, Zürich, befristet 08.09.2026                 |                 Informatikdienste</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -1495,29 +1495,29 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+          <t>...eiter:in IT (w/m/d) 60%-100%, Zürich, befristet print Drucken An d...</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.michaelpage.ch/job-detail/it-project-manager-product-owner/ref/jn-072026-7053211</t>
+          <t>https://jobs.ethz.ch/job/view/JOPG_ethz_Mv6A7zxfE2ogt3097w</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" t="inlineStr">
         <is>
-          <t>Michael Page Germany</t>
+          <t>Michael Page Switzerland</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>Zurich</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Projektmanager SAP Einführung (gn)</t>
+          <t>IT Project Manager / Product Owner</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -1525,29 +1525,29 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.michaelpage.de/job-detail/projektmanager-sap-einf%C3%BChrung-gn/ref/jn-072026-7074884</t>
+          <t>https://www.michaelpage.ch/job-detail/it-project-manager-product-owner/ref/jn-072026-7053211</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="B33" t="inlineStr">
         <is>
-          <t>Hensoldt</t>
+          <t>Michael Page Germany</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Zurich</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Projektleiter ILS/IPS (w/m/d)</t>
+          <t>Projektmanager SAP Einführung (gn)</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -1555,19 +1555,19 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>...für Produkte und Projekte des zugehörigen Programmbereichs Ange...</t>
+          <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://jobs.hensoldt.net/job/Ulm-Projektleiter-ILSIPS-%28wmd%29-89077/1363566455/</t>
+          <t>https://www.michaelpage.de/job-detail/projektmanager-sap-einf%C3%BChrung-gn/ref/jn-072026-7074884</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="B34" t="inlineStr">
         <is>
-          <t>Bundesamt fur Informatik BIT</t>
+          <t>Hensoldt</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1577,7 +1577,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Projektleiter/-in für grosskalibrige Munition Bundesamt für Rüstung armasuisse Bern | 100%</t>
+          <t>Projektleiter ILS/IPS (w/m/d)</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -1585,29 +1585,29 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>...hschulabschluss (Bachelor) vorzugsweise in Elektrotechnik oder...</t>
+          <t>...für Produkte und Projekte des zugehörigen Programmbereichs Ange...</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://jobs.admin.ch/offene-stellen/projektleiter-in-fuer-grosskalibrige-munition/54119111-a980-43d3-8597-e9fd348e9a01</t>
+          <t>https://jobs.hensoldt.net/job/Ulm-Projektleiter-ILSIPS-%28wmd%29-89077/1363566455/</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="B35" t="inlineStr">
         <is>
-          <t>GAF Geospatial GmbH</t>
+          <t>Bundesamt fur Informatik BIT</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>Zurich</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Junior Project Manager – Software Development and Operations</t>
+          <t>Projektleiter/-in für grosskalibrige Munition Bundesamt für Rüstung armasuisse Bern | 100%</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -1615,50 +1615,49 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
+          <t>...hschulabschluss (Bachelor) vorzugsweise in Elektrotechnik oder...</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://jobs.admin.ch/offene-stellen/projektleiter-in-fuer-grosskalibrige-munition/54119111-a980-43d3-8597-e9fd348e9a01</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>GAF Geospatial GmbH</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Junior Project Manager – Software Development and Operations</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>4</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
           <t>...r team at our headquarters in Munich , we are looking for a motiva...</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>https://careers.gaf.de/junior-project-manager-software-development-and-operations/</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr"/>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>Hensoldt</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>Project Lead Police Helicopters (w/m/d)</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>...equisition ID: 5556 Location: Fürstenfeldbruck, DE, 82256 Company: ESG Elekt...</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Project-Lead-Police-Helicopters-%28wmd%29-82256/1361623855/</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="B37" t="inlineStr">
         <is>
-          <t>Aeromaritime Systembau GmbH</t>
+          <t>Hensoldt</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1668,67 +1667,68 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Project Manager (m/f/d)</t>
+          <t>Project Lead Police Helicopters (w/m/d)</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>...ement Location: Neufahrn near Freising, Germany Start Date: As soon...</t>
+          <t>...equisition ID: 5556 Location: Fürstenfeldbruck, DE, 82256 Company: ESG Elekt...</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://aeromaritimegroup.com/jobs/project-manager-m-f-d/</t>
+          <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Project-Lead-Police-Helicopters-%28wmd%29-82256/1361623855/</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Michael Page Switzerland</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Siemens Energy</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Project Manager</t>
-        </is>
-      </c>
-      <c r="E38" t="n">
-        <v>3</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>https://www.michaelpage.ch/jobs/project-manager</t>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Cybersecurity Transformation Program Lead (f/m/d)</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>...ob ID 301947 Location Germany Baden-Wuerttemberg Karlsruhe Countr...</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.siemens-energy.com/en_US/jobs/FolderDetail/Cybersecurity-Transformation-Program-Lead-f-m-d/301947</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="B39" t="inlineStr">
         <is>
-          <t>Michael Page Switzerland</t>
+          <t>Aeromaritime Systembau GmbH</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Zurich</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>IT Project Manager - FR / GE</t>
+          <t>Project Manager (m/f/d)</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -1736,12 +1736,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+          <t>...ement Location: Neufahrn near Freising, Germany Start Date: As soon...</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.michaelpage.ch/fr/job-detail/it-project-manager-fr-ge/ref/jn-062026-7044696?lang=en</t>
+          <t>https://aeromaritimegroup.com/jobs/project-manager-m-f-d/</t>
         </is>
       </c>
     </row>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Senior Hands-On IT Project Manager - Integration</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -1771,24 +1771,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.michaelpage.ch/job-detail/senior-hands-it-project-manager-integration/ref/jn-052026-7008447</t>
+          <t>https://www.michaelpage.ch/jobs/project-manager</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="B41" t="inlineStr">
         <is>
-          <t>Hensoldt</t>
+          <t>Michael Page Switzerland</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>Zurich</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Projektleiter Software Defined Defence (SDD) (w/m/d)</t>
+          <t>IT Project Manager - FR / GE</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -1796,10 +1796,70 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.ch/fr/job-detail/it-project-manager-fr-ge/ref/jn-062026-7044696?lang=en</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Michael Page Switzerland</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Senior Hands-On IT Project Manager - Integration</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>3</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.ch/job-detail/senior-hands-it-project-manager-integration/ref/jn-052026-7008447</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Hensoldt</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Projektleiter Software Defined Defence (SDD) (w/m/d)</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>3</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
           <t>...equisition ID: 3422 Location: Fürstenfeldbruck, DE, 82256 Company: ESG Elekt...</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Projektleiter-Software-Defined-Defence-%28SDD%29-%28wmd%29-82256/1352828255/</t>
         </is>
@@ -1816,7 +1876,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1866,31 +1926,30 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr"/>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Bundesamt fur Informatik BIT</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Bern</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Projektleiter/-in Bundesamt für Rüstung armasuisse Bern | 80 - 100%</t>
         </is>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="E2" t="n">
         <v>8</v>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>...desamt für Rüstung armasuisse Bern (und Homeoffice) | 80-100% Ei...</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>https://jobs.admin.ch/offene-stellen/projektleiter-in/9a84a100-ca7d-474a-84d9-ffbe3eb167ed</t>
         </is>
@@ -1927,94 +1986,93 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr"/>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Hensoldt</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Bern</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Angebots- und Projektmanager EW Systems (w/m/d)</t>
         </is>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="E4" t="n">
         <v>4</v>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>...Angebots- und Projektmanager übernehmen Sie die Verantwortung fü...</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>https://jobs.hensoldt.net/job/Ulm-Angebots-und-Projektmanager-EW-Systems-%28wmd%29-89077/1361578255/</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr"/>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Hensoldt</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Bern</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Angebots- und Projektmanager EW Systems (w/m/d)</t>
         </is>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="E5" t="n">
         <v>4</v>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>...gplattformen. In Ihrer Rolle übernehmen Sie die Verantwortung fü...</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>https://jobs.hensoldt.net/job/Ulm-Angebots-und-Projektmanager-EW-Systems-%28wmd%29-89077/1364864055/</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>ILF Beratende Ingenieure GmbH</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>OBERMEYER Servbest GmbH</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>Bern</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Projektleiter:in im Bereich Infrastruktur</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>3</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>...Kabelinfrastrukturprojekten) übernehmen. Sie werden mit der Leit...</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://www.ilf.com/job/?id=2876</t>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>SENIOR PROJEKTMANAGER (m/w/d)</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>...wie internationale Märkte erobern und sowohl unsere als auch ih...</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>https://karriere.obermeyer-group.com/Vacancies/2564/Description/1</t>
         </is>
       </c>
     </row>
@@ -2044,7 +2102,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.ilf.com/job/?id=2999</t>
+          <t>https://www.ilf.com/job/?id=2876</t>
         </is>
       </c>
     </row>
@@ -2061,7 +2119,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Projektmanager:in Verkehr</t>
+          <t>Projektleiter:in im Bereich Infrastruktur</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -2069,10 +2127,40 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>...Kabelinfrastrukturprojekten) übernehmen. Sie werden mit der Leit...</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.ilf.com/job/?id=2999</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ILF Beratende Ingenieure GmbH</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Bern</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Projektmanager:in Verkehr</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>...städtische Verkehrssysteme) übernehmen. Sie werden mit der Leit...</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>https://www.ilf.com/job/?id=2771</t>
         </is>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -1244,31 +1244,30 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr"/>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>Michael Page Germany</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
         <is>
           <t>Projektleiter (m/w/d) Defence</t>
         </is>
       </c>
-      <c r="E24" s="2" t="n">
+      <c r="E24" t="n">
         <v>6</v>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>https://www.michaelpage.de/job-detail/projektleiter-mwd-defence/ref/jn-092026-7105457</t>
         </is>
@@ -1685,31 +1684,30 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr"/>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>Siemens Energy</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>Cybersecurity Transformation Program Lead (f/m/d)</t>
         </is>
       </c>
-      <c r="E38" s="2" t="n">
+      <c r="E38" t="n">
         <v>4</v>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>...ob ID 301947 Location Germany Baden-Wuerttemberg Karlsruhe Countr...</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>https://jobs.siemens-energy.com/en_US/jobs/FolderDetail/Cybersecurity-Transformation-Program-Lead-f-m-d/301947</t>
         </is>
@@ -2046,31 +2044,30 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr"/>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>OBERMEYER Servbest GmbH</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Bern</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>SENIOR PROJEKTMANAGER (m/w/d)</t>
         </is>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="E6" t="n">
         <v>4</v>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>...wie internationale Märkte erobern und sowohl unsere als auch ih...</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>https://karriere.obermeyer-group.com/Vacancies/2564/Description/1</t>
         </is>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -1874,7 +1874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2074,62 +2074,64 @@
       </c>
     </row>
     <row r="7">
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>ILF Beratende Ingenieure GmbH</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Siemens Energy</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>Bern</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Projektleiter:in im Bereich Infrastruktur</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>3</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>...Kabelinfrastrukturprojekten) übernehmen. Sie werden mit der Leit...</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.ilf.com/job/?id=2876</t>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Projektmanager (w/m/d) Air-Insulated Switchgear (AIS) / Transformatoren</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>...g Als Projektmanager (w/m/d) übernehmen Sie die Verantwortung fü...</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>https://jobs.siemens-energy.com/en_US/jobs/FolderDetail/Projektmanager-w-m-d-Air-Insulated-Switchgear-AIS-Transformatoren/303755</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>ILF Beratende Ingenieure GmbH</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Siemens Energy</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>Bern</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Projektleiter:in im Bereich Infrastruktur</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>3</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>...Kabelinfrastrukturprojekten) übernehmen. Sie werden mit der Leit...</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.ilf.com/job/?id=2999</t>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Projektmanager (w/m/d) Gas-Insulated Switchgear (GIS)</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>...sen hinweg – von der Auftragsübernahme bis zur Übergabe an den K...</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>https://jobs.siemens-energy.com/en_US/jobs/FolderDetail/Projektmanager-w-m-d-Gas-Insulated-Switchgear-GIS/303756</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2148,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Projektmanager:in Verkehr</t>
+          <t>Projektleiter:in im Bereich Infrastruktur</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -2154,10 +2156,70 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>...Kabelinfrastrukturprojekten) übernehmen. Sie werden mit der Leit...</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.ilf.com/job/?id=2876</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ILF Beratende Ingenieure GmbH</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Bern</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Projektleiter:in im Bereich Infrastruktur</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>...Kabelinfrastrukturprojekten) übernehmen. Sie werden mit der Leit...</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.ilf.com/job/?id=2999</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ILF Beratende Ingenieure GmbH</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Bern</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Projektmanager:in Verkehr</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>3</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t>...städtische Verkehrssysteme) übernehmen. Sie werden mit der Leit...</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>https://www.ilf.com/job/?id=2771</t>
         </is>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G43"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1274,54 +1274,55 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Hensoldt</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Systems Engineer / Development Project Manager (DPM) (w/m/d)</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>...ntwicklungsarbeitspakete in Bezug auf Termine, Kosten und Quali...</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.hensoldt.net/job/Ulm-Systems-Engineer-Development-Project-Manager-%28DPM%29-%28wmd%29-89077/1362037255/</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>Isar Aerospace</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
         <is>
           <t>Project Manager Commercial (m/f/d)</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>5</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Ottobrunn, Bavaria, Germany; Parsdorf, Bavaria, Germany</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4949469101</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Munich Re</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Project Manager - SAP SuccessFactors (m/f/d)*</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -1329,29 +1330,29 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>...AP SuccessFactors (m/f/d)* in Munich at Munich Re Skip to main con...</t>
+          <t>Ottobrunn, Bavaria, Germany; Parsdorf, Bavaria, Germany</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://careers.munichre.com/en/job/munich/project-manager-sap-successfactors-m-f-d/3342/44462004480</t>
+          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4949469101</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="B27" t="inlineStr">
         <is>
-          <t>Michael Page Switzerland</t>
+          <t>Munich Re</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Zurich</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>IT Project Manager</t>
+          <t>Project Manager - SAP SuccessFactors (m/f/d)*</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -1359,47 +1360,42 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
+          <t>...AP SuccessFactors (m/f/d)* in Munich at Munich Re Skip to main con...</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://careers.munichre.com/en/job/munich/project-manager-sap-successfactors-m-f-d/3342/44462004480</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Michael Page Switzerland</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>IT Project Manager</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>5</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
           <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>https://www.michaelpage.ch/job-detail/it-project-manager/ref/jn-092026-7100459</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Celonis</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Customer Engagement Program Manager - Scale Team</t>
-        </is>
-      </c>
-      <c r="E28" t="n">
-        <v>4</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Munich, Germany</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/7823007003?gh_jid=7823007003</t>
         </is>
       </c>
     </row>
@@ -1421,7 +1417,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Customer Success Program Manager - Scale Team</t>
+          <t>Customer Engagement Program Manager - Scale Team</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -1434,14 +1430,14 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/7823005003?gh_jid=7823005003</t>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7823007003?gh_jid=7823007003</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1456,7 +1452,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Lead Project Manager</t>
+          <t>Customer Success Program Manager - Scale Team</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -1469,24 +1465,29 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/7683452003?gh_jid=7683452003</t>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7823005003?gh_jid=7823005003</t>
         </is>
       </c>
     </row>
     <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ETH Zurich</t>
+          <t>Celonis</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Zurich</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Projektleiter:in IT (w/m/d) 60%-100%, Zürich, befristet 08.09.2026                 |                 Informatikdienste</t>
+          <t>Lead Project Manager</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -1494,19 +1495,19 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>...eiter:in IT (w/m/d) 60%-100%, Zürich, befristet print Drucken An d...</t>
+          <t>Munich, Germany</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://jobs.ethz.ch/job/view/JOPG_ethz_Mv6A7zxfE2ogt3097w</t>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7683452003?gh_jid=7683452003</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" t="inlineStr">
         <is>
-          <t>Michael Page Switzerland</t>
+          <t>ETH Zurich</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1516,7 +1517,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>IT Project Manager / Product Owner</t>
+          <t>Projektleiter:in IT (w/m/d) 60%-100%, Zürich, befristet 08.09.2026                 |                 Informatikdienste</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -1524,29 +1525,29 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+          <t>...eiter:in IT (w/m/d) 60%-100%, Zürich, befristet print Drucken An d...</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.michaelpage.ch/job-detail/it-project-manager-product-owner/ref/jn-072026-7053211</t>
+          <t>https://jobs.ethz.ch/job/view/JOPG_ethz_Mv6A7zxfE2ogt3097w</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="B33" t="inlineStr">
         <is>
-          <t>Michael Page Germany</t>
+          <t>Michael Page Switzerland</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>Zurich</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Projektmanager SAP Einführung (gn)</t>
+          <t>IT Project Manager / Product Owner</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -1554,29 +1555,29 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.michaelpage.de/job-detail/projektmanager-sap-einf%C3%BChrung-gn/ref/jn-072026-7074884</t>
+          <t>https://www.michaelpage.ch/job-detail/it-project-manager-product-owner/ref/jn-072026-7053211</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="B34" t="inlineStr">
         <is>
-          <t>Hensoldt</t>
+          <t>Michael Page Germany</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Zurich</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Projektleiter ILS/IPS (w/m/d)</t>
+          <t>Projektmanager SAP Einführung (gn)</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -1584,19 +1585,19 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>...für Produkte und Projekte des zugehörigen Programmbereichs Ange...</t>
+          <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://jobs.hensoldt.net/job/Ulm-Projektleiter-ILSIPS-%28wmd%29-89077/1363566455/</t>
+          <t>https://www.michaelpage.de/job-detail/projektmanager-sap-einf%C3%BChrung-gn/ref/jn-072026-7074884</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="B35" t="inlineStr">
         <is>
-          <t>Bundesamt fur Informatik BIT</t>
+          <t>Hensoldt</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1606,7 +1607,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Projektleiter/-in für grosskalibrige Munition Bundesamt für Rüstung armasuisse Bern | 100%</t>
+          <t>Projektleiter ILS/IPS (w/m/d)</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -1614,29 +1615,29 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>...hschulabschluss (Bachelor) vorzugsweise in Elektrotechnik oder...</t>
+          <t>...für Produkte und Projekte des zugehörigen Programmbereichs Ange...</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://jobs.admin.ch/offene-stellen/projektleiter-in-fuer-grosskalibrige-munition/54119111-a980-43d3-8597-e9fd348e9a01</t>
+          <t>https://jobs.hensoldt.net/job/Ulm-Projektleiter-ILSIPS-%28wmd%29-89077/1363566455/</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="B36" t="inlineStr">
         <is>
-          <t>GAF Geospatial GmbH</t>
+          <t>Bundesamt fur Informatik BIT</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>Zurich</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Junior Project Manager – Software Development and Operations</t>
+          <t>Projektleiter/-in für grosskalibrige Munition Bundesamt für Rüstung armasuisse Bern | 100%</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -1644,19 +1645,19 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>...r team at our headquarters in Munich , we are looking for a motiva...</t>
+          <t>...hschulabschluss (Bachelor) vorzugsweise in Elektrotechnik oder...</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://careers.gaf.de/junior-project-manager-software-development-and-operations/</t>
+          <t>https://jobs.admin.ch/offene-stellen/projektleiter-in-fuer-grosskalibrige-munition/54119111-a980-43d3-8597-e9fd348e9a01</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="B37" t="inlineStr">
         <is>
-          <t>Hensoldt</t>
+          <t>GAF Geospatial GmbH</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1666,7 +1667,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Project Lead Police Helicopters (w/m/d)</t>
+          <t>Junior Project Manager – Software Development and Operations</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -1674,29 +1675,29 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>...equisition ID: 5556 Location: Fürstenfeldbruck, DE, 82256 Company: ESG Elekt...</t>
+          <t>...r team at our headquarters in Munich , we are looking for a motiva...</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Project-Lead-Police-Helicopters-%28wmd%29-82256/1361623855/</t>
+          <t>https://careers.gaf.de/junior-project-manager-software-development-and-operations/</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="B38" t="inlineStr">
         <is>
-          <t>Siemens Energy</t>
+          <t>Hensoldt</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Zurich</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Cybersecurity Transformation Program Lead (f/m/d)</t>
+          <t>Project Lead Police Helicopters (w/m/d)</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -1704,59 +1705,59 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>...ob ID 301947 Location Germany Baden-Wuerttemberg Karlsruhe Countr...</t>
+          <t>...equisition ID: 5556 Location: Fürstenfeldbruck, DE, 82256 Company: ESG Elekt...</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://jobs.siemens-energy.com/en_US/jobs/FolderDetail/Cybersecurity-Transformation-Program-Lead-f-m-d/301947</t>
+          <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Project-Lead-Police-Helicopters-%28wmd%29-82256/1361623855/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="B39" t="inlineStr">
         <is>
-          <t>Aeromaritime Systembau GmbH</t>
+          <t>Siemens Energy</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>Zurich</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Project Manager (m/f/d)</t>
+          <t>Cybersecurity Transformation Program Lead (f/m/d)</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>...ement Location: Neufahrn near Freising, Germany Start Date: As soon...</t>
+          <t>...ob ID 301947 Location Germany Baden-Wuerttemberg Karlsruhe Countr...</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://aeromaritimegroup.com/jobs/project-manager-m-f-d/</t>
+          <t>https://jobs.siemens-energy.com/en_US/jobs/FolderDetail/Cybersecurity-Transformation-Program-Lead-f-m-d/301947</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="B40" t="inlineStr">
         <is>
-          <t>Michael Page Switzerland</t>
+          <t>Aeromaritime Systembau GmbH</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Zurich</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Project Manager</t>
+          <t>Project Manager (m/f/d)</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -1764,12 +1765,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+          <t>...ement Location: Neufahrn near Freising, Germany Start Date: As soon...</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.michaelpage.ch/jobs/project-manager</t>
+          <t>https://aeromaritimegroup.com/jobs/project-manager-m-f-d/</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1787,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>IT Project Manager - FR / GE</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -1799,7 +1800,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.michaelpage.ch/fr/job-detail/it-project-manager-fr-ge/ref/jn-062026-7044696?lang=en</t>
+          <t>https://www.michaelpage.ch/jobs/project-manager</t>
         </is>
       </c>
     </row>
@@ -1816,7 +1817,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Senior Hands-On IT Project Manager - Integration</t>
+          <t>IT Project Manager - FR / GE</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -1829,24 +1830,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.michaelpage.ch/job-detail/senior-hands-it-project-manager-integration/ref/jn-052026-7008447</t>
+          <t>https://www.michaelpage.ch/fr/job-detail/it-project-manager-fr-ge/ref/jn-062026-7044696?lang=en</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="B43" t="inlineStr">
         <is>
-          <t>Hensoldt</t>
+          <t>Michael Page Switzerland</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>Zurich</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Projektleiter Software Defined Defence (SDD) (w/m/d)</t>
+          <t>Senior Hands-On IT Project Manager - Integration</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -1854,10 +1855,40 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.ch/job-detail/senior-hands-it-project-manager-integration/ref/jn-052026-7008447</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Hensoldt</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Projektleiter Software Defined Defence (SDD) (w/m/d)</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>3</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
           <t>...equisition ID: 3422 Location: Fürstenfeldbruck, DE, 82256 Company: ESG Elekt...</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Projektleiter-Software-Defined-Defence-%28SDD%29-%28wmd%29-82256/1352828255/</t>
         </is>
@@ -2074,62 +2105,60 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr"/>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Siemens Energy</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Bern</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Projektmanager (w/m/d) Air-Insulated Switchgear (AIS) / Transformatoren</t>
         </is>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="E7" t="n">
         <v>4</v>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>...g Als Projektmanager (w/m/d) übernehmen Sie die Verantwortung fü...</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>https://jobs.siemens-energy.com/en_US/jobs/FolderDetail/Projektmanager-w-m-d-Air-Insulated-Switchgear-AIS-Transformatoren/303755</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr"/>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Siemens Energy</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Bern</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Projektmanager (w/m/d) Gas-Insulated Switchgear (GIS)</t>
         </is>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="E8" t="n">
         <v>4</v>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>...sen hinweg – von der Auftragsübernahme bis zur Übergabe an den K...</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>https://jobs.siemens-energy.com/en_US/jobs/FolderDetail/Projektmanager-w-m-d-Gas-Insulated-Switchgear-GIS/303756</t>
         </is>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G44"/>
+  <dimension ref="A1:G45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1274,31 +1274,30 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr"/>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>Hensoldt</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>Systems Engineer / Development Project Manager (DPM) (w/m/d)</t>
         </is>
       </c>
-      <c r="E25" s="2" t="n">
+      <c r="E25" t="n">
         <v>6</v>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>...ntwicklungsarbeitspakete in Bezug auf Termine, Kosten und Quali...</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>https://jobs.hensoldt.net/job/Ulm-Systems-Engineer-Development-Project-Manager-%28DPM%29-%28wmd%29-89077/1362037255/</t>
         </is>
@@ -1745,49 +1744,50 @@
       </c>
     </row>
     <row r="40">
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Aeromaritime Systembau GmbH</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Project Manager (m/f/d)</t>
-        </is>
-      </c>
-      <c r="E40" t="n">
-        <v>3</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>...ement Location: Neufahrn near Freising, Germany Start Date: As soon...</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>https://aeromaritimegroup.com/jobs/project-manager-m-f-d/</t>
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Siemens Energy</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Projektmanager (w/m/d) für Leistungstransformatoren</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>...m Power Transformers Europe Clusters (MPT) in Deutschland, Österr...</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.siemens-energy.com/en_US/jobs/FolderDetail/Projektmanager-w-m-d-f-r-Leistungstransformatoren/301604</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="B41" t="inlineStr">
         <is>
-          <t>Michael Page Switzerland</t>
+          <t>Aeromaritime Systembau GmbH</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Zurich</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Project Manager</t>
+          <t>Project Manager (m/f/d)</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+          <t>...ement Location: Neufahrn near Freising, Germany Start Date: As soon...</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.michaelpage.ch/jobs/project-manager</t>
+          <t>https://aeromaritimegroup.com/jobs/project-manager-m-f-d/</t>
         </is>
       </c>
     </row>
@@ -1817,7 +1817,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>IT Project Manager - FR / GE</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.michaelpage.ch/fr/job-detail/it-project-manager-fr-ge/ref/jn-062026-7044696?lang=en</t>
+          <t>https://www.michaelpage.ch/jobs/project-manager</t>
         </is>
       </c>
     </row>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Senior Hands-On IT Project Manager - Integration</t>
+          <t>IT Project Manager - FR / GE</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -1860,24 +1860,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.michaelpage.ch/job-detail/senior-hands-it-project-manager-integration/ref/jn-052026-7008447</t>
+          <t>https://www.michaelpage.ch/fr/job-detail/it-project-manager-fr-ge/ref/jn-062026-7044696?lang=en</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="B44" t="inlineStr">
         <is>
-          <t>Hensoldt</t>
+          <t>Michael Page Switzerland</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>Zurich</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Projektleiter Software Defined Defence (SDD) (w/m/d)</t>
+          <t>Senior Hands-On IT Project Manager - Integration</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -1885,10 +1885,40 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.ch/job-detail/senior-hands-it-project-manager-integration/ref/jn-052026-7008447</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Hensoldt</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Projektleiter Software Defined Defence (SDD) (w/m/d)</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>3</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
           <t>...equisition ID: 3422 Location: Fürstenfeldbruck, DE, 82256 Company: ESG Elekt...</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Projektleiter-Software-Defined-Defence-%28SDD%29-%28wmd%29-82256/1352828255/</t>
         </is>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1304,54 +1304,55 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Hensoldt</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Projektmanager Selfprotection Ground (w/m/d)</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>...equisition ID: 1850 Location: Taufkirchen, DE, 82024 Company: HENSOLDT...</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.hensoldt.net/job/Taufkirchen-Projektmanager-Selfprotection-Ground-%28wmd%29-82024/1325906955/</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>Isar Aerospace</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
         <is>
           <t>Project Manager Commercial (m/f/d)</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>5</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Ottobrunn, Bavaria, Germany; Parsdorf, Bavaria, Germany</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4949469101</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Munich Re</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Project Manager - SAP SuccessFactors (m/f/d)*</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -1359,29 +1360,29 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>...AP SuccessFactors (m/f/d)* in Munich at Munich Re Skip to main con...</t>
+          <t>Ottobrunn, Bavaria, Germany; Parsdorf, Bavaria, Germany</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://careers.munichre.com/en/job/munich/project-manager-sap-successfactors-m-f-d/3342/44462004480</t>
+          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4949469101</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" t="inlineStr">
         <is>
-          <t>Michael Page Switzerland</t>
+          <t>Munich Re</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Zurich</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>IT Project Manager</t>
+          <t>Project Manager - SAP SuccessFactors (m/f/d)*</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -1389,47 +1390,42 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
+          <t>...AP SuccessFactors (m/f/d)* in Munich at Munich Re Skip to main con...</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://careers.munichre.com/en/job/munich/project-manager-sap-successfactors-m-f-d/3342/44462004480</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Michael Page Switzerland</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>IT Project Manager</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>5</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
           <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>https://www.michaelpage.ch/job-detail/it-project-manager/ref/jn-092026-7100459</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Celonis</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Customer Engagement Program Manager - Scale Team</t>
-        </is>
-      </c>
-      <c r="E29" t="n">
-        <v>4</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Munich, Germany</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/7823007003?gh_jid=7823007003</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1447,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Customer Success Program Manager - Scale Team</t>
+          <t>Customer Engagement Program Manager - Scale Team</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -1464,14 +1460,14 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/7823005003?gh_jid=7823005003</t>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7823007003?gh_jid=7823007003</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1486,7 +1482,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Lead Project Manager</t>
+          <t>Customer Success Program Manager - Scale Team</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -1499,24 +1495,29 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/7683452003?gh_jid=7683452003</t>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7823005003?gh_jid=7823005003</t>
         </is>
       </c>
     </row>
     <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>ETH Zurich</t>
+          <t>Celonis</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Zurich</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Projektleiter:in IT (w/m/d) 60%-100%, Zürich, befristet 08.09.2026                 |                 Informatikdienste</t>
+          <t>Lead Project Manager</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -1524,19 +1525,19 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>...eiter:in IT (w/m/d) 60%-100%, Zürich, befristet print Drucken An d...</t>
+          <t>Munich, Germany</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://jobs.ethz.ch/job/view/JOPG_ethz_Mv6A7zxfE2ogt3097w</t>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7683452003?gh_jid=7683452003</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="B33" t="inlineStr">
         <is>
-          <t>Michael Page Switzerland</t>
+          <t>ETH Zurich</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1546,7 +1547,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>IT Project Manager / Product Owner</t>
+          <t>Projektleiter:in IT (w/m/d) 60%-100%, Zürich, befristet 08.09.2026                 |                 Informatikdienste</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -1554,29 +1555,29 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+          <t>...eiter:in IT (w/m/d) 60%-100%, Zürich, befristet print Drucken An d...</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.michaelpage.ch/job-detail/it-project-manager-product-owner/ref/jn-072026-7053211</t>
+          <t>https://jobs.ethz.ch/job/view/JOPG_ethz_Mv6A7zxfE2ogt3097w</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="B34" t="inlineStr">
         <is>
-          <t>Michael Page Germany</t>
+          <t>Michael Page Switzerland</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>Zurich</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Projektmanager SAP Einführung (gn)</t>
+          <t>IT Project Manager / Product Owner</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -1584,29 +1585,29 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.michaelpage.de/job-detail/projektmanager-sap-einf%C3%BChrung-gn/ref/jn-072026-7074884</t>
+          <t>https://www.michaelpage.ch/job-detail/it-project-manager-product-owner/ref/jn-072026-7053211</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="B35" t="inlineStr">
         <is>
-          <t>Hensoldt</t>
+          <t>Michael Page Germany</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Zurich</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Projektleiter ILS/IPS (w/m/d)</t>
+          <t>Projektmanager SAP Einführung (gn)</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -1614,19 +1615,19 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>...für Produkte und Projekte des zugehörigen Programmbereichs Ange...</t>
+          <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://jobs.hensoldt.net/job/Ulm-Projektleiter-ILSIPS-%28wmd%29-89077/1363566455/</t>
+          <t>https://www.michaelpage.de/job-detail/projektmanager-sap-einf%C3%BChrung-gn/ref/jn-072026-7074884</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="B36" t="inlineStr">
         <is>
-          <t>Bundesamt fur Informatik BIT</t>
+          <t>Hensoldt</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1636,7 +1637,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Projektleiter/-in für grosskalibrige Munition Bundesamt für Rüstung armasuisse Bern | 100%</t>
+          <t>Projektleiter ILS/IPS (w/m/d)</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -1644,29 +1645,29 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>...hschulabschluss (Bachelor) vorzugsweise in Elektrotechnik oder...</t>
+          <t>...für Produkte und Projekte des zugehörigen Programmbereichs Ange...</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://jobs.admin.ch/offene-stellen/projektleiter-in-fuer-grosskalibrige-munition/54119111-a980-43d3-8597-e9fd348e9a01</t>
+          <t>https://jobs.hensoldt.net/job/Ulm-Projektleiter-ILSIPS-%28wmd%29-89077/1363566455/</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="B37" t="inlineStr">
         <is>
-          <t>GAF Geospatial GmbH</t>
+          <t>Bundesamt fur Informatik BIT</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>Zurich</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Junior Project Manager – Software Development and Operations</t>
+          <t>Projektleiter/-in für grosskalibrige Munition Bundesamt für Rüstung armasuisse Bern | 100%</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -1674,19 +1675,19 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>...r team at our headquarters in Munich , we are looking for a motiva...</t>
+          <t>...hschulabschluss (Bachelor) vorzugsweise in Elektrotechnik oder...</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://careers.gaf.de/junior-project-manager-software-development-and-operations/</t>
+          <t>https://jobs.admin.ch/offene-stellen/projektleiter-in-fuer-grosskalibrige-munition/54119111-a980-43d3-8597-e9fd348e9a01</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="B38" t="inlineStr">
         <is>
-          <t>Hensoldt</t>
+          <t>GAF Geospatial GmbH</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1696,7 +1697,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Project Lead Police Helicopters (w/m/d)</t>
+          <t>Junior Project Manager – Software Development and Operations</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -1704,29 +1705,29 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>...equisition ID: 5556 Location: Fürstenfeldbruck, DE, 82256 Company: ESG Elekt...</t>
+          <t>...r team at our headquarters in Munich , we are looking for a motiva...</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Project-Lead-Police-Helicopters-%28wmd%29-82256/1361623855/</t>
+          <t>https://careers.gaf.de/junior-project-manager-software-development-and-operations/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="B39" t="inlineStr">
         <is>
-          <t>Siemens Energy</t>
+          <t>Hensoldt</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Zurich</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Cybersecurity Transformation Program Lead (f/m/d)</t>
+          <t>Project Lead Police Helicopters (w/m/d)</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -1734,90 +1735,89 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
+          <t>...equisition ID: 5556 Location: Fürstenfeldbruck, DE, 82256 Company: ESG Elekt...</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Project-Lead-Police-Helicopters-%28wmd%29-82256/1361623855/</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Siemens Energy</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Cybersecurity Transformation Program Lead (f/m/d)</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>4</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
           <t>...ob ID 301947 Location Germany Baden-Wuerttemberg Karlsruhe Countr...</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>https://jobs.siemens-energy.com/en_US/jobs/FolderDetail/Cybersecurity-Transformation-Program-Lead-f-m-d/301947</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr"/>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>Siemens Energy</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>Zurich</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>Projektmanager (w/m/d) für Leistungstransformatoren</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>...m Power Transformers Europe Clusters (MPT) in Deutschland, Österr...</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>https://jobs.siemens-energy.com/en_US/jobs/FolderDetail/Projektmanager-w-m-d-f-r-Leistungstransformatoren/301604</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="B41" t="inlineStr">
         <is>
-          <t>Aeromaritime Systembau GmbH</t>
+          <t>Siemens Energy</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>Zurich</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Project Manager (m/f/d)</t>
+          <t>Projektmanager (w/m/d) für Leistungstransformatoren</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>...ement Location: Neufahrn near Freising, Germany Start Date: As soon...</t>
+          <t>...m Power Transformers Europe Clusters (MPT) in Deutschland, Österr...</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://aeromaritimegroup.com/jobs/project-manager-m-f-d/</t>
+          <t>https://jobs.siemens-energy.com/en_US/jobs/FolderDetail/Projektmanager-w-m-d-f-r-Leistungstransformatoren/301604</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="B42" t="inlineStr">
         <is>
-          <t>Michael Page Switzerland</t>
+          <t>Aeromaritime Systembau GmbH</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Zurich</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Project Manager</t>
+          <t>Project Manager (m/f/d)</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -1825,12 +1825,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+          <t>...ement Location: Neufahrn near Freising, Germany Start Date: As soon...</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.michaelpage.ch/jobs/project-manager</t>
+          <t>https://aeromaritimegroup.com/jobs/project-manager-m-f-d/</t>
         </is>
       </c>
     </row>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>IT Project Manager - FR / GE</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -1860,7 +1860,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.michaelpage.ch/fr/job-detail/it-project-manager-fr-ge/ref/jn-062026-7044696?lang=en</t>
+          <t>https://www.michaelpage.ch/jobs/project-manager</t>
         </is>
       </c>
     </row>
@@ -1877,7 +1877,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Senior Hands-On IT Project Manager - Integration</t>
+          <t>IT Project Manager - FR / GE</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -1890,24 +1890,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.michaelpage.ch/job-detail/senior-hands-it-project-manager-integration/ref/jn-052026-7008447</t>
+          <t>https://www.michaelpage.ch/fr/job-detail/it-project-manager-fr-ge/ref/jn-062026-7044696?lang=en</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="B45" t="inlineStr">
         <is>
-          <t>Hensoldt</t>
+          <t>Michael Page Switzerland</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>Zurich</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Projektleiter Software Defined Defence (SDD) (w/m/d)</t>
+          <t>Senior Hands-On IT Project Manager - Integration</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -1915,10 +1915,40 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.ch/job-detail/senior-hands-it-project-manager-integration/ref/jn-052026-7008447</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Hensoldt</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Projektleiter Software Defined Defence (SDD) (w/m/d)</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>3</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
           <t>...equisition ID: 3422 Location: Fürstenfeldbruck, DE, 82256 Company: ESG Elekt...</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Projektleiter-Software-Defined-Defence-%28SDD%29-%28wmd%29-82256/1352828255/</t>
         </is>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G46"/>
+  <dimension ref="A1:G47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1304,31 +1304,30 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr"/>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>Hensoldt</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
         <is>
           <t>Projektmanager Selfprotection Ground (w/m/d)</t>
         </is>
       </c>
-      <c r="E26" s="2" t="n">
+      <c r="E26" t="n">
         <v>6</v>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>...equisition ID: 1850 Location: Taufkirchen, DE, 82024 Company: HENSOLDT...</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>https://jobs.hensoldt.net/job/Taufkirchen-Projektmanager-Selfprotection-Ground-%28wmd%29-82024/1325906955/</t>
         </is>
@@ -1805,49 +1804,50 @@
       </c>
     </row>
     <row r="42">
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Aeromaritime Systembau GmbH</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Project Manager (m/f/d)</t>
-        </is>
-      </c>
-      <c r="E42" t="n">
-        <v>3</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>...ement Location: Neufahrn near Freising, Germany Start Date: As soon...</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>https://aeromaritimegroup.com/jobs/project-manager-m-f-d/</t>
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Hensoldt</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Technical Project Manager Space (w/m/d)</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>...ng technischer Arbeitspakete, Meilensteine, Liefergegenstände, Res...</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.hensoldt.net/job/Immenstaad-Technical-Project-Manager-Space-%28wmd%29-88090/1365577355/</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="B43" t="inlineStr">
         <is>
-          <t>Michael Page Switzerland</t>
+          <t>Aeromaritime Systembau GmbH</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Zurich</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Project Manager</t>
+          <t>Project Manager (m/f/d)</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -1855,12 +1855,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+          <t>...ement Location: Neufahrn near Freising, Germany Start Date: As soon...</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.michaelpage.ch/jobs/project-manager</t>
+          <t>https://aeromaritimegroup.com/jobs/project-manager-m-f-d/</t>
         </is>
       </c>
     </row>
@@ -1877,7 +1877,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>IT Project Manager - FR / GE</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.michaelpage.ch/fr/job-detail/it-project-manager-fr-ge/ref/jn-062026-7044696?lang=en</t>
+          <t>https://www.michaelpage.ch/jobs/project-manager</t>
         </is>
       </c>
     </row>
@@ -1907,7 +1907,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Senior Hands-On IT Project Manager - Integration</t>
+          <t>IT Project Manager - FR / GE</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -1920,24 +1920,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.michaelpage.ch/job-detail/senior-hands-it-project-manager-integration/ref/jn-052026-7008447</t>
+          <t>https://www.michaelpage.ch/fr/job-detail/it-project-manager-fr-ge/ref/jn-062026-7044696?lang=en</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="B46" t="inlineStr">
         <is>
-          <t>Hensoldt</t>
+          <t>Michael Page Switzerland</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>Zurich</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Projektleiter Software Defined Defence (SDD) (w/m/d)</t>
+          <t>Senior Hands-On IT Project Manager - Integration</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -1945,10 +1945,40 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.ch/job-detail/senior-hands-it-project-manager-integration/ref/jn-052026-7008447</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Hensoldt</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Projektleiter Software Defined Defence (SDD) (w/m/d)</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>3</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
           <t>...equisition ID: 3422 Location: Fürstenfeldbruck, DE, 82256 Company: ESG Elekt...</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Projektleiter-Software-Defined-Defence-%28SDD%29-%28wmd%29-82256/1352828255/</t>
         </is>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G47"/>
+  <dimension ref="A1:G48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1804,80 +1804,80 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr"/>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>Hensoldt</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>Technical Project Manager Space (w/m/d)</t>
         </is>
       </c>
-      <c r="E42" s="2" t="n">
+      <c r="E42" t="n">
         <v>4</v>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>...ng technischer Arbeitspakete, Meilensteine, Liefergegenstände, Res...</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>https://jobs.hensoldt.net/job/Immenstaad-Technical-Project-Manager-Space-%28wmd%29-88090/1365577355/</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Aeromaritime Systembau GmbH</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Project Manager (m/f/d)</t>
-        </is>
-      </c>
-      <c r="E43" t="n">
-        <v>3</v>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>...ement Location: Neufahrn near Freising, Germany Start Date: As soon...</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>https://aeromaritimegroup.com/jobs/project-manager-m-f-d/</t>
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Hensoldt</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Projektleiter Space (w/m/d)</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>...ationaler Kundenprojekte in Bezug auf elektro-optische Systeme...</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.hensoldt.net/job/Oberkochen-Projektleiter-Space-%28wmd%29-73447/1362330955/</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="B44" t="inlineStr">
         <is>
-          <t>Michael Page Switzerland</t>
+          <t>Aeromaritime Systembau GmbH</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Zurich</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Project Manager</t>
+          <t>Project Manager (m/f/d)</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+          <t>...ement Location: Neufahrn near Freising, Germany Start Date: As soon...</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.michaelpage.ch/jobs/project-manager</t>
+          <t>https://aeromaritimegroup.com/jobs/project-manager-m-f-d/</t>
         </is>
       </c>
     </row>
@@ -1907,7 +1907,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>IT Project Manager - FR / GE</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.michaelpage.ch/fr/job-detail/it-project-manager-fr-ge/ref/jn-062026-7044696?lang=en</t>
+          <t>https://www.michaelpage.ch/jobs/project-manager</t>
         </is>
       </c>
     </row>
@@ -1937,7 +1937,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Senior Hands-On IT Project Manager - Integration</t>
+          <t>IT Project Manager - FR / GE</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -1950,24 +1950,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.michaelpage.ch/job-detail/senior-hands-it-project-manager-integration/ref/jn-052026-7008447</t>
+          <t>https://www.michaelpage.ch/fr/job-detail/it-project-manager-fr-ge/ref/jn-062026-7044696?lang=en</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="B47" t="inlineStr">
         <is>
-          <t>Hensoldt</t>
+          <t>Michael Page Switzerland</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>Zurich</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Projektleiter Software Defined Defence (SDD) (w/m/d)</t>
+          <t>Senior Hands-On IT Project Manager - Integration</t>
         </is>
       </c>
       <c r="E47" t="n">
@@ -1975,10 +1975,40 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.ch/job-detail/senior-hands-it-project-manager-integration/ref/jn-052026-7008447</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Hensoldt</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Projektleiter Software Defined Defence (SDD) (w/m/d)</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>3</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
           <t>...equisition ID: 3422 Location: Fürstenfeldbruck, DE, 82256 Company: ESG Elekt...</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Projektleiter-Software-Defined-Defence-%28SDD%29-%28wmd%29-82256/1352828255/</t>
         </is>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -1834,31 +1834,30 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr"/>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>Hensoldt</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>Projektleiter Space (w/m/d)</t>
         </is>
       </c>
-      <c r="E43" s="2" t="n">
+      <c r="E43" t="n">
         <v>4</v>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>...ationaler Kundenprojekte in Bezug auf elektro-optische Systeme...</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>https://jobs.hensoldt.net/job/Oberkochen-Projektleiter-Space-%28wmd%29-73447/1362330955/</t>
         </is>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G48"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1429,37 +1429,33 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Celonis</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Customer Engagement Program Manager - Scale Team</t>
-        </is>
-      </c>
-      <c r="E30" t="n">
-        <v>4</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Munich, Germany</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/7823007003?gh_jid=7823007003</t>
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Hensoldt</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Projektleiter Integrated Product Support Sanität (w/m/d)</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>...equisition ID: 4940 Location: Fürstenfeldbruck, DE, 82256 Company: ESG Elekt...</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Projektleiter-Integrated-Product-Support-Sanit%C3%A4t-%28wmd%29-82256/1362543455/</t>
         </is>
       </c>
     </row>
@@ -1481,7 +1477,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Customer Success Program Manager - Scale Team</t>
+          <t>Customer Engagement Program Manager - Scale Team</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -1494,14 +1490,14 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/7823005003?gh_jid=7823005003</t>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7823007003?gh_jid=7823007003</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1516,7 +1512,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Lead Project Manager</t>
+          <t>Customer Success Program Manager - Scale Team</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -1529,24 +1525,29 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/7683452003?gh_jid=7683452003</t>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7823005003?gh_jid=7823005003</t>
         </is>
       </c>
     </row>
     <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ETH Zurich</t>
+          <t>Celonis</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Zurich</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Projektleiter:in IT (w/m/d) 60%-100%, Zürich, befristet 08.09.2026                 |                 Informatikdienste</t>
+          <t>Lead Project Manager</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -1554,19 +1555,19 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>...eiter:in IT (w/m/d) 60%-100%, Zürich, befristet print Drucken An d...</t>
+          <t>Munich, Germany</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://jobs.ethz.ch/job/view/JOPG_ethz_Mv6A7zxfE2ogt3097w</t>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7683452003?gh_jid=7683452003</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="B34" t="inlineStr">
         <is>
-          <t>Michael Page Switzerland</t>
+          <t>ETH Zurich</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1576,7 +1577,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>IT Project Manager / Product Owner</t>
+          <t>Projektleiter:in IT (w/m/d) 60%-100%, Zürich, befristet 08.09.2026                 |                 Informatikdienste</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -1584,29 +1585,29 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+          <t>...eiter:in IT (w/m/d) 60%-100%, Zürich, befristet print Drucken An d...</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.michaelpage.ch/job-detail/it-project-manager-product-owner/ref/jn-072026-7053211</t>
+          <t>https://jobs.ethz.ch/job/view/JOPG_ethz_Mv6A7zxfE2ogt3097w</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="B35" t="inlineStr">
         <is>
-          <t>Michael Page Germany</t>
+          <t>Michael Page Switzerland</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>Zurich</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Projektmanager SAP Einführung (gn)</t>
+          <t>IT Project Manager / Product Owner</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -1614,29 +1615,29 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.michaelpage.de/job-detail/projektmanager-sap-einf%C3%BChrung-gn/ref/jn-072026-7074884</t>
+          <t>https://www.michaelpage.ch/job-detail/it-project-manager-product-owner/ref/jn-072026-7053211</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="B36" t="inlineStr">
         <is>
-          <t>Hensoldt</t>
+          <t>Michael Page Germany</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Zurich</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Projektleiter ILS/IPS (w/m/d)</t>
+          <t>Projektmanager SAP Einführung (gn)</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -1644,19 +1645,19 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>...für Produkte und Projekte des zugehörigen Programmbereichs Ange...</t>
+          <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://jobs.hensoldt.net/job/Ulm-Projektleiter-ILSIPS-%28wmd%29-89077/1363566455/</t>
+          <t>https://www.michaelpage.de/job-detail/projektmanager-sap-einf%C3%BChrung-gn/ref/jn-072026-7074884</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="B37" t="inlineStr">
         <is>
-          <t>Bundesamt fur Informatik BIT</t>
+          <t>Hensoldt</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1666,7 +1667,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Projektleiter/-in für grosskalibrige Munition Bundesamt für Rüstung armasuisse Bern | 100%</t>
+          <t>Projektleiter ILS/IPS (w/m/d)</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -1674,29 +1675,29 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>...hschulabschluss (Bachelor) vorzugsweise in Elektrotechnik oder...</t>
+          <t>...für Produkte und Projekte des zugehörigen Programmbereichs Ange...</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://jobs.admin.ch/offene-stellen/projektleiter-in-fuer-grosskalibrige-munition/54119111-a980-43d3-8597-e9fd348e9a01</t>
+          <t>https://jobs.hensoldt.net/job/Ulm-Projektleiter-ILSIPS-%28wmd%29-89077/1363566455/</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="B38" t="inlineStr">
         <is>
-          <t>GAF Geospatial GmbH</t>
+          <t>Bundesamt fur Informatik BIT</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>Zurich</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Junior Project Manager – Software Development and Operations</t>
+          <t>Projektleiter/-in für grosskalibrige Munition Bundesamt für Rüstung armasuisse Bern | 100%</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -1704,19 +1705,19 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>...r team at our headquarters in Munich , we are looking for a motiva...</t>
+          <t>...hschulabschluss (Bachelor) vorzugsweise in Elektrotechnik oder...</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://careers.gaf.de/junior-project-manager-software-development-and-operations/</t>
+          <t>https://jobs.admin.ch/offene-stellen/projektleiter-in-fuer-grosskalibrige-munition/54119111-a980-43d3-8597-e9fd348e9a01</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="B39" t="inlineStr">
         <is>
-          <t>Hensoldt</t>
+          <t>GAF Geospatial GmbH</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1726,7 +1727,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Project Lead Police Helicopters (w/m/d)</t>
+          <t>Junior Project Manager – Software Development and Operations</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -1734,29 +1735,29 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>...equisition ID: 5556 Location: Fürstenfeldbruck, DE, 82256 Company: ESG Elekt...</t>
+          <t>...r team at our headquarters in Munich , we are looking for a motiva...</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Project-Lead-Police-Helicopters-%28wmd%29-82256/1361623855/</t>
+          <t>https://careers.gaf.de/junior-project-manager-software-development-and-operations/</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="B40" t="inlineStr">
         <is>
-          <t>Siemens Energy</t>
+          <t>Hensoldt</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Zurich</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Cybersecurity Transformation Program Lead (f/m/d)</t>
+          <t>Project Lead Police Helicopters (w/m/d)</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -1764,12 +1765,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>...ob ID 301947 Location Germany Baden-Wuerttemberg Karlsruhe Countr...</t>
+          <t>...equisition ID: 5556 Location: Fürstenfeldbruck, DE, 82256 Company: ESG Elekt...</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://jobs.siemens-energy.com/en_US/jobs/FolderDetail/Cybersecurity-Transformation-Program-Lead-f-m-d/301947</t>
+          <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Project-Lead-Police-Helicopters-%28wmd%29-82256/1361623855/</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1787,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Projektmanager (w/m/d) für Leistungstransformatoren</t>
+          <t>Cybersecurity Transformation Program Lead (f/m/d)</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -1794,19 +1795,19 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>...m Power Transformers Europe Clusters (MPT) in Deutschland, Österr...</t>
+          <t>...ob ID 301947 Location Germany Baden-Wuerttemberg Karlsruhe Countr...</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://jobs.siemens-energy.com/en_US/jobs/FolderDetail/Projektmanager-w-m-d-f-r-Leistungstransformatoren/301604</t>
+          <t>https://jobs.siemens-energy.com/en_US/jobs/FolderDetail/Cybersecurity-Transformation-Program-Lead-f-m-d/301947</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="B42" t="inlineStr">
         <is>
-          <t>Hensoldt</t>
+          <t>Siemens Energy</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1816,7 +1817,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Technical Project Manager Space (w/m/d)</t>
+          <t>Projektmanager (w/m/d) für Leistungstransformatoren</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -1824,12 +1825,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>...ng technischer Arbeitspakete, Meilensteine, Liefergegenstände, Res...</t>
+          <t>...m Power Transformers Europe Clusters (MPT) in Deutschland, Österr...</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://jobs.hensoldt.net/job/Immenstaad-Technical-Project-Manager-Space-%28wmd%29-88090/1365577355/</t>
+          <t>https://jobs.siemens-energy.com/en_US/jobs/FolderDetail/Projektmanager-w-m-d-f-r-Leistungstransformatoren/301604</t>
         </is>
       </c>
     </row>
@@ -1846,7 +1847,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Projektleiter Space (w/m/d)</t>
+          <t>Technical Project Manager Space (w/m/d)</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -1854,59 +1855,59 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>...ationaler Kundenprojekte in Bezug auf elektro-optische Systeme...</t>
+          <t>...ng technischer Arbeitspakete, Meilensteine, Liefergegenstände, Res...</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://jobs.hensoldt.net/job/Oberkochen-Projektleiter-Space-%28wmd%29-73447/1362330955/</t>
+          <t>https://jobs.hensoldt.net/job/Immenstaad-Technical-Project-Manager-Space-%28wmd%29-88090/1365577355/</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="B44" t="inlineStr">
         <is>
-          <t>Aeromaritime Systembau GmbH</t>
+          <t>Hensoldt</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>Zurich</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Project Manager (m/f/d)</t>
+          <t>Projektleiter Space (w/m/d)</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>...ement Location: Neufahrn near Freising, Germany Start Date: As soon...</t>
+          <t>...ationaler Kundenprojekte in Bezug auf elektro-optische Systeme...</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://aeromaritimegroup.com/jobs/project-manager-m-f-d/</t>
+          <t>https://jobs.hensoldt.net/job/Oberkochen-Projektleiter-Space-%28wmd%29-73447/1362330955/</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="B45" t="inlineStr">
         <is>
-          <t>Michael Page Switzerland</t>
+          <t>Aeromaritime Systembau GmbH</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Zurich</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Project Manager</t>
+          <t>Project Manager (m/f/d)</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -1914,12 +1915,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+          <t>...ement Location: Neufahrn near Freising, Germany Start Date: As soon...</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.michaelpage.ch/jobs/project-manager</t>
+          <t>https://aeromaritimegroup.com/jobs/project-manager-m-f-d/</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1937,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>IT Project Manager - FR / GE</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -1949,7 +1950,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.michaelpage.ch/fr/job-detail/it-project-manager-fr-ge/ref/jn-062026-7044696?lang=en</t>
+          <t>https://www.michaelpage.ch/jobs/project-manager</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1967,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Senior Hands-On IT Project Manager - Integration</t>
+          <t>IT Project Manager - FR / GE</t>
         </is>
       </c>
       <c r="E47" t="n">
@@ -1979,24 +1980,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.michaelpage.ch/job-detail/senior-hands-it-project-manager-integration/ref/jn-052026-7008447</t>
+          <t>https://www.michaelpage.ch/fr/job-detail/it-project-manager-fr-ge/ref/jn-062026-7044696?lang=en</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="B48" t="inlineStr">
         <is>
-          <t>Hensoldt</t>
+          <t>Michael Page Switzerland</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>Zurich</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Projektleiter Software Defined Defence (SDD) (w/m/d)</t>
+          <t>Senior Hands-On IT Project Manager - Integration</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -2004,10 +2005,40 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.ch/job-detail/senior-hands-it-project-manager-integration/ref/jn-052026-7008447</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Hensoldt</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Projektleiter Software Defined Defence (SDD) (w/m/d)</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>3</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
           <t>...equisition ID: 3422 Location: Fürstenfeldbruck, DE, 82256 Company: ESG Elekt...</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Projektleiter-Software-Defined-Defence-%28SDD%29-%28wmd%29-82256/1352828255/</t>
         </is>
@@ -2024,7 +2055,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2104,99 +2135,101 @@
       </c>
     </row>
     <row r="3">
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Siemens Energy</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Basel</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Project Manager (f/m/d) – Service &amp; Repair (Gas Turbine Components)</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>5</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>...gungssicherheit. Steuerung globaler Lieferketten einschließlich...</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>https://jobs.siemens-energy.com/en_US/jobs/FolderDetail/Project-Manager-f-m-d-Service-Repair-Gas-Turbine-Components/303134</t>
+      <c r="A3" s="3" t="inlineStr"/>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>MBDA Deutschland</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Bern</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>DS Procurement SAP Project Manager F/H Informatique Le Plessis-Robinson (92) CDI</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>...-M SURFACE LAUNCHED BRIMSTONE THUNDART Area Protection ASTER Fam...</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>https://www.mbda-systems.com/country-fr/careers/ds-procurement-sap-project-manager-fh-r38140</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Hensoldt</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr"/>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>MBDA Deutschland</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Bern</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Angebots- und Projektmanager EW Systems (w/m/d)</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>4</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>...Angebots- und Projektmanager übernehmen Sie die Verantwortung fü...</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>https://jobs.hensoldt.net/job/Ulm-Angebots-und-Projektmanager-EW-Systems-%28wmd%29-89077/1361578255/</t>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Chef de projet métier FPGA  F/H Electronique, Electrique Le Plessis-Robinson (92) CDI</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>...-M SURFACE LAUNCHED BRIMSTONE THUNDART Area Protection ASTER Fam...</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>https://www.mbda-systems.com/country-fr/careers/chef-de-projet-metier-fpga-fh-r38173</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="B5" t="inlineStr">
         <is>
-          <t>Hensoldt</t>
+          <t>Siemens Energy</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bern</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Angebots- und Projektmanager EW Systems (w/m/d)</t>
+          <t>Project Manager (f/m/d) – Service &amp; Repair (Gas Turbine Components)</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>...gplattformen. In Ihrer Rolle übernehmen Sie die Verantwortung fü...</t>
+          <t>...gungssicherheit. Steuerung globaler Lieferketten einschließlich...</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://jobs.hensoldt.net/job/Ulm-Angebots-und-Projektmanager-EW-Systems-%28wmd%29-89077/1364864055/</t>
+          <t>https://jobs.siemens-energy.com/en_US/jobs/FolderDetail/Project-Manager-f-m-d-Service-Repair-Gas-Turbine-Components/303134</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="B6" t="inlineStr">
         <is>
-          <t>OBERMEYER Servbest GmbH</t>
+          <t>Hensoldt</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2206,7 +2239,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>SENIOR PROJEKTMANAGER (m/w/d)</t>
+          <t>Angebots- und Projektmanager EW Systems (w/m/d)</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -2214,19 +2247,19 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>...wie internationale Märkte erobern und sowohl unsere als auch ih...</t>
+          <t>...Angebots- und Projektmanager übernehmen Sie die Verantwortung fü...</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://karriere.obermeyer-group.com/Vacancies/2564/Description/1</t>
+          <t>https://jobs.hensoldt.net/job/Ulm-Angebots-und-Projektmanager-EW-Systems-%28wmd%29-89077/1361578255/</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="B7" t="inlineStr">
         <is>
-          <t>Siemens Energy</t>
+          <t>Hensoldt</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2236,7 +2269,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Projektmanager (w/m/d) Air-Insulated Switchgear (AIS) / Transformatoren</t>
+          <t>Angebots- und Projektmanager EW Systems (w/m/d)</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -2244,19 +2277,19 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>...g Als Projektmanager (w/m/d) übernehmen Sie die Verantwortung fü...</t>
+          <t>...gplattformen. In Ihrer Rolle übernehmen Sie die Verantwortung fü...</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://jobs.siemens-energy.com/en_US/jobs/FolderDetail/Projektmanager-w-m-d-Air-Insulated-Switchgear-AIS-Transformatoren/303755</t>
+          <t>https://jobs.hensoldt.net/job/Ulm-Angebots-und-Projektmanager-EW-Systems-%28wmd%29-89077/1364864055/</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="B8" t="inlineStr">
         <is>
-          <t>Siemens Energy</t>
+          <t>OBERMEYER Servbest GmbH</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2266,7 +2299,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Projektmanager (w/m/d) Gas-Insulated Switchgear (GIS)</t>
+          <t>SENIOR PROJEKTMANAGER (m/w/d)</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -2274,19 +2307,19 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>...sen hinweg – von der Auftragsübernahme bis zur Übergabe an den K...</t>
+          <t>...wie internationale Märkte erobern und sowohl unsere als auch ih...</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://jobs.siemens-energy.com/en_US/jobs/FolderDetail/Projektmanager-w-m-d-Gas-Insulated-Switchgear-GIS/303756</t>
+          <t>https://karriere.obermeyer-group.com/Vacancies/2564/Description/1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="B9" t="inlineStr">
         <is>
-          <t>ILF Beratende Ingenieure GmbH</t>
+          <t>Siemens Energy</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2296,27 +2329,27 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Projektleiter:in im Bereich Infrastruktur</t>
+          <t>Projektmanager (w/m/d) Air-Insulated Switchgear (AIS) / Transformatoren</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>...Kabelinfrastrukturprojekten) übernehmen. Sie werden mit der Leit...</t>
+          <t>...g Als Projektmanager (w/m/d) übernehmen Sie die Verantwortung fü...</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.ilf.com/job/?id=2876</t>
+          <t>https://jobs.siemens-energy.com/en_US/jobs/FolderDetail/Projektmanager-w-m-d-Air-Insulated-Switchgear-AIS-Transformatoren/303755</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="B10" t="inlineStr">
         <is>
-          <t>ILF Beratende Ingenieure GmbH</t>
+          <t>Siemens Energy</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2326,20 +2359,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Projektleiter:in im Bereich Infrastruktur</t>
+          <t>Projektmanager (w/m/d) Gas-Insulated Switchgear (GIS)</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>...Kabelinfrastrukturprojekten) übernehmen. Sie werden mit der Leit...</t>
+          <t>...sen hinweg – von der Auftragsübernahme bis zur Übergabe an den K...</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.ilf.com/job/?id=2999</t>
+          <t>https://jobs.siemens-energy.com/en_US/jobs/FolderDetail/Projektmanager-w-m-d-Gas-Insulated-Switchgear-GIS/303756</t>
         </is>
       </c>
     </row>
@@ -2356,7 +2389,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Projektmanager:in Verkehr</t>
+          <t>Projektleiter:in im Bereich Infrastruktur</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -2364,10 +2397,70 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>...Kabelinfrastrukturprojekten) übernehmen. Sie werden mit der Leit...</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.ilf.com/job/?id=2876</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ILF Beratende Ingenieure GmbH</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Bern</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Projektleiter:in im Bereich Infrastruktur</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>3</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>...Kabelinfrastrukturprojekten) übernehmen. Sie werden mit der Leit...</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.ilf.com/job/?id=2999</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ILF Beratende Ingenieure GmbH</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Bern</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Projektmanager:in Verkehr</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>3</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t>...städtische Verkehrssysteme) übernehmen. Sie werden mit der Leit...</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>https://www.ilf.com/job/?id=2771</t>
         </is>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -1429,31 +1429,30 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr"/>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>Hensoldt</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
         <is>
           <t>Projektleiter Integrated Product Support Sanität (w/m/d)</t>
         </is>
       </c>
-      <c r="E30" s="2" t="n">
+      <c r="E30" t="n">
         <v>5</v>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>...equisition ID: 4940 Location: Fürstenfeldbruck, DE, 82256 Company: ESG Elekt...</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Projektleiter-Integrated-Product-Support-Sanit%C3%A4t-%28wmd%29-82256/1362543455/</t>
         </is>
@@ -2135,62 +2134,60 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr"/>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>MBDA Deutschland</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Bern</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>DS Procurement SAP Project Manager F/H Informatique Le Plessis-Robinson (92) CDI</t>
         </is>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="E3" t="n">
         <v>8</v>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>...-M SURFACE LAUNCHED BRIMSTONE THUNDART Area Protection ASTER Fam...</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>https://www.mbda-systems.com/country-fr/careers/ds-procurement-sap-project-manager-fh-r38140</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr"/>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>MBDA Deutschland</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Bern</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Chef de projet métier FPGA  F/H Electronique, Electrique Le Plessis-Robinson (92) CDI</t>
         </is>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="E4" t="n">
         <v>8</v>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>...-M SURFACE LAUNCHED BRIMSTONE THUNDART Area Protection ASTER Fam...</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>https://www.mbda-systems.com/country-fr/careers/chef-de-projet-metier-fpga-fh-r38173</t>
         </is>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G49"/>
+  <dimension ref="A1:G50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -944,54 +944,50 @@
       </c>
     </row>
     <row r="15">
-      <c r="B15" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Hensoldt</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Projektmanager Integration IAMD (w/m/d)</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>...equisition ID: 4098 Location: Fürstenfeldbruck, DE, 82256 Company: ESG Elekt...</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Projektmanager-Integration-IAMD-%28wmd%29-82256/1348113655/</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="inlineStr">
         <is>
           <t>Adnovum</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>Senior IT Program / Project Manager Financial Services (a)</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>6</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>...inancial Services (a) 80-100% Zurich What you're going to do Ready...</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://careers.adnovum.com/job/Zurich-Senior-IT-Program-Project-Manager-Financial-Services-%28a%29/1164878455/</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>ProGlove</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Senior Technical Project Manager</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -999,24 +995,24 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Munich Office</t>
+          <t>...inancial Services (a) 80-100% Zurich What you're going to do Ready...</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://proglove.jobs.personio.de/job/2732130</t>
+          <t>https://careers.adnovum.com/job/Zurich-Senior-IT-Program-Project-Manager-Financial-Services-%28a%29/1164878455/</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Helsing</t>
+          <t>ProGlove</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1026,7 +1022,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Programme Manager</t>
+          <t>Senior Technical Project Manager</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -1034,12 +1030,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>Munich Office</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://helsing.ai/jobs/4636978101?gh_jid=4636978101</t>
+          <t>https://proglove.jobs.personio.de/job/2732130</t>
         </is>
       </c>
     </row>
@@ -1061,7 +1057,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Programme Manager - Space</t>
+          <t>Programme Manager</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -1069,12 +1065,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Munich - Berlin</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://helsing.ai/jobs/4942502101?gh_jid=4942502101</t>
+          <t>https://helsing.ai/jobs/4636978101?gh_jid=4636978101</t>
         </is>
       </c>
     </row>
@@ -1096,7 +1092,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Senior Programme Manager - Maritime</t>
+          <t>Programme Manager - Space</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -1109,14 +1105,14 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://helsing.ai/jobs/4875025101?gh_jid=4875025101</t>
+          <t>https://helsing.ai/jobs/4942502101?gh_jid=4942502101</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1131,7 +1127,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>(Senior) Programme Manager Mission Systems</t>
+          <t>Senior Programme Manager - Maritime</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -1139,19 +1135,19 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>Munich - Berlin</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://helsing.ai/jobs/4968741101?gh_jid=4968741101</t>
+          <t>https://helsing.ai/jobs/4875025101?gh_jid=4875025101</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1166,7 +1162,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Technical Programme Manager - Air</t>
+          <t>(Senior) Programme Manager Mission Systems</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -1179,24 +1175,29 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://helsing.ai/jobs/4865991101?gh_jid=4865991101</t>
+          <t>https://helsing.ai/jobs/4968741101?gh_jid=4968741101</t>
         </is>
       </c>
     </row>
     <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Siemens Energy</t>
+          <t>Helsing</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Zurich</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Real Estate Project Manager (w/m/d)</t>
+          <t>Technical Programme Manager - Air</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -1204,29 +1205,29 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>...eichung der Projektziele in Bezug auf Qualität, Budget und Zeit...</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://jobs.siemens-energy.com/en_US/jobs/FolderDetail/Real-Estate-Project-Manager-w-m-d/302381</t>
+          <t>https://helsing.ai/jobs/4865991101?gh_jid=4865991101</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" t="inlineStr">
         <is>
-          <t>Hensoldt</t>
+          <t>Siemens Energy</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>Zurich</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Projektleiter TLB und Informationssicherheit P-8A (w/m/d)</t>
+          <t>Real Estate Project Manager (w/m/d)</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -1234,19 +1235,19 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>...equisition ID: 4852 Location: Fürstenfeldbruck, DE, 82256 Wurster Nordseeküs...</t>
+          <t>...eichung der Projektziele in Bezug auf Qualität, Budget und Zeit...</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Projektleiter-TLB-und-Informationssicherheit-P-8A-%28wmd%29-82256/1361632455/</t>
+          <t>https://jobs.siemens-energy.com/en_US/jobs/FolderDetail/Real-Estate-Project-Manager-w-m-d/302381</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" t="inlineStr">
         <is>
-          <t>Michael Page Germany</t>
+          <t>Hensoldt</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1256,7 +1257,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Projektleiter (m/w/d) Defence</t>
+          <t>Projektleiter TLB und Informationssicherheit P-8A (w/m/d)</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -1264,29 +1265,29 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
+          <t>...equisition ID: 4852 Location: Fürstenfeldbruck, DE, 82256 Wurster Nordseeküs...</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.michaelpage.de/job-detail/projektleiter-mwd-defence/ref/jn-092026-7105457</t>
+          <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Projektleiter-TLB-und-Informationssicherheit-P-8A-%28wmd%29-82256/1361632455/</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" t="inlineStr">
         <is>
-          <t>Hensoldt</t>
+          <t>Michael Page Germany</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Zurich</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Systems Engineer / Development Project Manager (DPM) (w/m/d)</t>
+          <t>Projektleiter (m/w/d) Defence</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -1294,12 +1295,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>...ntwicklungsarbeitspakete in Bezug auf Termine, Kosten und Quali...</t>
+          <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://jobs.hensoldt.net/job/Ulm-Systems-Engineer-Development-Project-Manager-%28DPM%29-%28wmd%29-89077/1362037255/</t>
+          <t>https://www.michaelpage.de/job-detail/projektleiter-mwd-defence/ref/jn-092026-7105457</t>
         </is>
       </c>
     </row>
@@ -1311,12 +1312,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>Zurich</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Projektmanager Selfprotection Ground (w/m/d)</t>
+          <t>Systems Engineer / Development Project Manager (DPM) (w/m/d)</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -1324,64 +1325,64 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
+          <t>...ntwicklungsarbeitspakete in Bezug auf Termine, Kosten und Quali...</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://jobs.hensoldt.net/job/Ulm-Systems-Engineer-Development-Project-Manager-%28DPM%29-%28wmd%29-89077/1362037255/</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Hensoldt</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Projektmanager Selfprotection Ground (w/m/d)</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
           <t>...equisition ID: 1850 Location: Taufkirchen, DE, 82024 Company: HENSOLDT...</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>https://jobs.hensoldt.net/job/Taufkirchen-Projektmanager-Selfprotection-Ground-%28wmd%29-82024/1325906955/</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>Isar Aerospace</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
         <is>
           <t>Project Manager Commercial (m/f/d)</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>5</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Ottobrunn, Bavaria, Germany; Parsdorf, Bavaria, Germany</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4949469101</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Munich Re</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Project Manager - SAP SuccessFactors (m/f/d)*</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -1389,29 +1390,29 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>...AP SuccessFactors (m/f/d)* in Munich at Munich Re Skip to main con...</t>
+          <t>Ottobrunn, Bavaria, Germany; Parsdorf, Bavaria, Germany</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://careers.munichre.com/en/job/munich/project-manager-sap-successfactors-m-f-d/3342/44462004480</t>
+          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4949469101</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="B29" t="inlineStr">
         <is>
-          <t>Michael Page Switzerland</t>
+          <t>Munich Re</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Zurich</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>IT Project Manager</t>
+          <t>Project Manager - SAP SuccessFactors (m/f/d)*</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -1419,29 +1420,29 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+          <t>...AP SuccessFactors (m/f/d)* in Munich at Munich Re Skip to main con...</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.michaelpage.ch/job-detail/it-project-manager/ref/jn-092026-7100459</t>
+          <t>https://careers.munichre.com/en/job/munich/project-manager-sap-successfactors-m-f-d/3342/44462004480</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" t="inlineStr">
         <is>
-          <t>Hensoldt</t>
+          <t>Michael Page Switzerland</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>Zurich</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Projektleiter Integrated Product Support Sanität (w/m/d)</t>
+          <t>IT Project Manager</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -1449,47 +1450,42 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.ch/job-detail/it-project-manager/ref/jn-092026-7100459</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Hensoldt</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Projektleiter Integrated Product Support Sanität (w/m/d)</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>5</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
           <t>...equisition ID: 4940 Location: Fürstenfeldbruck, DE, 82256 Company: ESG Elekt...</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Projektleiter-Integrated-Product-Support-Sanit%C3%A4t-%28wmd%29-82256/1362543455/</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Celonis</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Customer Engagement Program Manager - Scale Team</t>
-        </is>
-      </c>
-      <c r="E31" t="n">
-        <v>4</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Munich, Germany</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/7823007003?gh_jid=7823007003</t>
         </is>
       </c>
     </row>
@@ -1511,7 +1507,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Customer Success Program Manager - Scale Team</t>
+          <t>Customer Engagement Program Manager - Scale Team</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -1524,14 +1520,14 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/7823005003?gh_jid=7823005003</t>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7823007003?gh_jid=7823007003</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1546,7 +1542,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Lead Project Manager</t>
+          <t>Customer Success Program Manager - Scale Team</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -1559,24 +1555,29 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/7683452003?gh_jid=7683452003</t>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7823005003?gh_jid=7823005003</t>
         </is>
       </c>
     </row>
     <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ETH Zurich</t>
+          <t>Celonis</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Zurich</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Projektleiter:in IT (w/m/d) 60%-100%, Zürich, befristet 08.09.2026                 |                 Informatikdienste</t>
+          <t>Lead Project Manager</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -1584,19 +1585,19 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>...eiter:in IT (w/m/d) 60%-100%, Zürich, befristet print Drucken An d...</t>
+          <t>Munich, Germany</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://jobs.ethz.ch/job/view/JOPG_ethz_Mv6A7zxfE2ogt3097w</t>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7683452003?gh_jid=7683452003</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="B35" t="inlineStr">
         <is>
-          <t>Michael Page Switzerland</t>
+          <t>ETH Zurich</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1606,7 +1607,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>IT Project Manager / Product Owner</t>
+          <t>Projektleiter:in IT (w/m/d) 60%-100%, Zürich, befristet 08.09.2026                 |                 Informatikdienste</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -1614,29 +1615,29 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+          <t>...eiter:in IT (w/m/d) 60%-100%, Zürich, befristet print Drucken An d...</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.michaelpage.ch/job-detail/it-project-manager-product-owner/ref/jn-072026-7053211</t>
+          <t>https://jobs.ethz.ch/job/view/JOPG_ethz_Mv6A7zxfE2ogt3097w</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="B36" t="inlineStr">
         <is>
-          <t>Michael Page Germany</t>
+          <t>Michael Page Switzerland</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>Zurich</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Projektmanager SAP Einführung (gn)</t>
+          <t>IT Project Manager / Product Owner</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -1644,29 +1645,29 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.michaelpage.de/job-detail/projektmanager-sap-einf%C3%BChrung-gn/ref/jn-072026-7074884</t>
+          <t>https://www.michaelpage.ch/job-detail/it-project-manager-product-owner/ref/jn-072026-7053211</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="B37" t="inlineStr">
         <is>
-          <t>Hensoldt</t>
+          <t>Michael Page Germany</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Zurich</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Projektleiter ILS/IPS (w/m/d)</t>
+          <t>Projektmanager SAP Einführung (gn)</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -1674,19 +1675,19 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>...für Produkte und Projekte des zugehörigen Programmbereichs Ange...</t>
+          <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://jobs.hensoldt.net/job/Ulm-Projektleiter-ILSIPS-%28wmd%29-89077/1363566455/</t>
+          <t>https://www.michaelpage.de/job-detail/projektmanager-sap-einf%C3%BChrung-gn/ref/jn-072026-7074884</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="B38" t="inlineStr">
         <is>
-          <t>Bundesamt fur Informatik BIT</t>
+          <t>Hensoldt</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1696,7 +1697,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Projektleiter/-in für grosskalibrige Munition Bundesamt für Rüstung armasuisse Bern | 100%</t>
+          <t>Projektleiter ILS/IPS (w/m/d)</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -1704,29 +1705,29 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>...hschulabschluss (Bachelor) vorzugsweise in Elektrotechnik oder...</t>
+          <t>...für Produkte und Projekte des zugehörigen Programmbereichs Ange...</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://jobs.admin.ch/offene-stellen/projektleiter-in-fuer-grosskalibrige-munition/54119111-a980-43d3-8597-e9fd348e9a01</t>
+          <t>https://jobs.hensoldt.net/job/Ulm-Projektleiter-ILSIPS-%28wmd%29-89077/1363566455/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="B39" t="inlineStr">
         <is>
-          <t>GAF Geospatial GmbH</t>
+          <t>Bundesamt fur Informatik BIT</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>Zurich</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Junior Project Manager – Software Development and Operations</t>
+          <t>Projektleiter/-in für grosskalibrige Munition Bundesamt für Rüstung armasuisse Bern | 100%</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -1734,19 +1735,19 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>...r team at our headquarters in Munich , we are looking for a motiva...</t>
+          <t>...hschulabschluss (Bachelor) vorzugsweise in Elektrotechnik oder...</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://careers.gaf.de/junior-project-manager-software-development-and-operations/</t>
+          <t>https://jobs.admin.ch/offene-stellen/projektleiter-in-fuer-grosskalibrige-munition/54119111-a980-43d3-8597-e9fd348e9a01</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="B40" t="inlineStr">
         <is>
-          <t>Hensoldt</t>
+          <t>GAF Geospatial GmbH</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1756,7 +1757,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Project Lead Police Helicopters (w/m/d)</t>
+          <t>Junior Project Manager – Software Development and Operations</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -1764,29 +1765,29 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>...equisition ID: 5556 Location: Fürstenfeldbruck, DE, 82256 Company: ESG Elekt...</t>
+          <t>...r team at our headquarters in Munich , we are looking for a motiva...</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Project-Lead-Police-Helicopters-%28wmd%29-82256/1361623855/</t>
+          <t>https://careers.gaf.de/junior-project-manager-software-development-and-operations/</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="B41" t="inlineStr">
         <is>
-          <t>Siemens Energy</t>
+          <t>Hensoldt</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Zurich</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Cybersecurity Transformation Program Lead (f/m/d)</t>
+          <t>Project Lead Police Helicopters (w/m/d)</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -1794,12 +1795,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>...ob ID 301947 Location Germany Baden-Wuerttemberg Karlsruhe Countr...</t>
+          <t>...equisition ID: 5556 Location: Fürstenfeldbruck, DE, 82256 Company: ESG Elekt...</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://jobs.siemens-energy.com/en_US/jobs/FolderDetail/Cybersecurity-Transformation-Program-Lead-f-m-d/301947</t>
+          <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Project-Lead-Police-Helicopters-%28wmd%29-82256/1361623855/</t>
         </is>
       </c>
     </row>
@@ -1816,7 +1817,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Projektmanager (w/m/d) für Leistungstransformatoren</t>
+          <t>Cybersecurity Transformation Program Lead (f/m/d)</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -1824,19 +1825,19 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>...m Power Transformers Europe Clusters (MPT) in Deutschland, Österr...</t>
+          <t>...ob ID 301947 Location Germany Baden-Wuerttemberg Karlsruhe Countr...</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://jobs.siemens-energy.com/en_US/jobs/FolderDetail/Projektmanager-w-m-d-f-r-Leistungstransformatoren/301604</t>
+          <t>https://jobs.siemens-energy.com/en_US/jobs/FolderDetail/Cybersecurity-Transformation-Program-Lead-f-m-d/301947</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="B43" t="inlineStr">
         <is>
-          <t>Hensoldt</t>
+          <t>Siemens Energy</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1846,7 +1847,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Technical Project Manager Space (w/m/d)</t>
+          <t>Projektmanager (w/m/d) für Leistungstransformatoren</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -1854,12 +1855,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>...ng technischer Arbeitspakete, Meilensteine, Liefergegenstände, Res...</t>
+          <t>...m Power Transformers Europe Clusters (MPT) in Deutschland, Österr...</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://jobs.hensoldt.net/job/Immenstaad-Technical-Project-Manager-Space-%28wmd%29-88090/1365577355/</t>
+          <t>https://jobs.siemens-energy.com/en_US/jobs/FolderDetail/Projektmanager-w-m-d-f-r-Leistungstransformatoren/301604</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1877,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Projektleiter Space (w/m/d)</t>
+          <t>Technical Project Manager Space (w/m/d)</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -1884,59 +1885,59 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>...ationaler Kundenprojekte in Bezug auf elektro-optische Systeme...</t>
+          <t>...ng technischer Arbeitspakete, Meilensteine, Liefergegenstände, Res...</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://jobs.hensoldt.net/job/Oberkochen-Projektleiter-Space-%28wmd%29-73447/1362330955/</t>
+          <t>https://jobs.hensoldt.net/job/Immenstaad-Technical-Project-Manager-Space-%28wmd%29-88090/1365577355/</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="B45" t="inlineStr">
         <is>
-          <t>Aeromaritime Systembau GmbH</t>
+          <t>Hensoldt</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>Zurich</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Project Manager (m/f/d)</t>
+          <t>Projektleiter Space (w/m/d)</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>...ement Location: Neufahrn near Freising, Germany Start Date: As soon...</t>
+          <t>...ationaler Kundenprojekte in Bezug auf elektro-optische Systeme...</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://aeromaritimegroup.com/jobs/project-manager-m-f-d/</t>
+          <t>https://jobs.hensoldt.net/job/Oberkochen-Projektleiter-Space-%28wmd%29-73447/1362330955/</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="B46" t="inlineStr">
         <is>
-          <t>Michael Page Switzerland</t>
+          <t>Aeromaritime Systembau GmbH</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Zurich</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Project Manager</t>
+          <t>Project Manager (m/f/d)</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -1944,12 +1945,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+          <t>...ement Location: Neufahrn near Freising, Germany Start Date: As soon...</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.michaelpage.ch/jobs/project-manager</t>
+          <t>https://aeromaritimegroup.com/jobs/project-manager-m-f-d/</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1967,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>IT Project Manager - FR / GE</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="E47" t="n">
@@ -1979,7 +1980,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.michaelpage.ch/fr/job-detail/it-project-manager-fr-ge/ref/jn-062026-7044696?lang=en</t>
+          <t>https://www.michaelpage.ch/jobs/project-manager</t>
         </is>
       </c>
     </row>
@@ -1996,7 +1997,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Senior Hands-On IT Project Manager - Integration</t>
+          <t>IT Project Manager - FR / GE</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -2009,24 +2010,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.michaelpage.ch/job-detail/senior-hands-it-project-manager-integration/ref/jn-052026-7008447</t>
+          <t>https://www.michaelpage.ch/fr/job-detail/it-project-manager-fr-ge/ref/jn-062026-7044696?lang=en</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="B49" t="inlineStr">
         <is>
-          <t>Hensoldt</t>
+          <t>Michael Page Switzerland</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>Zurich</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Projektleiter Software Defined Defence (SDD) (w/m/d)</t>
+          <t>Senior Hands-On IT Project Manager - Integration</t>
         </is>
       </c>
       <c r="E49" t="n">
@@ -2034,10 +2035,40 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.ch/job-detail/senior-hands-it-project-manager-integration/ref/jn-052026-7008447</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Hensoldt</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Projektleiter Software Defined Defence (SDD) (w/m/d)</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>3</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
           <t>...equisition ID: 3422 Location: Fürstenfeldbruck, DE, 82256 Company: ESG Elekt...</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Projektleiter-Software-Defined-Defence-%28SDD%29-%28wmd%29-82256/1352828255/</t>
         </is>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -31,7 +31,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -42,6 +42,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="001F2937"/>
         <bgColor rgb="001F2937"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D1FAE5"/>
+        <bgColor rgb="00D1FAE5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDE68A"/>
+        <bgColor rgb="00FDE68A"/>
       </patternFill>
     </fill>
   </fills>
@@ -57,9 +69,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -474,6 +488,565 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Alpine Eagle</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Project Manager (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Karlsruhe, Baden-Württemberg, Germany, München, Bavaria, Germany</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/alpineeagle/jobs/4699459101</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>ARX Robotics</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Mission Operations Project Manager (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/arxroboticsgmbh/jobs/4953147101</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Auterion</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Technical Program Manager</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>https://auterion.com/company/careers-open-position/8470060002?gh_jid=8470060002</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr"/>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Hensoldt</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Projektmanager Integration IAMD (w/m/d)</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>...equisition ID: 4098 Location: Fürstenfeldbruck, DE, 82256 Company: ESG Elekt...</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Projektmanager-Integration-IAMD-%28wmd%29-82256/1348113655/</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Isar Aerospace</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Senior Project Manager - Ground Systems Infrastructure (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Ottobrunn, Bavaria, Germany</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4756747101</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>ProGlove</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Senior Technical Project Manager</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Munich Office</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>https://proglove.jobs.personio.de/job/2732130</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr"/>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Germany</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Projektleiter (m/w/d) Defence</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.de/job-detail/projektleiter-mwd-defence/ref/jn-092026-7105457</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr"/>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Switzerland</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>IT Project Manager</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.ch/job-detail/it-project-manager/ref/jn-092026-7100459</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Customer Engagement Program Manager - Scale Team</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7823007003?gh_jid=7823007003</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Customer Success Program Manager - Scale Team</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7823005003?gh_jid=7823005003</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Lead Project Manager</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7683452003?gh_jid=7683452003</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>ETH Zurich</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Projektleiter:in IT (m/w/d) 60%-100%, Zürich, befristet 08.09.2026                 |                 Informatikdienste</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>...eiter:in IT (m/w/d) 60%-100%, Zürich, befristet print Drucken An d...</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.ethz.ch/job/view/JOPG_ethz_Mv6A7zxfE2ogt3097w</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>GAF Geospatial GmbH</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Junior Project Manager – Software Development and Operations</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>...r team at our headquarters in Munich , we are looking for a motiva...</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>https://careers.gaf.de/junior-project-manager-software-development-and-operations/</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Switzerland</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>IT Project Manager / Product Owner</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.ch/job-detail/it-project-manager-product-owner/ref/jn-072026-7053211</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Aeromaritime Systembau GmbH</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Project Manager (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>...ement Location: Neufahrn near Freising, Germany Start Date: As soon...</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>https://aeromaritimegroup.com/jobs/project-manager-m-f-d/</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Switzerland</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.ch/jobs/project-manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Switzerland</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>IT Project Manager - FR / GE</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.ch/fr/job-detail/it-project-manager-fr-ge/ref/jn-062026-7044696?lang=en</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -485,7 +1058,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -534,6 +1107,254 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr"/>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>MBDA Deutschland</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Bern</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>DS Procurement SAP Project Manager F/H Informatique Le Plessis-Robinson (92) CDI</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>...-M SURFACE LAUNCHED BRIMSTONE THUNDART Area Protection ASTER Fam...</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>https://www.mbda-systems.com/country-fr/careers/ds-procurement-sap-project-manager-fh-r38140</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr"/>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>MBDA Deutschland</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Bern</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Chef de projet métier FPGA  F/H Electronique, Electrique Le Plessis-Robinson (92) CDI</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>...-M SURFACE LAUNCHED BRIMSTONE THUNDART Area Protection ASTER Fam...</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>https://www.mbda-systems.com/country-fr/careers/chef-de-projet-metier-fpga-fh-r38173</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr"/>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Hensoldt</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Bern</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Projektleiter Airborne Solutions (w/m/d)</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>...eit mit öffentlichen Auftraggebern und Partnern Ausgeprägtes tec...</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>https://jobs.hensoldt.net/job/Immenstaad-Projektleiter-Airborne-Solutions-%28wmd%29-88090/1366090255/</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Siemens Energy</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Bern</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Projektleiter (w/m/d) Auftragsabwicklung und SAP-Schnittstellenkoordinator</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>...eblich voran. Darüber hinaus übernehmen Sie eine zentrale Rolle...</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>https://jobs.siemens-energy.com/en_US/jobs/FolderDetail/Projektleiter-w-m-d-Auftragsabwicklung-und-SAP-Schnittstellenkoordinator/302334</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>ERGO Group</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Basel</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Projektleiter Financial Closing Systems (m/w/d)</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>...dell Fachliche Führung von globalen und standortübergreifenden P...</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>https://careers.munichre.com/en/job/hamburg/projektleiter-financial-closing-systems-m-w-d/3382/35604047488</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>ILF Beratende Ingenieure GmbH</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Bern</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Projektleiter:in im Bereich Infrastruktur</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>...Kabelinfrastrukturprojekten) übernehmen. Sie werden mit der Leit...</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ilf.com/job/?id=2876</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>ILF Beratende Ingenieure GmbH</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Bern</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Projektleiter:in im Bereich Infrastruktur</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>...Kabelinfrastrukturprojekten) übernehmen. Sie werden mit der Leit...</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ilf.com/job/?id=2999</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>ILF Beratende Ingenieure GmbH</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Bern</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Projektmanager:in Verkehr</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>...städtische Verkehrssysteme) übernehmen. Sie werden mit der Leit...</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ilf.com/job/?id=2771</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -489,559 +489,550 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>2026-06-02</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Alpine Eagle</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Project Manager (m/f/d)</t>
         </is>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" t="n">
         <v>10</v>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Karlsruhe, Baden-Württemberg, Germany, München, Bavaria, Germany</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>https://job-boards.eu.greenhouse.io/alpineeagle/jobs/4699459101</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>ARX Robotics</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Mission Operations Project Manager (m/f/d)</t>
         </is>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E3" t="n">
         <v>10</v>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>https://job-boards.eu.greenhouse.io/arxroboticsgmbh/jobs/4953147101</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Auterion</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Technical Program Manager</t>
         </is>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="E4" t="n">
         <v>8</v>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>https://auterion.com/company/careers-open-position/8470060002?gh_jid=8470060002</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr"/>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Hensoldt</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Projektmanager Integration IAMD (w/m/d)</t>
         </is>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="E5" t="n">
         <v>7</v>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>...equisition ID: 4098 Location: Fürstenfeldbruck, DE, 82256 Company: ESG Elekt...</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Projektmanager-Integration-IAMD-%28wmd%29-82256/1348113655/</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Isar Aerospace</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>Senior Project Manager - Ground Systems Infrastructure (m/f/d)</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="E6" t="n">
         <v>7</v>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>Ottobrunn, Bavaria, Germany</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4756747101</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>ProGlove</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Senior Technical Project Manager</t>
         </is>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="E7" t="n">
         <v>6</v>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>Munich Office</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>https://proglove.jobs.personio.de/job/2732130</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr"/>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Michael Page Germany</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Projektleiter (m/w/d) Defence</t>
         </is>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="E8" t="n">
         <v>6</v>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>https://www.michaelpage.de/job-detail/projektleiter-mwd-defence/ref/jn-092026-7105457</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr"/>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Michael Page Switzerland</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>IT Project Manager</t>
         </is>
       </c>
-      <c r="E9" s="2" t="n">
+      <c r="E9" t="n">
         <v>5</v>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>https://www.michaelpage.ch/job-detail/it-project-manager/ref/jn-092026-7100459</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>Customer Engagement Program Manager - Scale Team</t>
         </is>
       </c>
-      <c r="E10" s="2" t="n">
+      <c r="E10" t="n">
         <v>4</v>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/7823007003?gh_jid=7823007003</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>Customer Success Program Manager - Scale Team</t>
         </is>
       </c>
-      <c r="E11" s="2" t="n">
+      <c r="E11" t="n">
         <v>4</v>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/7823005003?gh_jid=7823005003</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>Lead Project Manager</t>
         </is>
       </c>
-      <c r="E12" s="2" t="n">
+      <c r="E12" t="n">
         <v>4</v>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/7683452003?gh_jid=7683452003</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr"/>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>ETH Zurich</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>Projektleiter:in IT (m/w/d) 60%-100%, Zürich, befristet 08.09.2026                 |                 Informatikdienste</t>
         </is>
       </c>
-      <c r="E13" s="2" t="n">
+      <c r="E13" t="n">
         <v>4</v>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>...eiter:in IT (m/w/d) 60%-100%, Zürich, befristet print Drucken An d...</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>https://jobs.ethz.ch/job/view/JOPG_ethz_Mv6A7zxfE2ogt3097w</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr"/>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>GAF Geospatial GmbH</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>Junior Project Manager – Software Development and Operations</t>
         </is>
       </c>
-      <c r="E14" s="2" t="n">
+      <c r="E14" t="n">
         <v>4</v>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>...r team at our headquarters in Munich , we are looking for a motiva...</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>https://careers.gaf.de/junior-project-manager-software-development-and-operations/</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr"/>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>Michael Page Switzerland</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>IT Project Manager / Product Owner</t>
         </is>
       </c>
-      <c r="E15" s="2" t="n">
+      <c r="E15" t="n">
         <v>4</v>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>https://www.michaelpage.ch/job-detail/it-project-manager-product-owner/ref/jn-072026-7053211</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr"/>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>Aeromaritime Systembau GmbH</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>Project Manager (m/f/d)</t>
         </is>
       </c>
-      <c r="E16" s="2" t="n">
+      <c r="E16" t="n">
         <v>3</v>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>...ement Location: Neufahrn near Freising, Germany Start Date: As soon...</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>https://aeromaritimegroup.com/jobs/project-manager-m-f-d/</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr"/>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>Michael Page Switzerland</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>Project Manager</t>
         </is>
       </c>
-      <c r="E17" s="2" t="n">
+      <c r="E17" t="n">
         <v>3</v>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>https://www.michaelpage.ch/jobs/project-manager</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr"/>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>Michael Page Switzerland</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>IT Project Manager - FR / GE</t>
         </is>
       </c>
-      <c r="E18" s="2" t="n">
+      <c r="E18" t="n">
         <v>3</v>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>https://www.michaelpage.ch/fr/job-detail/it-project-manager-fr-ge/ref/jn-062026-7044696?lang=en</t>
         </is>
@@ -1058,7 +1049,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1108,62 +1099,60 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr"/>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>MBDA Deutschland</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Bern</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>DS Procurement SAP Project Manager F/H Informatique Le Plessis-Robinson (92) CDI</t>
         </is>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="E2" t="n">
         <v>8</v>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>...-M SURFACE LAUNCHED BRIMSTONE THUNDART Area Protection ASTER Fam...</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>https://www.mbda-systems.com/country-fr/careers/ds-procurement-sap-project-manager-fh-r38140</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr"/>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>MBDA Deutschland</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Bern</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Chef de projet métier FPGA  F/H Electronique, Electrique Le Plessis-Robinson (92) CDI</t>
         </is>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="E3" t="n">
         <v>8</v>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>...-M SURFACE LAUNCHED BRIMSTONE THUNDART Area Protection ASTER Fam...</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>https://www.mbda-systems.com/country-fr/careers/chef-de-projet-metier-fpga-fh-r38173</t>
         </is>
@@ -1173,183 +1162,208 @@
       <c r="A4" s="3" t="inlineStr"/>
       <c r="B4" s="3" t="inlineStr">
         <is>
+          <t>MBDA Deutschland</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Bern</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Chef de projet Equipement de tests  F/H Nouveau Electronique, Electrique Bourges (18) CDI</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>...-M SURFACE LAUNCHED BRIMSTONE THUNDART Area Protection ASTER Fam...</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>https://www.mbda-systems.com/country-fr/careers/chef-de-projet-equipement-de-tests-fh-r39318</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
           <t>Hensoldt</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Bern</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Projektleiter Airborne Solutions (w/m/d)</t>
         </is>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="E5" t="n">
         <v>6</v>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>...eit mit öffentlichen Auftraggebern und Partnern Ausgeprägtes tec...</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>https://jobs.hensoldt.net/job/Immenstaad-Projektleiter-Airborne-Solutions-%28wmd%29-88090/1366090255/</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr"/>
-      <c r="B5" s="3" t="inlineStr">
+    <row r="6">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Siemens Energy</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Bern</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>Projektleiter (w/m/d) Auftragsabwicklung und SAP-Schnittstellenkoordinator</t>
         </is>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="E6" t="n">
         <v>4</v>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>...eblich voran. Darüber hinaus übernehmen Sie eine zentrale Rolle...</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>https://jobs.siemens-energy.com/en_US/jobs/FolderDetail/Projektleiter-w-m-d-Auftragsabwicklung-und-SAP-Schnittstellenkoordinator/302334</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr"/>
-      <c r="B6" s="3" t="inlineStr">
+    <row r="7">
+      <c r="B7" t="inlineStr">
         <is>
           <t>ERGO Group</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Basel</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Projektleiter Financial Closing Systems (m/w/d)</t>
         </is>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="E7" t="n">
         <v>4</v>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>...dell Fachliche Führung von globalen und standortübergreifenden P...</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>https://careers.munichre.com/en/job/hamburg/projektleiter-financial-closing-systems-m-w-d/3382/35604047488</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr"/>
-      <c r="B7" s="3" t="inlineStr">
+    <row r="8">
+      <c r="B8" t="inlineStr">
         <is>
           <t>ILF Beratende Ingenieure GmbH</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Bern</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Projektleiter:in im Bereich Infrastruktur</t>
         </is>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="E8" t="n">
         <v>3</v>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>...Kabelinfrastrukturprojekten) übernehmen. Sie werden mit der Leit...</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>https://www.ilf.com/job/?id=2876</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr"/>
-      <c r="B8" s="3" t="inlineStr">
+    <row r="9">
+      <c r="B9" t="inlineStr">
         <is>
           <t>ILF Beratende Ingenieure GmbH</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Bern</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>Projektleiter:in im Bereich Infrastruktur</t>
         </is>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="E9" t="n">
         <v>3</v>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>...Kabelinfrastrukturprojekten) übernehmen. Sie werden mit der Leit...</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>https://www.ilf.com/job/?id=2999</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr"/>
-      <c r="B9" s="3" t="inlineStr">
+    <row r="10">
+      <c r="B10" t="inlineStr">
         <is>
           <t>ILF Beratende Ingenieure GmbH</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Bern</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>Projektmanager:in Verkehr</t>
         </is>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="E10" t="n">
         <v>3</v>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>...städtische Verkehrssysteme) übernehmen. Sie werden mit der Leit...</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>https://www.ilf.com/job/?id=2771</t>
         </is>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -31,7 +31,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -42,6 +42,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="001F2937"/>
         <bgColor rgb="001F2937"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D1FAE5"/>
+        <bgColor rgb="00D1FAE5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDE68A"/>
+        <bgColor rgb="00FDE68A"/>
       </patternFill>
     </fill>
   </fills>
@@ -57,9 +69,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -474,6 +488,441 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Alpine Eagle</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Project Manager (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Karlsruhe, Baden-Württemberg, Germany, München, Bavaria, Germany</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/alpineeagle/jobs/4699459101</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>ARX Robotics</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Mission Operations Project Manager (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/arxroboticsgmbh/jobs/4953147101</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Auterion</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Technical Program Manager</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>https://auterion.com/company/careers-open-position/8470060002?gh_jid=8470060002</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Isar Aerospace</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Senior Project Manager - Ground Systems Infrastructure (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Ottobrunn, Bavaria, Germany</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4756747101</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>ProGlove</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Senior Technical Project Manager</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Munich Office</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>https://proglove.jobs.personio.de/job/2732130</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr"/>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Germany</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Projektleiter (m/w/d) Defence</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.de/job-detail/projektleiter-mwd-defence/ref/jn-092026-7105457</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr"/>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Switzerland</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>IT Project Manager</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.ch/job-detail/it-project-manager/ref/jn-092026-7100459</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Customer Engagement Program Manager - Scale Team</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7823007003?gh_jid=7823007003</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Customer Success Program Manager - Scale Team</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7823005003?gh_jid=7823005003</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Lead Project Manager</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7683452003?gh_jid=7683452003</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>GAF Geospatial GmbH</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Junior Project Manager – Software Development and Operations</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>...r team at our headquarters in Munich , we are looking for a motiva...</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>https://careers.gaf.de/junior-project-manager-software-development-and-operations/</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Switzerland</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.ch/jobs/project-manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Switzerland</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>IT Project Manager - FR / GE</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.ch/fr/job-detail/it-project-manager-fr-ge/ref/jn-062026-7044696?lang=en</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -485,7 +934,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -534,6 +983,223 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr"/>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>MBDA Deutschland</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Bern</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Chef de projet Equipement de tests  F/H Nouveau Electronique, Electrique Bourges (18) CDI</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>...-M SURFACE LAUNCHED BRIMSTONE THUNDART Area Protection ASTER Fam...</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>https://www.mbda-systems.com/country-fr/careers/chef-de-projet-equipement-de-tests-fh-r39318</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr"/>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Hensoldt</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Bern</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Projektleiter Airborne Solutions (w/m/d)</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>...eit mit öffentlichen Auftraggebern und Partnern Ausgeprägtes tec...</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>https://jobs.hensoldt.net/job/Immenstaad-Projektleiter-Airborne-Solutions-%28wmd%29-88090/1366090255/</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr"/>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Siemens Energy</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Bern</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Projektleiter (w/m/d) Auftragsabwicklung und SAP-Schnittstellenkoordinator</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>...eblich voran. Darüber hinaus übernehmen Sie eine zentrale Rolle...</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>https://jobs.siemens-energy.com/en_US/jobs/FolderDetail/Projektleiter-w-m-d-Auftragsabwicklung-und-SAP-Schnittstellenkoordinator/302334</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>ERGO Group</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Basel</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Projektleiter Financial Closing Systems (m/w/d)</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>...dell Fachliche Führung von globalen und standortübergreifenden P...</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>https://careers.munichre.com/en/job/hamburg/projektleiter-financial-closing-systems-m-w-d/3382/35604047488</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>ILF Beratende Ingenieure GmbH</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Bern</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Projektleiter:in im Bereich Infrastruktur</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>...Kabelinfrastrukturprojekten) übernehmen. Sie werden mit der Leit...</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ilf.com/job/?id=2876</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>ILF Beratende Ingenieure GmbH</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Bern</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Projektleiter:in im Bereich Infrastruktur</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>...Kabelinfrastrukturprojekten) übernehmen. Sie werden mit der Leit...</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ilf.com/job/?id=2999</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>ILF Beratende Ingenieure GmbH</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Bern</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Projektmanager:in Verkehr</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>...städtische Verkehrssysteme) übernehmen. Sie werden mit der Leit...</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ilf.com/job/?id=2771</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -31,7 +31,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -42,6 +42,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="001F2937"/>
         <bgColor rgb="001F2937"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D1FAE5"/>
+        <bgColor rgb="00D1FAE5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDE68A"/>
+        <bgColor rgb="00FDE68A"/>
       </patternFill>
     </fill>
   </fills>
@@ -57,9 +69,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -474,6 +488,375 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Alpine Eagle</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Project Manager (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Karlsruhe, Baden-Württemberg, Germany, München, Bavaria, Germany</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/alpineeagle/jobs/4699459101</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>ARX Robotics</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Mission Operations Project Manager (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/arxroboticsgmbh/jobs/4953147101</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Auterion</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Technical Program Manager</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>https://auterion.com/company/careers-open-position/8470060002?gh_jid=8470060002</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Isar Aerospace</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Senior Project Manager - Ground Systems Infrastructure (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Ottobrunn, Bavaria, Germany</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4756747101</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr"/>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Germany</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Projektleiter (m/w/d) Defence</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.de/job-detail/projektleiter-mwd-defence/ref/jn-092026-7105457</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr"/>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Switzerland</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>IT Project Manager</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.ch/job-detail/it-project-manager/ref/jn-092026-7100459</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Customer Engagement Program Manager - Scale Team</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7823007003?gh_jid=7823007003</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Customer Success Program Manager - Scale Team</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7823005003?gh_jid=7823005003</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Lead Project Manager</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7683452003?gh_jid=7683452003</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Switzerland</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.ch/jobs/project-manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Switzerland</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>IT Project Manager - FR / GE</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.ch/fr/job-detail/it-project-manager-fr-ge/ref/jn-062026-7044696?lang=en</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -485,7 +868,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -534,6 +917,68 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr"/>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>MBDA Deutschland</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Bern</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Chef de projet Equipement de tests  F/H Nouveau Electronique, Electrique Bourges (18) CDI</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>...-M SURFACE LAUNCHED BRIMSTONE THUNDART Area Protection ASTER Fam...</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>https://www.mbda-systems.com/country-fr/careers/chef-de-projet-equipement-de-tests-fh-r39318</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr"/>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Hensoldt</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Bern</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Projektleiter Airborne Solutions (w/m/d)</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>...eit mit öffentlichen Auftraggebern und Partnern Ausgeprägtes tec...</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>https://jobs.hensoldt.net/job/Immenstaad-Projektleiter-Airborne-Solutions-%28wmd%29-88090/1366090255/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -489,369 +489,365 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>2026-06-02</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Alpine Eagle</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Project Manager (m/f/d)</t>
         </is>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" t="n">
         <v>10</v>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Karlsruhe, Baden-Württemberg, Germany, München, Bavaria, Germany</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>https://job-boards.eu.greenhouse.io/alpineeagle/jobs/4699459101</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>ARX Robotics</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Mission Operations Project Manager (m/f/d)</t>
         </is>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E3" t="n">
         <v>10</v>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>https://job-boards.eu.greenhouse.io/arxroboticsgmbh/jobs/4953147101</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Auterion</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Technical Program Manager</t>
         </is>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="E4" t="n">
         <v>8</v>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>https://auterion.com/company/careers-open-position/8470060002?gh_jid=8470060002</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Isar Aerospace</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Senior Project Manager - Ground Systems Infrastructure (m/f/d)</t>
         </is>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="E5" t="n">
         <v>7</v>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>Ottobrunn, Bavaria, Germany</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4756747101</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr"/>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Michael Page Germany</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>Projektleiter (m/w/d) Defence</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="E6" t="n">
         <v>6</v>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>https://www.michaelpage.de/job-detail/projektleiter-mwd-defence/ref/jn-092026-7105457</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr"/>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Michael Page Switzerland</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>IT Project Manager</t>
         </is>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="E7" t="n">
         <v>5</v>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>https://www.michaelpage.ch/job-detail/it-project-manager/ref/jn-092026-7100459</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Customer Engagement Program Manager - Scale Team</t>
         </is>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="E8" t="n">
         <v>4</v>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/7823007003?gh_jid=7823007003</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>Customer Success Program Manager - Scale Team</t>
         </is>
       </c>
-      <c r="E9" s="2" t="n">
+      <c r="E9" t="n">
         <v>4</v>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/7823005003?gh_jid=7823005003</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>Lead Project Manager</t>
         </is>
       </c>
-      <c r="E10" s="2" t="n">
+      <c r="E10" t="n">
         <v>4</v>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/7683452003?gh_jid=7683452003</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr"/>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Michael Page Switzerland</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>Project Manager</t>
         </is>
       </c>
-      <c r="E11" s="2" t="n">
+      <c r="E11" t="n">
         <v>3</v>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>https://www.michaelpage.ch/jobs/project-manager</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr"/>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Michael Page Switzerland</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>IT Project Manager - FR / GE</t>
         </is>
       </c>
-      <c r="E12" s="2" t="n">
+      <c r="E12" t="n">
         <v>3</v>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>https://www.michaelpage.ch/fr/job-detail/it-project-manager-fr-ge/ref/jn-062026-7044696?lang=en</t>
         </is>
@@ -918,62 +914,60 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr"/>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>MBDA Deutschland</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Bern</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Chef de projet Equipement de tests  F/H Nouveau Electronique, Electrique Bourges (18) CDI</t>
         </is>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="E2" t="n">
         <v>8</v>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>...-M SURFACE LAUNCHED BRIMSTONE THUNDART Area Protection ASTER Fam...</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>https://www.mbda-systems.com/country-fr/careers/chef-de-projet-equipement-de-tests-fh-r39318</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr"/>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Hensoldt</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Bern</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Projektleiter Airborne Solutions (w/m/d)</t>
         </is>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="E3" t="n">
         <v>6</v>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>...eit mit öffentlichen Auftraggebern und Partnern Ausgeprägtes tec...</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>https://jobs.hensoldt.net/job/Immenstaad-Projektleiter-Airborne-Solutions-%28wmd%29-88090/1366090255/</t>
         </is>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -864,7 +864,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -944,30 +944,61 @@
       </c>
     </row>
     <row r="3">
-      <c r="B3" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr"/>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>MBDA Deutschland</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Bern</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Chef de Projets Événementiel Recrutement &amp; Marque Employeur F/H Nouveau Ressources humaines Le Plessis-Robinson (92) CDD</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>...-M SURFACE LAUNCHED BRIMSTONE THUNDART Area Protection ASTER Fam...</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>https://www.mbda-systems.com/country-fr/careers/chef-de-projets-evenementiel-recrutement-marque-employeur-fh-r39446</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Hensoldt</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Bern</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Projektleiter Airborne Solutions (w/m/d)</t>
         </is>
       </c>
-      <c r="E3" t="n">
+      <c r="E4" t="n">
         <v>6</v>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>...eit mit öffentlichen Auftraggebern und Partnern Ausgeprägtes tec...</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>https://jobs.hensoldt.net/job/Immenstaad-Projektleiter-Airborne-Solutions-%28wmd%29-88090/1366090255/</t>
         </is>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -629,97 +629,93 @@
       </c>
     </row>
     <row r="6">
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Michael Page Germany</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Projektleiter (m/w/d) Defence</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>6</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://www.michaelpage.de/job-detail/projektleiter-mwd-defence/ref/jn-092026-7105457</t>
+      <c r="A6" s="2" t="inlineStr"/>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Hensoldt</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>(Teil-)Projektleiter Counter-UAS Requirements &amp; Design (m/w/d)</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>...rganisatorische Steuerung der zugeordneten Mitarbeiter Ansprech...</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-%28Teil-%29Projektleiter-Counter-UAS-Requirements-&amp;-Design-%28mwd%29-82256/1363116955/</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="B7" t="inlineStr">
         <is>
+          <t>Michael Page Germany</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Projektleiter (m/w/d) Defence</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.de/job-detail/projektleiter-mwd-defence/ref/jn-092026-7105457</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
           <t>Michael Page Switzerland</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>IT Project Manager</t>
         </is>
       </c>
-      <c r="E7" t="n">
+      <c r="E8" t="n">
         <v>5</v>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>https://www.michaelpage.ch/job-detail/it-project-manager/ref/jn-092026-7100459</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Celonis</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Customer Engagement Program Manager - Scale Team</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>4</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Munich, Germany</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/7823007003?gh_jid=7823007003</t>
         </is>
       </c>
     </row>
@@ -741,7 +737,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Customer Success Program Manager - Scale Team</t>
+          <t>Customer Engagement Program Manager - Scale Team</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -754,14 +750,14 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/7823005003?gh_jid=7823005003</t>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7823007003?gh_jid=7823007003</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -776,7 +772,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Lead Project Manager</t>
+          <t>Customer Success Program Manager - Scale Team</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -789,37 +785,42 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7823005003?gh_jid=7823005003</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Lead Project Manager</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>4</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/7683452003?gh_jid=7683452003</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Michael Page Switzerland</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Zurich</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Project Manager</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>3</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.michaelpage.ch/jobs/project-manager</t>
         </is>
       </c>
     </row>
@@ -836,7 +837,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>IT Project Manager - FR / GE</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -848,6 +849,36 @@
         </is>
       </c>
       <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.ch/jobs/project-manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Michael Page Switzerland</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>IT Project Manager - FR / GE</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>3</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
         <is>
           <t>https://www.michaelpage.ch/fr/job-detail/it-project-manager-fr-ge/ref/jn-062026-7044696?lang=en</t>
         </is>
@@ -944,31 +975,30 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr"/>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>MBDA Deutschland</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Bern</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Chef de Projets Événementiel Recrutement &amp; Marque Employeur F/H Nouveau Ressources humaines Le Plessis-Robinson (92) CDD</t>
         </is>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="E3" t="n">
         <v>8</v>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>...-M SURFACE LAUNCHED BRIMSTONE THUNDART Area Protection ASTER Fam...</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>https://www.mbda-systems.com/country-fr/careers/chef-de-projets-evenementiel-recrutement-marque-employeur-fh-r39446</t>
         </is>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -629,31 +629,30 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr"/>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Hensoldt</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>(Teil-)Projektleiter Counter-UAS Requirements &amp; Design (m/w/d)</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="E6" t="n">
         <v>7</v>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>...rganisatorische Steuerung der zugeordneten Mitarbeiter Ansprech...</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-%28Teil-%29Projektleiter-Counter-UAS-Requirements-&amp;-Design-%28mwd%29-82256/1363116955/</t>
         </is>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -31,7 +31,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -42,18 +42,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="001F2937"/>
         <bgColor rgb="001F2937"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D1FAE5"/>
-        <bgColor rgb="00D1FAE5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FDE68A"/>
-        <bgColor rgb="00FDE68A"/>
       </patternFill>
     </fill>
   </fills>
@@ -69,11 +57,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -439,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -488,401 +474,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Alpine Eagle</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Project Manager (m/f/d)</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>10</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Karlsruhe, Baden-Württemberg, Germany, München, Bavaria, Germany</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>https://job-boards.eu.greenhouse.io/alpineeagle/jobs/4699459101</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>ARX Robotics</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Mission Operations Project Manager (m/f/d)</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>10</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>https://job-boards.eu.greenhouse.io/arxroboticsgmbh/jobs/4953147101</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Auterion</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Technical Program Manager</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>8</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Munich, Germany</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>https://auterion.com/company/careers-open-position/8470060002?gh_jid=8470060002</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Isar Aerospace</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Senior Project Manager - Ground Systems Infrastructure (m/f/d)</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>7</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Ottobrunn, Bavaria, Germany</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4756747101</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Hensoldt</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Zurich</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>(Teil-)Projektleiter Counter-UAS Requirements &amp; Design (m/w/d)</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>7</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>...rganisatorische Steuerung der zugeordneten Mitarbeiter Ansprech...</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-%28Teil-%29Projektleiter-Counter-UAS-Requirements-&amp;-Design-%28mwd%29-82256/1363116955/</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Michael Page Germany</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Projektleiter (m/w/d) Defence</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>6</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.michaelpage.de/job-detail/projektleiter-mwd-defence/ref/jn-092026-7105457</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Michael Page Switzerland</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Zurich</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>IT Project Manager</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>5</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.michaelpage.ch/job-detail/it-project-manager/ref/jn-092026-7100459</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Celonis</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Customer Engagement Program Manager - Scale Team</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>4</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Munich, Germany</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/7823007003?gh_jid=7823007003</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Celonis</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Customer Success Program Manager - Scale Team</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>4</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Munich, Germany</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/7823005003?gh_jid=7823005003</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Celonis</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Lead Project Manager</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>4</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Munich, Germany</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/7683452003?gh_jid=7683452003</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Michael Page Switzerland</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Zurich</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Project Manager</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>3</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.michaelpage.ch/jobs/project-manager</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Michael Page Switzerland</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Zurich</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>IT Project Manager - FR / GE</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>3</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.michaelpage.ch/fr/job-detail/it-project-manager-fr-ge/ref/jn-062026-7044696?lang=en</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -894,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -943,96 +534,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>MBDA Deutschland</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Bern</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Chef de projet Equipement de tests  F/H Nouveau Electronique, Electrique Bourges (18) CDI</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>8</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>...-M SURFACE LAUNCHED BRIMSTONE THUNDART Area Protection ASTER Fam...</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>https://www.mbda-systems.com/country-fr/careers/chef-de-projet-equipement-de-tests-fh-r39318</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>MBDA Deutschland</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Bern</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Chef de Projets Événementiel Recrutement &amp; Marque Employeur F/H Nouveau Ressources humaines Le Plessis-Robinson (92) CDD</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>8</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>...-M SURFACE LAUNCHED BRIMSTONE THUNDART Area Protection ASTER Fam...</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>https://www.mbda-systems.com/country-fr/careers/chef-de-projets-evenementiel-recrutement-marque-employeur-fh-r39446</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Hensoldt</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Bern</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Projektleiter Airborne Solutions (w/m/d)</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>6</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>...eit mit öffentlichen Auftraggebern und Partnern Ausgeprägtes tec...</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>https://jobs.hensoldt.net/job/Immenstaad-Projektleiter-Airborne-Solutions-%28wmd%29-88090/1366090255/</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -31,7 +31,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -42,6 +42,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="001F2937"/>
         <bgColor rgb="001F2937"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D1FAE5"/>
+        <bgColor rgb="00D1FAE5"/>
       </patternFill>
     </fill>
   </fills>
@@ -57,9 +63,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -471,6 +478,410 @@
       <c r="G1" s="1" t="inlineStr">
         <is>
           <t>URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Alpine Eagle</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Project Manager (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Karlsruhe, Baden-Württemberg, Germany, München, Bavaria, Germany</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/alpineeagle/jobs/4699459101</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>ARX Robotics</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Mission Operations Project Manager (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/arxroboticsgmbh/jobs/4953147101</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Auterion</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Technical Program Manager</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>https://auterion.com/company/careers-open-position/8470060002?gh_jid=8470060002</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Isar Aerospace</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Senior Project Manager - Ground Systems Infrastructure (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Ottobrunn, Bavaria, Germany</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4756747101</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr"/>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Germany</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Projektleiter (m/w/d) Defence</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.de/job-detail/projektleiter-mwd-defence/ref/jn-092026-7105457</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr"/>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Switzerland</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>IT Project Manager</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.ch/job-detail/it-project-manager/ref/jn-092026-7100459</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Customer Engagement Program Manager - Scale Team</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7823007003?gh_jid=7823007003</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Customer Success Program Manager - Scale Team</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7823005003?gh_jid=7823005003</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Lead Project Manager</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7683452003?gh_jid=7683452003</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Entrix</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Junior Portfolio Manager (d/f/m)</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>https://entrix.jobs.personio.de/job/2663715</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Switzerland</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.ch/jobs/project-manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Switzerland</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>IT Project Manager - FR / GE</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.ch/fr/job-detail/it-project-manager-fr-ge/ref/jn-062026-7044696?lang=en</t>
         </is>
       </c>
     </row>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -482,373 +482,370 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>2026-06-02</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Alpine Eagle</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
         <is>
           <t>Project Manager (m/f/d)</t>
         </is>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" t="n">
         <v>10</v>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Karlsruhe, Baden-Württemberg, Germany, München, Bavaria, Germany</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>https://job-boards.eu.greenhouse.io/alpineeagle/jobs/4699459101</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>ARX Robotics</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
         <is>
           <t>Mission Operations Project Manager (m/f/d)</t>
         </is>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E3" t="n">
         <v>10</v>
       </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
         <is>
           <t>https://job-boards.eu.greenhouse.io/arxroboticsgmbh/jobs/4953147101</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Auterion</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
         <is>
           <t>Technical Program Manager</t>
         </is>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="E4" t="n">
         <v>8</v>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>https://auterion.com/company/careers-open-position/8470060002?gh_jid=8470060002</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Isar Aerospace</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
         <is>
           <t>Senior Project Manager - Ground Systems Infrastructure (m/f/d)</t>
         </is>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="E5" t="n">
         <v>7</v>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>Ottobrunn, Bavaria, Germany</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4756747101</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr"/>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Michael Page Germany</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
         <is>
           <t>Projektleiter (m/w/d) Defence</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="E6" t="n">
         <v>6</v>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>https://www.michaelpage.de/job-detail/projektleiter-mwd-defence/ref/jn-092026-7105457</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr"/>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Michael Page Switzerland</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>IT Project Manager</t>
         </is>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="E7" t="n">
         <v>5</v>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>https://www.michaelpage.ch/job-detail/it-project-manager/ref/jn-092026-7100459</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
         <is>
           <t>Customer Engagement Program Manager - Scale Team</t>
         </is>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="E8" t="n">
         <v>4</v>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/7823007003?gh_jid=7823007003</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
         <is>
           <t>Customer Success Program Manager - Scale Team</t>
         </is>
       </c>
-      <c r="E9" s="2" t="n">
+      <c r="E9" t="n">
         <v>4</v>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/7823005003?gh_jid=7823005003</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
         <is>
           <t>Lead Project Manager</t>
         </is>
       </c>
-      <c r="E10" s="2" t="n">
+      <c r="E10" t="n">
         <v>4</v>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/7683452003?gh_jid=7683452003</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Entrix</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
         <is>
           <t>Junior Portfolio Manager (d/f/m)</t>
         </is>
       </c>
-      <c r="E11" s="2" t="n">
+      <c r="E11" t="n">
         <v>4</v>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
         <is>
           <t>https://entrix.jobs.personio.de/job/2663715</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr"/>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Michael Page Switzerland</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>Project Manager</t>
         </is>
       </c>
-      <c r="E12" s="2" t="n">
+      <c r="E12" t="n">
         <v>4</v>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>https://www.michaelpage.ch/jobs/project-manager</t>
         </is>
@@ -858,30 +855,122 @@
       <c r="A13" s="2" t="inlineStr"/>
       <c r="B13" s="2" t="inlineStr">
         <is>
+          <t>Hensoldt</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Projektleiter Programm in Tactical Datalink Solutions (w/m/d)</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>...equisition ID: 4887 Location: Taufkirchen, DE, 82024 Company: HENSOLDT...</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.hensoldt.net/job/Taufkirchen-Projektleiter-Programm-in-Tactical-Datalink-Solutions-%28wmd%29-82024/1352617455/</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>Michael Page Switzerland</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Creative Project Manager (9-Month Interim Assignment) Asap- Asana &amp; Figma- English</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.ch/job-detail/creative-project-manager-9-month-interim-assignment/ref/jn-102026-7120382</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Michael Page Switzerland</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
         <is>
           <t>IT Project Manager - FR / GE</t>
         </is>
       </c>
-      <c r="E13" s="2" t="n">
+      <c r="E15" t="n">
         <v>3</v>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>https://www.michaelpage.ch/fr/job-detail/it-project-manager-fr-ge/ref/jn-062026-7044696?lang=en</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Switzerland</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>IT Project Manager</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.ch/job-detail/it-project-manager/ref/jn-102026-7121274</t>
         </is>
       </c>
     </row>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -31,7 +31,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -42,12 +42,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="001F2937"/>
         <bgColor rgb="001F2937"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D1FAE5"/>
-        <bgColor rgb="00D1FAE5"/>
       </patternFill>
     </fill>
   </fills>
@@ -63,10 +57,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -432,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -478,499 +471,6 @@
       <c r="G1" s="1" t="inlineStr">
         <is>
           <t>URL</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Alpine Eagle</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Project Manager (m/f/d)</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>10</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Karlsruhe, Baden-Württemberg, Germany, München, Bavaria, Germany</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>https://job-boards.eu.greenhouse.io/alpineeagle/jobs/4699459101</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>ARX Robotics</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Mission Operations Project Manager (m/f/d)</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>10</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>https://job-boards.eu.greenhouse.io/arxroboticsgmbh/jobs/4953147101</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Auterion</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Technical Program Manager</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>8</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Munich, Germany</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>https://auterion.com/company/careers-open-position/8470060002?gh_jid=8470060002</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Isar Aerospace</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Senior Project Manager - Ground Systems Infrastructure (m/f/d)</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>7</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Ottobrunn, Bavaria, Germany</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4756747101</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Michael Page Germany</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Projektleiter (m/w/d) Defence</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>6</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://www.michaelpage.de/job-detail/projektleiter-mwd-defence/ref/jn-092026-7105457</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Michael Page Switzerland</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Zurich</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>IT Project Manager</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>5</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.michaelpage.ch/job-detail/it-project-manager/ref/jn-092026-7100459</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Celonis</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Customer Engagement Program Manager - Scale Team</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>4</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Munich, Germany</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/7823007003?gh_jid=7823007003</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Celonis</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Customer Success Program Manager - Scale Team</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>4</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Munich, Germany</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/7823005003?gh_jid=7823005003</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Celonis</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Lead Project Manager</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>4</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Munich, Germany</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/7683452003?gh_jid=7683452003</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Entrix</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Junior Portfolio Manager (d/f/m)</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>4</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://entrix.jobs.personio.de/job/2663715</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Michael Page Switzerland</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Zurich</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Project Manager</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>4</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.michaelpage.ch/jobs/project-manager</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr"/>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>Hensoldt</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>Projektleiter Programm in Tactical Datalink Solutions (w/m/d)</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>...equisition ID: 4887 Location: Taufkirchen, DE, 82024 Company: HENSOLDT...</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>https://jobs.hensoldt.net/job/Taufkirchen-Projektleiter-Programm-in-Tactical-Datalink-Solutions-%28wmd%29-82024/1352617455/</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr"/>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>Michael Page Switzerland</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Zurich</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>Creative Project Manager (9-Month Interim Assignment) Asap- Asana &amp; Figma- English</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>https://www.michaelpage.ch/job-detail/creative-project-manager-9-month-interim-assignment/ref/jn-102026-7120382</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Michael Page Switzerland</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Zurich</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>IT Project Manager - FR / GE</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>3</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.michaelpage.ch/fr/job-detail/it-project-manager-fr-ge/ref/jn-062026-7044696?lang=en</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr"/>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>Michael Page Switzerland</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Zurich</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>IT Project Manager</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>https://www.michaelpage.ch/job-detail/it-project-manager/ref/jn-102026-7121274</t>
         </is>
       </c>
     </row>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -31,7 +31,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -42,6 +42,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="001F2937"/>
         <bgColor rgb="001F2937"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D1FAE5"/>
+        <bgColor rgb="00D1FAE5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDE68A"/>
+        <bgColor rgb="00FDE68A"/>
       </patternFill>
     </fill>
   </fills>
@@ -57,9 +69,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -474,6 +488,929 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Alpine Eagle</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Project Manager (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Karlsruhe, Baden-Württemberg, Germany, München, Bavaria, Germany</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/alpineeagle/jobs/4699459101</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>ARX Robotics</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Mission Operations Project Manager (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/arxroboticsgmbh/jobs/4953147101</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Isar Aerospace</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Senior Project Manager - Ground Systems Infrastructure (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Ottobrunn, Bavaria, Germany</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4756747101</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Scalable Capital</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>IT Project Manager (m/f/x)</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>München, de</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.smartrecruiters.com/ScalableGmbH/744000146123649</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>QPLIX</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>IT Project Manager (m/w/d)</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>München</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>https://qplix.jobs.personio.de/job/2269376</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr"/>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Randstad Germany</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Projektmanager</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>...am Main Hamburg Köln Leipzig München Stuttgart Top Suchbegriffe La...</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.randstad.de/jobs/b-wirtschaft-und-administration/t-administration-und-verwaltung/j-projektmanager/</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr"/>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Randstad Germany</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Projektmanager (m/w/d)</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>...am Main Hamburg Köln Leipzig München Stuttgart Top Suchbegriffe La...</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.randstad.de/jobs/projektmanager-mwd_bremen_c01338232/</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr"/>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Randstad Germany</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Projektmanager (m/w/d)</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>...am Main Hamburg Köln Leipzig München Stuttgart Top Suchbegriffe La...</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.randstad.de/jobs/projektmanager-mwd_barchfeld-immelborn_c01332512/</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr"/>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Randstad Germany</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Projektmanager (m/w/d)</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>...am Main Hamburg Köln Leipzig München Stuttgart Top Suchbegriffe La...</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.randstad.de/jobs/projektmanager-mwd_berlin_c01343736/</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Randstad Germany</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Projektmanager (m/w/d)</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>...am Main Hamburg Köln Leipzig München Stuttgart Top Suchbegriffe La...</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.randstad.de/jobs/projektmanager-mwd_augsburg_c01343637/</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Randstad Germany</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Projektmanager (m/w/d)</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Projektmanager (m/w/d) in München | Randstad randstad Jobsuche...</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.randstad.de/jobs/projektmanager-mwd_muenchen_c01346300/</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Randstad Germany</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Projektmanager Bau (m/w/d)</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>...am Main Hamburg Köln Leipzig München Stuttgart Top Suchbegriffe La...</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.randstad.de/jobs/projektmanager-bau-mwd_erkrath_c01327518/</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Randstad Germany</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Projektmanager (m/w/d)</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>...am Main Hamburg Köln Leipzig München Stuttgart Top Suchbegriffe La...</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.randstad.de/jobs/projektmanager-mwd_quedlinburg_c01322820/</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Randstad Germany</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Projektmanager (m/w/d)</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>...am Main Hamburg Köln Leipzig München Stuttgart Top Suchbegriffe La...</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.randstad.de/jobs/projektmanager-mwd_wilsdruff_c01340996/</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Randstad Germany</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Projektmanager (m/w/d), Airbus</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>...am Main Hamburg Köln Leipzig München Stuttgart Top Suchbegriffe La...</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.randstad.de/jobs/projektmanager-mwd_bremen_c01333741/</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Randstad Germany</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Projektmanager (m/w/d)</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>...am Main Hamburg Köln Leipzig München Stuttgart Top Suchbegriffe La...</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.randstad.de/jobs/projektmanager-mwd_bergheim_c01339132/</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Randstad Germany</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Projektmanager (m/w/d)</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>...am Main Hamburg Köln Leipzig München Stuttgart Top Suchbegriffe La...</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.randstad.de/jobs/projektmanager-mwd_bergheim_c01339130/</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Randstad Germany</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Projektmanager (m/w/d)</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>...am Main Hamburg Köln Leipzig München Stuttgart Top Suchbegriffe La...</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.randstad.de/jobs/projektmanager-mwd_bremen_c01326141/</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Randstad Germany</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Projektleiter ( 6 )</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>...am Main Hamburg Köln Leipzig München Stuttgart Top Suchbegriffe La...</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.randstad.de/jobs/b-wirtschaft-und-administration/t-administration-und-verwaltung/j-projektleiter/</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Germany</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Projektleiter (m/w/d) Defence</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.de/job-detail/projektleiter-mwd-defence/ref/jn-092026-7105457</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Switzerland</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>IT Project Manager</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.ch/job-detail/it-project-manager/ref/jn-092026-7100459</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Hensoldt</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Projektleiter Programm in Tactical Datalink Solutions (w/m/d)</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>...equisition ID: 4887 Location: Taufkirchen, DE, 82024 Company: HENSOLDT...</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.hensoldt.net/job/Taufkirchen-Projektleiter-Programm-in-Tactical-Datalink-Solutions-%28wmd%29-82024/1352617455/</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>QPLIX</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Senior Implementation Manager | Wealth Tech | 80-100% (m/w/d)</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Zürich</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>https://qplix.jobs.personio.de/job/2669346</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Switzerland</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.ch/jobs/project-manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Switzerland</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Creative Project Manager (9-Month Interim Assignment) Asap- Asana &amp; Figma- English</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.ch/job-detail/creative-project-manager-9-month-interim-assignment/ref/jn-102026-7120382</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Hoffmann Group</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>eBusiness Projektmanager (m/w/d) - München</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>...ness Projektmanager (m/w/d) - München bei Hoffmann SE 德语 český Deut...</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>https://career.hoffmann-group.com/eBusiness-Projektmanager-mwd-Muenchen-de-j2193.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Hoffmann Group</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>eBusiness Projektmanager (m/w/d) - Nürnberg</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>...uschuss Kostenlosen Werkzeugbezug/Mitarbeiterrabatt auf den ges...</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>https://career.hoffmann-group.com/eBusiness-Projektmanager-mwd-Nuernberg-de-j2152.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Switzerland</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>IT Project Manager</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.ch/job-detail/it-project-manager/ref/jn-102026-7121274</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Switzerland</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>IT Project Manager - FR / GE</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.ch/fr/job-detail/it-project-manager-fr-ge/ref/jn-062026-7044696?lang=en</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -485,7 +1422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -534,6 +1471,37 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr"/>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Siemens Energy</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Bern</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Experienced Commercial Project Manager (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>...on Ihrem Tag In dieser Rolle übernehmen Sie die kommerzielle Füh...</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>https://jobs.siemens-energy.com/en_US/jobs/FolderDetail/Experienced-Commercial-Project-Manager-m-f-d/301245</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -489,923 +489,970 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>2026-06-02</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Alpine Eagle</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
         <is>
           <t>Project Manager (m/f/d)</t>
         </is>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" t="n">
         <v>10</v>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Karlsruhe, Baden-Württemberg, Germany, München, Bavaria, Germany</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>https://job-boards.eu.greenhouse.io/alpineeagle/jobs/4699459101</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>ARX Robotics</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
         <is>
           <t>Mission Operations Project Manager (m/f/d)</t>
         </is>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E3" t="n">
         <v>10</v>
       </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
         <is>
           <t>https://job-boards.eu.greenhouse.io/arxroboticsgmbh/jobs/4953147101</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Isar Aerospace</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
         <is>
           <t>Senior Project Manager - Ground Systems Infrastructure (m/f/d)</t>
         </is>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="E4" t="n">
         <v>7</v>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Ottobrunn, Bavaria, Germany</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4756747101</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Scalable Capital</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
         <is>
           <t>IT Project Manager (m/f/x)</t>
         </is>
       </c>
-      <c r="E5" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="E5" t="n">
+        <v>6</v>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>München, de</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>https://jobs.smartrecruiters.com/ScalableGmbH/744000146123649</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>2025-07-30</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>QPLIX</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
         <is>
           <t>IT Project Manager (m/w/d)</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="E6" t="n">
+        <v>6</v>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>München</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>https://qplix.jobs.personio.de/job/2269376</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr"/>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Randstad Germany</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
         <is>
           <t>Projektmanager</t>
         </is>
       </c>
-      <c r="E7" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="E7" t="n">
+        <v>6</v>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>...am Main Hamburg Köln Leipzig München Stuttgart Top Suchbegriffe La...</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>https://www.randstad.de/jobs/b-wirtschaft-und-administration/t-administration-und-verwaltung/j-projektmanager/</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr"/>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Randstad Germany</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
         <is>
           <t>Projektmanager (m/w/d)</t>
         </is>
       </c>
-      <c r="E8" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="E8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>...am Main Hamburg Köln Leipzig München Stuttgart Top Suchbegriffe La...</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>https://www.randstad.de/jobs/projektmanager-mwd_bremen_c01338232/</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr"/>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Randstad Germany</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
         <is>
           <t>Projektmanager (m/w/d)</t>
         </is>
       </c>
-      <c r="E9" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="E9" t="n">
+        <v>6</v>
+      </c>
+      <c r="F9" t="inlineStr">
         <is>
           <t>...am Main Hamburg Köln Leipzig München Stuttgart Top Suchbegriffe La...</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>https://www.randstad.de/jobs/projektmanager-mwd_barchfeld-immelborn_c01332512/</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr"/>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Randstad Germany</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
         <is>
           <t>Projektmanager (m/w/d)</t>
         </is>
       </c>
-      <c r="E10" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="E10" t="n">
+        <v>6</v>
+      </c>
+      <c r="F10" t="inlineStr">
         <is>
           <t>...am Main Hamburg Köln Leipzig München Stuttgart Top Suchbegriffe La...</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>https://www.randstad.de/jobs/projektmanager-mwd_berlin_c01343736/</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr"/>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Randstad Germany</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
         <is>
           <t>Projektmanager (m/w/d)</t>
         </is>
       </c>
-      <c r="E11" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="E11" t="n">
+        <v>6</v>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t>...am Main Hamburg Köln Leipzig München Stuttgart Top Suchbegriffe La...</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>https://www.randstad.de/jobs/projektmanager-mwd_augsburg_c01343637/</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr"/>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Randstad Germany</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
         <is>
           <t>Projektmanager (m/w/d)</t>
         </is>
       </c>
-      <c r="E12" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="E12" t="n">
+        <v>6</v>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>Projektmanager (m/w/d) in München | Randstad randstad Jobsuche...</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>https://www.randstad.de/jobs/projektmanager-mwd_muenchen_c01346300/</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr"/>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Randstad Germany</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>Projektmanager Bau (m/w/d)</t>
         </is>
       </c>
-      <c r="E13" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="E13" t="n">
+        <v>6</v>
+      </c>
+      <c r="F13" t="inlineStr">
         <is>
           <t>...am Main Hamburg Köln Leipzig München Stuttgart Top Suchbegriffe La...</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>https://www.randstad.de/jobs/projektmanager-bau-mwd_erkrath_c01327518/</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr"/>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Randstad Germany</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t>Projektmanager (m/w/d)</t>
         </is>
       </c>
-      <c r="E14" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="E14" t="n">
+        <v>6</v>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>...am Main Hamburg Köln Leipzig München Stuttgart Top Suchbegriffe La...</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>https://www.randstad.de/jobs/projektmanager-mwd_quedlinburg_c01322820/</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr"/>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>Randstad Germany</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
         <is>
           <t>Projektmanager (m/w/d)</t>
         </is>
       </c>
-      <c r="E15" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="E15" t="n">
+        <v>6</v>
+      </c>
+      <c r="F15" t="inlineStr">
         <is>
           <t>...am Main Hamburg Köln Leipzig München Stuttgart Top Suchbegriffe La...</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>https://www.randstad.de/jobs/projektmanager-mwd_wilsdruff_c01340996/</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr"/>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>Randstad Germany</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
         <is>
           <t>Projektmanager (m/w/d), Airbus</t>
         </is>
       </c>
-      <c r="E16" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="E16" t="n">
+        <v>6</v>
+      </c>
+      <c r="F16" t="inlineStr">
         <is>
           <t>...am Main Hamburg Köln Leipzig München Stuttgart Top Suchbegriffe La...</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>https://www.randstad.de/jobs/projektmanager-mwd_bremen_c01333741/</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr"/>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>Randstad Germany</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
         <is>
           <t>Projektmanager (m/w/d)</t>
         </is>
       </c>
-      <c r="E17" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="E17" t="n">
+        <v>6</v>
+      </c>
+      <c r="F17" t="inlineStr">
         <is>
           <t>...am Main Hamburg Köln Leipzig München Stuttgart Top Suchbegriffe La...</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>https://www.randstad.de/jobs/projektmanager-mwd_bergheim_c01339132/</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr"/>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>Randstad Germany</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
         <is>
           <t>Projektmanager (m/w/d)</t>
         </is>
       </c>
-      <c r="E18" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="E18" t="n">
+        <v>6</v>
+      </c>
+      <c r="F18" t="inlineStr">
         <is>
           <t>...am Main Hamburg Köln Leipzig München Stuttgart Top Suchbegriffe La...</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>https://www.randstad.de/jobs/projektmanager-mwd_bergheim_c01339130/</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr"/>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>Randstad Germany</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
         <is>
           <t>Projektmanager (m/w/d)</t>
         </is>
       </c>
-      <c r="E19" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="E19" t="n">
+        <v>6</v>
+      </c>
+      <c r="F19" t="inlineStr">
         <is>
           <t>...am Main Hamburg Köln Leipzig München Stuttgart Top Suchbegriffe La...</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>https://www.randstad.de/jobs/projektmanager-mwd_bremen_c01326141/</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr"/>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>Randstad Germany</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
         <is>
           <t>Projektleiter ( 6 )</t>
         </is>
       </c>
-      <c r="E20" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="E20" t="n">
+        <v>6</v>
+      </c>
+      <c r="F20" t="inlineStr">
         <is>
           <t>...am Main Hamburg Köln Leipzig München Stuttgart Top Suchbegriffe La...</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>https://www.randstad.de/jobs/b-wirtschaft-und-administration/t-administration-und-verwaltung/j-projektleiter/</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr"/>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>Michael Page Germany</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
         <is>
           <t>Projektleiter (m/w/d) Defence</t>
         </is>
       </c>
-      <c r="E21" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="E21" t="n">
+        <v>6</v>
+      </c>
+      <c r="F21" t="inlineStr">
         <is>
           <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>https://www.michaelpage.de/job-detail/projektleiter-mwd-defence/ref/jn-092026-7105457</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr"/>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>Michael Page Switzerland</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>IT Project Manager</t>
         </is>
       </c>
-      <c r="E22" s="2" t="n">
+      <c r="E22" t="n">
         <v>5</v>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>https://www.michaelpage.ch/job-detail/it-project-manager/ref/jn-092026-7100459</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr"/>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>Hensoldt</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
         <is>
           <t>Projektleiter Programm in Tactical Datalink Solutions (w/m/d)</t>
         </is>
       </c>
-      <c r="E23" s="2" t="n">
+      <c r="E23" t="n">
         <v>4</v>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>...equisition ID: 4887 Location: Taufkirchen, DE, 82024 Company: HENSOLDT...</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>https://jobs.hensoldt.net/job/Taufkirchen-Projektleiter-Programm-in-Tactical-Datalink-Solutions-%28wmd%29-82024/1352617455/</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="A24" t="inlineStr">
         <is>
           <t>2026-06-12</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>QPLIX</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>Senior Implementation Manager | Wealth Tech | 80-100% (m/w/d)</t>
         </is>
       </c>
-      <c r="E24" s="2" t="n">
+      <c r="E24" t="n">
         <v>4</v>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>Zürich</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>https://qplix.jobs.personio.de/job/2669346</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr"/>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>Michael Page Switzerland</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>Project Manager</t>
         </is>
       </c>
-      <c r="E25" s="2" t="n">
+      <c r="E25" t="n">
         <v>4</v>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>https://www.michaelpage.ch/jobs/project-manager</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr"/>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>Michael Page Switzerland</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>Creative Project Manager (9-Month Interim Assignment) Asap- Asana &amp; Figma- English</t>
         </is>
       </c>
-      <c r="E26" s="2" t="n">
+      <c r="E26" t="n">
         <v>4</v>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>https://www.michaelpage.ch/job-detail/creative-project-manager-9-month-interim-assignment/ref/jn-102026-7120382</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr"/>
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
+          <t>Agile Robots</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>(Senior) Technical Program Manager (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Bavaria, Germany</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/agilerobotsse/jobs/4996481101</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Peter Park</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Junior Project Manager - Retrofit (m/w/d)</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>München</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>https://peter-park.jobs.personio.de/job/2793111</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="inlineStr">
+        <is>
           <t>Hoffmann Group</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
         <is>
           <t>eBusiness Projektmanager (m/w/d) - München</t>
         </is>
       </c>
-      <c r="E27" s="2" t="n">
+      <c r="E29" t="n">
         <v>3</v>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>...ness Projektmanager (m/w/d) - München bei Hoffmann SE 德语 český Deut...</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>https://career.hoffmann-group.com/eBusiness-Projektmanager-mwd-Muenchen-de-j2193.html</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr"/>
-      <c r="B28" s="2" t="inlineStr">
+    <row r="30">
+      <c r="B30" t="inlineStr">
         <is>
           <t>Hoffmann Group</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>eBusiness Projektmanager (m/w/d) - Nürnberg</t>
         </is>
       </c>
-      <c r="E28" s="2" t="n">
+      <c r="E30" t="n">
         <v>3</v>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>...uschuss Kostenlosen Werkzeugbezug/Mitarbeiterrabatt auf den ges...</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>https://career.hoffmann-group.com/eBusiness-Projektmanager-mwd-Nuernberg-de-j2152.html</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr"/>
-      <c r="B29" s="2" t="inlineStr">
+    <row r="31">
+      <c r="B31" t="inlineStr">
         <is>
           <t>Michael Page Switzerland</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>IT Project Manager</t>
         </is>
       </c>
-      <c r="E29" s="2" t="n">
+      <c r="E31" t="n">
         <v>3</v>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>https://www.michaelpage.ch/job-detail/it-project-manager/ref/jn-102026-7121274</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr"/>
-      <c r="B30" s="2" t="inlineStr">
+    <row r="32">
+      <c r="B32" t="inlineStr">
         <is>
           <t>Michael Page Switzerland</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>IT Project Manager - FR / GE</t>
         </is>
       </c>
-      <c r="E30" s="2" t="n">
+      <c r="E32" t="n">
         <v>3</v>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>https://www.michaelpage.ch/fr/job-detail/it-project-manager-fr-ge/ref/jn-062026-7044696?lang=en</t>
         </is>
@@ -1472,31 +1519,30 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr"/>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Siemens Energy</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Bern</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Experienced Commercial Project Manager (m/f/d)</t>
         </is>
       </c>
-      <c r="E2" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="E2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F2" t="inlineStr">
         <is>
           <t>...on Ihrem Tag In dieser Rolle übernehmen Sie die kommerzielle Füh...</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>https://jobs.siemens-energy.com/en_US/jobs/FolderDetail/Experienced-Commercial-Project-Manager-m-f-d/301245</t>
         </is>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -31,7 +31,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -42,6 +42,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="001F2937"/>
         <bgColor rgb="001F2937"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D1FAE5"/>
+        <bgColor rgb="00D1FAE5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDE68A"/>
+        <bgColor rgb="00FDE68A"/>
       </patternFill>
     </fill>
   </fills>
@@ -57,9 +69,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -474,6 +488,913 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr"/>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Hensoldt</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Projektleiter NNbS Mittelbereichsradar (w/m/d)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>...rung im Projektmanagement, vorzugsweise mit PMI-Zertifizierung,...</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.hensoldt.net/job/Ulm-Projektleiter-NNbS-Mittelbereichsradar-%28wmd%29-89077/1367853655/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr"/>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Randstad Germany</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Projektmanager</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>...am Main Hamburg Köln Leipzig München Stuttgart Top Suchbegriffe La...</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.randstad.de/jobs/b-wirtschaft-und-administration/t-administration-und-verwaltung/j-projektmanager/</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr"/>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Randstad Germany</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Projektmanager (m/w/d)</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>...am Main Hamburg Köln Leipzig München Stuttgart Top Suchbegriffe La...</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.randstad.de/jobs/projektmanager-mwd_bremen_c01338232/</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr"/>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Randstad Germany</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Projektmanager (m/w/d)</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>...am Main Hamburg Köln Leipzig München Stuttgart Top Suchbegriffe La...</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.randstad.de/jobs/projektmanager-mwd_barchfeld-immelborn_c01332512/</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr"/>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Randstad Germany</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Projektmanager (m/w/d)</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>...am Main Hamburg Köln Leipzig München Stuttgart Top Suchbegriffe La...</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.randstad.de/jobs/projektmanager-mwd_berlin_c01343736/</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr"/>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Randstad Germany</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Projektmanager (m/w/d)</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>...am Main Hamburg Köln Leipzig München Stuttgart Top Suchbegriffe La...</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.randstad.de/jobs/projektmanager-mwd_augsburg_c01343637/</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr"/>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Randstad Germany</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Projektmanager (m/w/d)</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Projektmanager (m/w/d) in München | Randstad randstad Jobsuche...</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.randstad.de/jobs/projektmanager-mwd_muenchen_c01346300/</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr"/>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Randstad Germany</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Projektmanager Bau (m/w/d)</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>...am Main Hamburg Köln Leipzig München Stuttgart Top Suchbegriffe La...</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.randstad.de/jobs/projektmanager-bau-mwd_erkrath_c01327518/</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr"/>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Randstad Germany</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Projektmanager (m/w/d)</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>...am Main Hamburg Köln Leipzig München Stuttgart Top Suchbegriffe La...</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.randstad.de/jobs/projektmanager-mwd_quedlinburg_c01322820/</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Randstad Germany</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Projektmanager (m/w/d)</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>...am Main Hamburg Köln Leipzig München Stuttgart Top Suchbegriffe La...</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.randstad.de/jobs/projektmanager-mwd_wilsdruff_c01340996/</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Randstad Germany</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Projektmanager (m/w/d), Airbus</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>...am Main Hamburg Köln Leipzig München Stuttgart Top Suchbegriffe La...</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.randstad.de/jobs/projektmanager-mwd_bremen_c01333741/</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Randstad Germany</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Projektmanager (m/w/d)</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>...am Main Hamburg Köln Leipzig München Stuttgart Top Suchbegriffe La...</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.randstad.de/jobs/projektmanager-mwd_bergheim_c01339132/</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Randstad Germany</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Projektmanager (m/w/d)</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>...am Main Hamburg Köln Leipzig München Stuttgart Top Suchbegriffe La...</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.randstad.de/jobs/projektmanager-mwd_bergheim_c01339130/</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Randstad Germany</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Projektmanager (m/w/d)</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>...am Main Hamburg Köln Leipzig München Stuttgart Top Suchbegriffe La...</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.randstad.de/jobs/projektmanager-mwd_bremen_c01326141/</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Randstad Germany</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Projektleiter ( 6 )</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>...am Main Hamburg Köln Leipzig München Stuttgart Top Suchbegriffe La...</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.randstad.de/jobs/b-wirtschaft-und-administration/t-administration-und-verwaltung/j-projektleiter/</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Germany</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Projektleiter (m/w/d) Defence</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.de/job-detail/projektleiter-mwd-defence/ref/jn-092026-7105457</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Agile Robots</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Senior Project Manager (all genders)</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Bavaria, Germany</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/agilerobotsse/jobs/4990647101</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Switzerland</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>IT Project Manager</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.ch/job-detail/it-project-manager/ref/jn-092026-7100459</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Hensoldt</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Projektleiter NNbS Project Office (w/m/d)</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>...eichung in Abstimmung mit dem zugeordneten Programm/Projekt Sic...</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.hensoldt.net/job/Ulm-Projektleiter-NNbS-Project-Office-%28wmd%29-89077/1367851655/</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Hensoldt</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Technischer Projektleiter (w/m/d)</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>...equisition ID: 5229 Location: Fürstenfeldbruck, DE, 82256 Company: ESG Elekt...</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Technischer-Projektleiter-%28wmd%29-82256/1355284255/</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Agile Robots</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>(Senior) Technical Program Manager (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Bavaria, Germany</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/agilerobotsse/jobs/4996481101</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Switzerland</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.ch/jobs/project-manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Switzerland</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Creative Project Manager (9-Month Interim Assignment) Asap- Asana &amp; Figma- English</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.ch/job-detail/creative-project-manager-9-month-interim-assignment/ref/jn-102026-7120382</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Diehl Defence</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Diehl Defence Projektleiter Fertigungsaufbau (m/w/d) 09.10.2026 Manufacturing/Production Lübben</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>...den bei gleicher Eignung bevorzugt behandelt. Sollten Sie das w...</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>https://new.diehl.com/career/en/jobs-application/job-offers/vacancies/projektleiter-fertigungsaufbau-m-w-d2</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Hoffmann Group</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>eBusiness Projektmanager (m/w/d) - München</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>...ness Projektmanager (m/w/d) - München bei Hoffmann SE 德语 český Deut...</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>https://career.hoffmann-group.com/eBusiness-Projektmanager-mwd-Muenchen-de-j2193.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Hoffmann Group</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>eBusiness Projektmanager (m/w/d) - Nürnberg</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>...uschuss Kostenlosen Werkzeugbezug/Mitarbeiterrabatt auf den ges...</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>https://career.hoffmann-group.com/eBusiness-Projektmanager-mwd-Nuernberg-de-j2152.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>VoiceLine</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Senior Project Manager Customer Implementations (m/w/d) München Vollzeit Festanstellung</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>...tomer Implementations (m/w/d) München Vollzeit Festanstellung Auf d...</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>https://voiceline.jobs.personio.de/job/2382820</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Switzerland</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>IT Project Manager</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.ch/job-detail/it-project-manager/ref/jn-102026-7121274</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Switzerland</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>IT Project Manager - FR / GE</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.ch/fr/job-detail/it-project-manager-fr-ge/ref/jn-062026-7044696?lang=en</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -485,7 +1406,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -534,6 +1455,37 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr"/>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Siemens Energy</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Bern</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Experienced Commercial Project Manager (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>...on Ihrem Tag In dieser Rolle übernehmen Sie die kommerzielle Füh...</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>https://jobs.siemens-energy.com/en_US/jobs/FolderDetail/Experienced-Commercial-Project-Manager-m-f-d/301245</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -30,7 +30,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -41,6 +41,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="001F2937"/>
         <bgColor rgb="001F2937"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D1FAE5"/>
+        <bgColor rgb="00D1FAE5"/>
       </patternFill>
     </fill>
   </fills>
@@ -56,9 +62,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -424,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -473,6 +480,200 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Agile Robots</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Senior Project Manager (all genders)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Bavaria, Germany</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/agilerobotsse/jobs/4990647101</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr"/>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Hensoldt</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Technischer Projektleiter (w/m/d)</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>...equisition ID: 5229 Location: Fürstenfeldbruck, DE, 82256 Company: ESG Elekt...</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Technischer-Projektleiter-%28wmd%29-82256/1355284255/</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr"/>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>zooplus</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Programme Manager - Supply Chain Optimization (All Genders) Munich, Germany Vendor Management &amp; Supply Full-time</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>...Optimization (All Genders) - Munich, Bavaria, Germany Home Life a...</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>https://careers.zooplus.com/jobs/programme-manager-supply-chain-optimization-all-genders-munich-bavaria-germany-5dfc2de1-feba-4717-b007-7c814d41b155</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Agile Robots</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>(Senior) Technical Program Manager (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Bavaria, Germany</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/agilerobotsse/jobs/4996481101</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr"/>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Hoffmann Group</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>eBusiness Projektmanager (m/w/d) - München</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>...ness Projektmanager (m/w/d) - München bei Hoffmann SE 德语 český Deut...</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>https://career.hoffmann-group.com/eBusiness-Projektmanager-mwd-Muenchen-de-j2193.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr"/>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>VoiceLine</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Senior Project Manager Customer Implementations (m/w/d) München Vollzeit Festanstellung</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>...tomer Implementations (m/w/d) München Vollzeit Festanstellung Auf d...</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>https://voiceline.jobs.personio.de/job/2382820</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -483,12 +483,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Agile Robots</t>
+          <t>Isar Aerospace</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -498,177 +498,208 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Senior Project Manager (all genders)</t>
+          <t>MES Delivery Manager / Project Manager (m/f/d)</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Munich, Bavaria, Germany</t>
+          <t>Parsdorf, Bavaria, Germany</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/agilerobotsse/jobs/4990647101</t>
+          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4989582101</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr"/>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Hensoldt</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Agile Robots</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Technischer Projektleiter (w/m/d)</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>...equisition ID: 5229 Location: Fürstenfeldbruck, DE, 82256 Company: ESG Elekt...</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Technischer-Projektleiter-%28wmd%29-82256/1355284255/</t>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Senior Project Manager (all genders)</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Munich, Bavaria, Germany</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/agilerobotsse/jobs/4990647101</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr"/>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>zooplus</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Hensoldt</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Programme Manager - Supply Chain Optimization (All Genders) Munich, Germany Vendor Management &amp; Supply Full-time</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="n">
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Technischer Projektleiter (w/m/d)</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
         <v>4</v>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>...Optimization (All Genders) - Munich, Bavaria, Germany Home Life a...</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>https://careers.zooplus.com/jobs/programme-manager-supply-chain-optimization-all-genders-munich-bavaria-germany-5dfc2de1-feba-4717-b007-7c814d41b155</t>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>...equisition ID: 5229 Location: Fürstenfeldbruck, DE, 82256 Company: ESG Elekt...</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Technischer-Projektleiter-%28wmd%29-82256/1355284255/</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Agile Robots</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>zooplus</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>(Senior) Technical Program Manager (m/f/d)</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="n">
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Programme Manager - Supply Chain Optimization (All Genders) Munich, Germany Vendor Management &amp; Supply Full-time</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
         <v>4</v>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Munich, Bavaria, Germany</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>https://job-boards.eu.greenhouse.io/agilerobotsse/jobs/4996481101</t>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>...Optimization (All Genders) - Munich, Bavaria, Germany Home Life a...</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://careers.zooplus.com/jobs/programme-manager-supply-chain-optimization-all-genders-munich-bavaria-germany-5dfc2de1-feba-4717-b007-7c814d41b155</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr"/>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Hoffmann Group</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Agile Robots</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>eBusiness Projektmanager (m/w/d) - München</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>...ness Projektmanager (m/w/d) - München bei Hoffmann SE 德语 český Deut...</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>https://career.hoffmann-group.com/eBusiness-Projektmanager-mwd-Muenchen-de-j2193.html</t>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>(Senior) Technical Program Manager (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Munich, Bavaria, Germany</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/agilerobotsse/jobs/4996481101</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr"/>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Hoffmann Group</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>eBusiness Projektmanager (m/w/d) - München</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>...ness Projektmanager (m/w/d) - München bei Hoffmann SE 德语 český Deut...</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://career.hoffmann-group.com/eBusiness-Projektmanager-mwd-Muenchen-de-j2193.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
         <is>
           <t>VoiceLine</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Senior Project Manager Customer Implementations (m/w/d) München Vollzeit Festanstellung</t>
         </is>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="E8" t="n">
         <v>3</v>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>...tomer Implementations (m/w/d) München Vollzeit Festanstellung Auf d...</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>https://voiceline.jobs.personio.de/job/2382820</t>
         </is>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -481,139 +481,137 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Isar Aerospace</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
         <is>
           <t>MES Delivery Manager / Project Manager (m/f/d)</t>
         </is>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" t="n">
         <v>8</v>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Parsdorf, Bavaria, Germany</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4989582101</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Agile Robots</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Senior Project Manager (all genders)</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>5</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Munich, Bavaria, Germany</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>https://job-boards.eu.greenhouse.io/agilerobotsse/jobs/4990647101</t>
+      <c r="A3" s="2" t="inlineStr"/>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>ATOSS Software</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Project Manager f/m/d</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>...s, and an in-house barista in Munich. Health &amp; Wellbeing: Includin...</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.atoss.com/en/company/career/jobs/4952966101-project-manager-f-m-d?gh_jid=4952966101</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Hensoldt</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Technischer Projektleiter (w/m/d)</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>4</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>...equisition ID: 5229 Location: Fürstenfeldbruck, DE, 82256 Company: ESG Elekt...</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Technischer-Projektleiter-%28wmd%29-82256/1355284255/</t>
+      <c r="A4" s="2" t="inlineStr"/>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>SES</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Customer Program Manager</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>...Type: Permanent Location(s): Munich (Unterföhring), DE Customer P...</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>https://careers.ses.com/job/Munich-%28Unterf%C3%B6hring%29-Customer-Program-Manager/1441583333/</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>zooplus</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Programme Manager - Supply Chain Optimization (All Genders) Munich, Germany Vendor Management &amp; Supply Full-time</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>4</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>...Optimization (All Genders) - Munich, Bavaria, Germany Home Life a...</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>https://careers.zooplus.com/jobs/programme-manager-supply-chain-optimization-all-genders-munich-bavaria-germany-5dfc2de1-feba-4717-b007-7c814d41b155</t>
+      <c r="A5" s="2" t="inlineStr"/>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>SES</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Project Manager, IVV, Satellite Systems, IRIS2 Programme Office</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>...Type: Permanent Location(s): Munich (Unterföhring), DE Betzdorf,...</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>https://careers.ses.com/job/Munich-%28Unterf%C3%B6hring%29-Project-Manager%2C-IVV%2C-Satellite-Systems%2C-IRIS2-Programme-Office/1396651333/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -628,11 +626,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>(Senior) Technical Program Manager (m/f/d)</t>
+          <t>Senior Project Manager (all genders)</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -641,14 +639,14 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/agilerobotsse/jobs/4996481101</t>
+          <t>https://job-boards.eu.greenhouse.io/agilerobotsse/jobs/4990647101</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="B7" t="inlineStr">
         <is>
-          <t>Hoffmann Group</t>
+          <t>Hensoldt</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -658,48 +656,209 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>eBusiness Projektmanager (m/w/d) - München</t>
+          <t>Technischer Projektleiter (w/m/d)</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>...ness Projektmanager (m/w/d) - München bei Hoffmann SE 德语 český Deut...</t>
+          <t>...equisition ID: 5229 Location: Fürstenfeldbruck, DE, 82256 Company: ESG Elekt...</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://career.hoffmann-group.com/eBusiness-Projektmanager-mwd-Muenchen-de-j2193.html</t>
+          <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Technischer-Projektleiter-%28wmd%29-82256/1355284255/</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="B8" t="inlineStr">
         <is>
+          <t>zooplus</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Programme Manager - Supply Chain Optimization (All Genders) Munich, Germany Vendor Management &amp; Supply Full-time</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>...Optimization (All Genders) - Munich, Bavaria, Germany Home Life a...</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://careers.zooplus.com/jobs/programme-manager-supply-chain-optimization-all-genders-munich-bavaria-germany-5dfc2de1-feba-4717-b007-7c814d41b155</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Agile Robots</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>(Senior) Technical Program Manager (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Munich, Bavaria, Germany</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/agilerobotsse/jobs/4996481101</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>RobCo</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>(Senior) Technical Program Manager (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/robco/a3b35c55-7d10-48b2-a1eb-a45a0e5d436a</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>SES</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Project Manager, Reporting &amp; Governance Manager, IRIS2 Programme Office</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>...Type: Permanent Location(s): Munich (Unterföhring), DE Betzdorf,...</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>https://careers.ses.com/job/Munich-%28Unterf%C3%B6hring%29-Project-Manager%2C-Reporting-&amp;-Governance-Manager%2C-IRIS2-Programme-Office/1403515633/</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Hoffmann Group</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>eBusiness Projektmanager (m/w/d) - München</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>3</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>...ness Projektmanager (m/w/d) - München bei Hoffmann SE 德语 český Deut...</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://career.hoffmann-group.com/eBusiness-Projektmanager-mwd-Muenchen-de-j2193.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
           <t>VoiceLine</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>Senior Project Manager Customer Implementations (m/w/d) München Vollzeit Festanstellung</t>
         </is>
       </c>
-      <c r="E8" t="n">
+      <c r="E13" t="n">
         <v>3</v>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>...tomer Implementations (m/w/d) München Vollzeit Festanstellung Auf d...</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>https://voiceline.jobs.personio.de/job/2382820</t>
         </is>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -516,93 +516,90 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr"/>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>ATOSS Software</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
         <is>
           <t>Project Manager f/m/d</t>
         </is>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E3" t="n">
         <v>6</v>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>...s, and an in-house barista in Munich. Health &amp; Wellbeing: Includin...</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>https://www.atoss.com/en/company/career/jobs/4952966101-project-manager-f-m-d?gh_jid=4952966101</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr"/>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>SES</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
         <is>
           <t>Customer Program Manager</t>
         </is>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="E4" t="n">
         <v>6</v>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>...Type: Permanent Location(s): Munich (Unterföhring), DE Customer P...</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>https://careers.ses.com/job/Munich-%28Unterf%C3%B6hring%29-Customer-Program-Manager/1441583333/</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr"/>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>SES</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
         <is>
           <t>Project Manager, IVV, Satellite Systems, IRIS2 Programme Office</t>
         </is>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="E5" t="n">
         <v>6</v>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>...Type: Permanent Location(s): Munich (Unterföhring), DE Betzdorf,...</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>https://careers.ses.com/job/Munich-%28Unterf%C3%B6hring%29-Project-Manager%2C-IVV%2C-Satellite-Systems%2C-IRIS2-Programme-Office/1396651333/</t>
         </is>
@@ -739,66 +736,65 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>RobCo</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
         <is>
           <t>(Senior) Technical Program Manager (m/f/d)</t>
         </is>
       </c>
-      <c r="E10" s="2" t="n">
+      <c r="E10" t="n">
         <v>4</v>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/robco/a3b35c55-7d10-48b2-a1eb-a45a0e5d436a</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr"/>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>SES</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
         <is>
           <t>Project Manager, Reporting &amp; Governance Manager, IRIS2 Programme Office</t>
         </is>
       </c>
-      <c r="E11" s="2" t="n">
+      <c r="E11" t="n">
         <v>4</v>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>...Type: Permanent Location(s): Munich (Unterföhring), DE Betzdorf,...</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>https://careers.ses.com/job/Munich-%28Unterf%C3%B6hring%29-Project-Manager%2C-Reporting-&amp;-Governance-Manager%2C-IRIS2-Programme-Office/1403515633/</t>
         </is>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -30,7 +30,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -41,12 +41,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="001F2937"/>
         <bgColor rgb="001F2937"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D1FAE5"/>
-        <bgColor rgb="00D1FAE5"/>
       </patternFill>
     </fill>
   </fills>
@@ -62,10 +56,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -431,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -480,386 +473,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Isar Aerospace</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>MES Delivery Manager / Project Manager (m/f/d)</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>8</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Parsdorf, Bavaria, Germany</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4989582101</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>ATOSS Software</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Project Manager f/m/d</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>6</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>...s, and an in-house barista in Munich. Health &amp; Wellbeing: Includin...</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>https://www.atoss.com/en/company/career/jobs/4952966101-project-manager-f-m-d?gh_jid=4952966101</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>SES</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Customer Program Manager</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>6</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>...Type: Permanent Location(s): Munich (Unterföhring), DE Customer P...</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>https://careers.ses.com/job/Munich-%28Unterf%C3%B6hring%29-Customer-Program-Manager/1441583333/</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>SES</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Project Manager, IVV, Satellite Systems, IRIS2 Programme Office</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>6</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>...Type: Permanent Location(s): Munich (Unterföhring), DE Betzdorf,...</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>https://careers.ses.com/job/Munich-%28Unterf%C3%B6hring%29-Project-Manager%2C-IVV%2C-Satellite-Systems%2C-IRIS2-Programme-Office/1396651333/</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Agile Robots</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Senior Project Manager (all genders)</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>5</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Munich, Bavaria, Germany</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://job-boards.eu.greenhouse.io/agilerobotsse/jobs/4990647101</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Hensoldt</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Technischer Projektleiter (w/m/d)</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>4</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>...equisition ID: 5229 Location: Fürstenfeldbruck, DE, 82256 Company: ESG Elekt...</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Technischer-Projektleiter-%28wmd%29-82256/1355284255/</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>zooplus</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Programme Manager - Supply Chain Optimization (All Genders) Munich, Germany Vendor Management &amp; Supply Full-time</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>4</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>...Optimization (All Genders) - Munich, Bavaria, Germany Home Life a...</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://careers.zooplus.com/jobs/programme-manager-supply-chain-optimization-all-genders-munich-bavaria-germany-5dfc2de1-feba-4717-b007-7c814d41b155</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Agile Robots</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>(Senior) Technical Program Manager (m/f/d)</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>4</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Munich, Bavaria, Germany</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://job-boards.eu.greenhouse.io/agilerobotsse/jobs/4996481101</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>RobCo</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>(Senior) Technical Program Manager (m/f/d)</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>4</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://jobs.ashbyhq.com/robco/a3b35c55-7d10-48b2-a1eb-a45a0e5d436a</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>SES</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Project Manager, Reporting &amp; Governance Manager, IRIS2 Programme Office</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>4</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>...Type: Permanent Location(s): Munich (Unterföhring), DE Betzdorf,...</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://careers.ses.com/job/Munich-%28Unterf%C3%B6hring%29-Project-Manager%2C-Reporting-&amp;-Governance-Manager%2C-IRIS2-Programme-Office/1403515633/</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Hoffmann Group</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>eBusiness Projektmanager (m/w/d) - München</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>3</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>...ness Projektmanager (m/w/d) - München bei Hoffmann SE 德语 český Deut...</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://career.hoffmann-group.com/eBusiness-Projektmanager-mwd-Muenchen-de-j2193.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>VoiceLine</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Senior Project Manager Customer Implementations (m/w/d) München Vollzeit Festanstellung</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>3</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>...tomer Implementations (m/w/d) München Vollzeit Festanstellung Auf d...</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://voiceline.jobs.personio.de/job/2382820</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -30,7 +30,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -41,6 +41,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="001F2937"/>
         <bgColor rgb="001F2937"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D1FAE5"/>
+        <bgColor rgb="00D1FAE5"/>
       </patternFill>
     </fill>
   </fills>
@@ -56,9 +62,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -424,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -473,6 +480,305 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Isar Aerospace</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>MES Delivery Manager / Project Manager (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Parsdorf, Bavaria, Germany</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4989582101</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr"/>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>ATOSS Software</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Project Manager f/m/d</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>...s, and an in-house barista in Munich. Health &amp; Wellbeing: Includin...</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.atoss.com/en/company/career/jobs/4952966101-project-manager-f-m-d?gh_jid=4952966101</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr"/>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>SES</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Customer Program Manager</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>...Type: Permanent Location(s): Munich (Unterföhring), DE Customer P...</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>https://careers.ses.com/job/Munich-%28Unterf%C3%B6hring%29-Customer-Program-Manager/1441583333/</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr"/>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>SES</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Project Manager, IVV, Satellite Systems, IRIS2 Programme Office</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>...Type: Permanent Location(s): Munich (Unterföhring), DE Betzdorf,...</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>https://careers.ses.com/job/Munich-%28Unterf%C3%B6hring%29-Project-Manager%2C-IVV%2C-Satellite-Systems%2C-IRIS2-Programme-Office/1396651333/</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Agile Robots</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Senior Project Manager (all genders)</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Bavaria, Germany</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/agilerobotsse/jobs/4990647101</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>zooplus</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Programme Manager - Supply Chain Optimization (All Genders) Munich, Germany Vendor Management &amp; Supply Full-time</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Bavaria, de</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>https://careers.zooplus.com/jobs/programme-manager-supply-chain-optimization-all-genders-munich-bavaria-germany-5dfc2de1-feba-4717-b007-7c814d41b155</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>RobCo</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>(Senior) Technical Program Manager (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/robco/a3b35c55-7d10-48b2-a1eb-a45a0e5d436a</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Agile Robots</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>(Senior) Technical Program Manager (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Bavaria, Germany</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/agilerobotsse/jobs/4996481101</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr"/>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>SES</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Project Manager, Reporting &amp; Governance Manager, IRIS2 Programme Office</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>...Type: Permanent Location(s): Munich (Unterföhring), DE Betzdorf,...</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>https://careers.ses.com/job/Munich-%28Unterf%C3%B6hring%29-Project-Manager%2C-Reporting-&amp;-Governance-Manager%2C-IRIS2-Programme-Office/1403515633/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -481,299 +481,295 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Isar Aerospace</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
         <is>
           <t>MES Delivery Manager / Project Manager (m/f/d)</t>
         </is>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" t="n">
         <v>8</v>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Parsdorf, Bavaria, Germany</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4989582101</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr"/>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>ATOSS Software</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
         <is>
           <t>Project Manager f/m/d</t>
         </is>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E3" t="n">
         <v>6</v>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>...s, and an in-house barista in Munich. Health &amp; Wellbeing: Includin...</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>https://www.atoss.com/en/company/career/jobs/4952966101-project-manager-f-m-d?gh_jid=4952966101</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr"/>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>SES</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
         <is>
           <t>Customer Program Manager</t>
         </is>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="E4" t="n">
         <v>6</v>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>...Type: Permanent Location(s): Munich (Unterföhring), DE Customer P...</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>https://careers.ses.com/job/Munich-%28Unterf%C3%B6hring%29-Customer-Program-Manager/1441583333/</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr"/>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>SES</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
         <is>
           <t>Project Manager, IVV, Satellite Systems, IRIS2 Programme Office</t>
         </is>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="E5" t="n">
         <v>6</v>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>...Type: Permanent Location(s): Munich (Unterföhring), DE Betzdorf,...</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>https://careers.ses.com/job/Munich-%28Unterf%C3%B6hring%29-Project-Manager%2C-IVV%2C-Satellite-Systems%2C-IRIS2-Programme-Office/1396651333/</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Agile Robots</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
         <is>
           <t>Senior Project Manager (all genders)</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="E6" t="n">
         <v>5</v>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>Munich, Bavaria, Germany</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>https://job-boards.eu.greenhouse.io/agilerobotsse/jobs/4990647101</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>zooplus</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
         <is>
           <t>Programme Manager - Supply Chain Optimization (All Genders) Munich, Germany Vendor Management &amp; Supply Full-time</t>
         </is>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="E7" t="n">
         <v>4</v>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>Munich, Bavaria, de</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>https://careers.zooplus.com/jobs/programme-manager-supply-chain-optimization-all-genders-munich-bavaria-germany-5dfc2de1-feba-4717-b007-7c814d41b155</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>RobCo</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
         <is>
           <t>(Senior) Technical Program Manager (m/f/d)</t>
         </is>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="E8" t="n">
         <v>4</v>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/robco/a3b35c55-7d10-48b2-a1eb-a45a0e5d436a</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Agile Robots</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
         <is>
           <t>(Senior) Technical Program Manager (m/f/d)</t>
         </is>
       </c>
-      <c r="E9" s="2" t="n">
+      <c r="E9" t="n">
         <v>4</v>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>Munich, Bavaria, Germany</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>https://job-boards.eu.greenhouse.io/agilerobotsse/jobs/4996481101</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr"/>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>SES</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
         <is>
           <t>Project Manager, Reporting &amp; Governance Manager, IRIS2 Programme Office</t>
         </is>
       </c>
-      <c r="E10" s="2" t="n">
+      <c r="E10" t="n">
         <v>4</v>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>...Type: Permanent Location(s): Munich (Unterföhring), DE Betzdorf,...</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>https://careers.ses.com/job/Munich-%28Unterf%C3%B6hring%29-Project-Manager%2C-Reporting-&amp;-Governance-Manager%2C-IRIS2-Programme-Office/1403515633/</t>
         </is>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -481,14 +481,9 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Isar Aerospace</t>
+          <t>SES</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -498,27 +493,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>MES Delivery Manager / Project Manager (m/f/d)</t>
+          <t>Customer Program Manager</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Parsdorf, Bavaria, Germany</t>
+          <t>...Type: Permanent Location(s): Munich (Unterföhring), DE Customer P...</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4989582101</t>
+          <t>https://careers.ses.com/job/Munich-%28Unterf%C3%B6hring%29-Customer-Program-Manager/1441583333/</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="B3" t="inlineStr">
         <is>
-          <t>ATOSS Software</t>
+          <t>SES</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -528,7 +523,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Project Manager f/m/d</t>
+          <t>Project Manager, IVV, Satellite Systems, IRIS2 Programme Office</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -536,12 +531,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>...s, and an in-house barista in Munich. Health &amp; Wellbeing: Includin...</t>
+          <t>...Type: Permanent Location(s): Munich (Unterföhring), DE Betzdorf,...</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.atoss.com/en/company/career/jobs/4952966101-project-manager-f-m-d?gh_jid=4952966101</t>
+          <t>https://careers.ses.com/job/Munich-%28Unterf%C3%B6hring%29-Project-Manager%2C-IVV%2C-Satellite-Systems%2C-IRIS2-Programme-Office/1396651333/</t>
         </is>
       </c>
     </row>
@@ -558,27 +553,27 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Customer Program Manager</t>
+          <t>Project Manager, Reporting &amp; Governance Manager, IRIS2 Programme Office</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>...Type: Permanent Location(s): Munich (Unterföhring), DE Customer P...</t>
+          <t>...Type: Permanent Location(s): Munich (Unterföhring), DE Betzdorf,...</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://careers.ses.com/job/Munich-%28Unterf%C3%B6hring%29-Customer-Program-Manager/1441583333/</t>
+          <t>https://careers.ses.com/job/Munich-%28Unterf%C3%B6hring%29-Project-Manager%2C-Reporting-&amp;-Governance-Manager%2C-IRIS2-Programme-Office/1403515633/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="B5" t="inlineStr">
         <is>
-          <t>SES</t>
+          <t>ATOSS Software</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -588,7 +583,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Project Manager, IVV, Satellite Systems, IRIS2 Programme Office</t>
+          <t>Project Manager f/m/d</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -596,12 +591,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>...Type: Permanent Location(s): Munich (Unterföhring), DE Betzdorf,...</t>
+          <t>...s, and an in-house barista in Munich. Health &amp; Wellbeing: Includin...</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://careers.ses.com/job/Munich-%28Unterf%C3%B6hring%29-Project-Manager%2C-IVV%2C-Satellite-Systems%2C-IRIS2-Programme-Office/1396651333/</t>
+          <t>https://www.atoss.com/en/company/career/jobs/4952966101-project-manager-f-m-d?gh_jid=4952966101</t>
         </is>
       </c>
     </row>
@@ -746,9 +741,14 @@
       </c>
     </row>
     <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SES</t>
+          <t>Isar Aerospace</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -758,20 +758,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Project Manager, Reporting &amp; Governance Manager, IRIS2 Programme Office</t>
+          <t>MES Delivery Manager / Project Manager (m/f/d)</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>...Type: Permanent Location(s): Munich (Unterföhring), DE Betzdorf,...</t>
+          <t>Parsdorf, Bavaria, Germany</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://careers.ses.com/job/Munich-%28Unterf%C3%B6hring%29-Project-Manager%2C-Reporting-&amp;-Governance-Manager%2C-IRIS2-Programme-Office/1403515633/</t>
+          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4989582101</t>
         </is>
       </c>
     </row>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -741,35 +741,105 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Proxima Fusion</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Site Development Program Manager</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/proxima-fusion/db5bc40c-aa3e-4735-94e7-096a556dd55d</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>VoiceLine</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Senior Project Manager Customer Implementations (m/w/d) München Vollzeit Festanstellung</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>München, Bayern, DE</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>https://voiceline.jobs.personio.de/job/2382820</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Isar Aerospace</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
         <is>
           <t>MES Delivery Manager / Project Manager (m/f/d)</t>
         </is>
       </c>
-      <c r="E10" t="n">
+      <c r="E12" t="n">
         <v>8</v>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>Parsdorf, Bavaria, Germany</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4989582101</t>
         </is>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -601,37 +601,37 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Agile Robots</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Senior Project Manager (all genders)</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>5</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Munich, Bavaria, Germany</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://job-boards.eu.greenhouse.io/agilerobotsse/jobs/4990647101</t>
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>ARX Robotics</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Project Manager - Infrastructure &amp; Expansion</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/arxroboticsgmbh/jobs/5005798101</t>
         </is>
       </c>
     </row>
@@ -643,7 +643,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>zooplus</t>
+          <t>Agile Robots</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -653,32 +653,32 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Programme Manager - Supply Chain Optimization (All Genders) Munich, Germany Vendor Management &amp; Supply Full-time</t>
+          <t>Senior Project Manager (all genders)</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Munich, Bavaria, de</t>
+          <t>Munich, Bavaria, Germany</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://careers.zooplus.com/jobs/programme-manager-supply-chain-optimization-all-genders-munich-bavaria-germany-5dfc2de1-feba-4717-b007-7c814d41b155</t>
+          <t>https://job-boards.eu.greenhouse.io/agilerobotsse/jobs/4990647101</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>RobCo</t>
+          <t>zooplus</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>(Senior) Technical Program Manager (m/f/d)</t>
+          <t>Programme Manager - Supply Chain Optimization (All Genders) Munich, Germany Vendor Management &amp; Supply Full-time</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -696,24 +696,24 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>Munich, Bavaria, de</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/robco/a3b35c55-7d10-48b2-a1eb-a45a0e5d436a</t>
+          <t>https://careers.zooplus.com/jobs/programme-manager-supply-chain-optimization-all-genders-munich-bavaria-germany-5dfc2de1-feba-4717-b007-7c814d41b155</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Agile Robots</t>
+          <t>RobCo</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -731,115 +731,185 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/robco/a3b35c55-7d10-48b2-a1eb-a45a0e5d436a</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Agile Robots</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>(Senior) Technical Program Manager (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>Munich, Bavaria, Germany</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>https://job-boards.eu.greenhouse.io/agilerobotsse/jobs/4996481101</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Proxima Fusion</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
         <is>
           <t>Site Development Program Manager</t>
         </is>
       </c>
-      <c r="E10" s="2" t="n">
+      <c r="E11" t="n">
         <v>3</v>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/proxima-fusion/db5bc40c-aa3e-4735-94e7-096a556dd55d</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>VoiceLine</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>Senior Project Manager Customer Implementations (m/w/d) München Vollzeit Festanstellung</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>München, Bayern, DE</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>https://voiceline.jobs.personio.de/job/2382820</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>VoiceLine</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Senior Project Manager Customer Implementations (m/w/d) München Vollzeit Festanstellung</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>3</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>München, Bayern, DE</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://voiceline.jobs.personio.de/job/2382820</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Airbus</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Projectmanager Industrialisierung (d/m/w)</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Augsburg Area</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Augsburg-Area/Projectmanager-Industrialisierung--d-m-w-_JR10430741-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Isar Aerospace</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t>MES Delivery Manager / Project Manager (m/f/d)</t>
         </is>
       </c>
-      <c r="E12" t="n">
+      <c r="E14" t="n">
         <v>8</v>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>Parsdorf, Bavaria, Germany</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4989582101</t>
         </is>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -601,35 +601,35 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>ARX Robotics</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
         <is>
           <t>Project Manager - Infrastructure &amp; Expansion</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="E6" t="n">
         <v>6</v>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
         <is>
           <t>https://job-boards.eu.greenhouse.io/arxroboticsgmbh/jobs/5005798101</t>
         </is>
@@ -846,35 +846,35 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Airbus</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>Projectmanager Industrialisierung (d/m/w)</t>
         </is>
       </c>
-      <c r="E13" s="2" t="n">
+      <c r="E13" t="n">
         <v>10</v>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>Augsburg Area</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Augsburg-Area/Projectmanager-Industrialisierung--d-m-w-_JR10430741-1</t>
         </is>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -571,54 +571,54 @@
       </c>
     </row>
     <row r="5">
-      <c r="B5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>(Senior) Programme Manager - Military Exercises</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/5004102101?gh_jid=5004102101</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
         <is>
           <t>ATOSS Software</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
         <is>
           <t>Project Manager f/m/d</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>6</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>...s, and an in-house barista in Munich. Health &amp; Wellbeing: Includin...</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>https://www.atoss.com/en/company/career/jobs/4952966101-project-manager-f-m-d?gh_jid=4952966101</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>ARX Robotics</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Project Manager - Infrastructure &amp; Expansion</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -626,24 +626,24 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>...s, and an in-house barista in Munich. Health &amp; Wellbeing: Includin...</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/arxroboticsgmbh/jobs/5005798101</t>
+          <t>https://www.atoss.com/en/company/career/jobs/4952966101-project-manager-f-m-d?gh_jid=4952966101</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Agile Robots</t>
+          <t>ARX Robotics</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -653,20 +653,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Senior Project Manager (all genders)</t>
+          <t>Project Manager - Infrastructure &amp; Expansion</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Munich, Bavaria, Germany</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/agilerobotsse/jobs/4990647101</t>
+          <t>https://job-boards.eu.greenhouse.io/arxroboticsgmbh/jobs/5005798101</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>zooplus</t>
+          <t>Agile Robots</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -688,32 +688,32 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Programme Manager - Supply Chain Optimization (All Genders) Munich, Germany Vendor Management &amp; Supply Full-time</t>
+          <t>Senior Project Manager (all genders)</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Munich, Bavaria, de</t>
+          <t>Munich, Bavaria, Germany</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://careers.zooplus.com/jobs/programme-manager-supply-chain-optimization-all-genders-munich-bavaria-germany-5dfc2de1-feba-4717-b007-7c814d41b155</t>
+          <t>https://job-boards.eu.greenhouse.io/agilerobotsse/jobs/4990647101</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>RobCo</t>
+          <t>zooplus</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>(Senior) Technical Program Manager (m/f/d)</t>
+          <t>Programme Manager - Supply Chain Optimization (All Genders) Munich, Germany Vendor Management &amp; Supply Full-time</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -731,24 +731,24 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>Munich, Bavaria, de</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/robco/a3b35c55-7d10-48b2-a1eb-a45a0e5d436a</t>
+          <t>https://careers.zooplus.com/jobs/programme-manager-supply-chain-optimization-all-genders-munich-bavaria-germany-5dfc2de1-feba-4717-b007-7c814d41b155</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Agile Robots</t>
+          <t>RobCo</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -766,24 +766,24 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Munich, Bavaria, Germany</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/agilerobotsse/jobs/4996481101</t>
+          <t>https://jobs.ashbyhq.com/robco/a3b35c55-7d10-48b2-a1eb-a45a0e5d436a</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Proxima Fusion</t>
+          <t>Agile Robots</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -793,32 +793,32 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Site Development Program Manager</t>
+          <t>(Senior) Technical Program Manager (m/f/d)</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>Munich, Bavaria, Germany</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/proxima-fusion/db5bc40c-aa3e-4735-94e7-096a556dd55d</t>
+          <t>https://job-boards.eu.greenhouse.io/agilerobotsse/jobs/4996481101</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>VoiceLine</t>
+          <t>Proxima Fusion</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Senior Project Manager Customer Implementations (m/w/d) München Vollzeit Festanstellung</t>
+          <t>Site Development Program Manager</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -836,24 +836,24 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>München, Bayern, DE</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://voiceline.jobs.personio.de/job/2382820</t>
+          <t>https://jobs.ashbyhq.com/proxima-fusion/db5bc40c-aa3e-4735-94e7-096a556dd55d</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Airbus</t>
+          <t>VoiceLine</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -863,55 +863,160 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Projectmanager Industrialisierung (d/m/w)</t>
+          <t>Senior Project Manager Customer Implementations (m/w/d) München Vollzeit Festanstellung</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Augsburg Area</t>
+          <t>München, Bayern, DE</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Augsburg-Area/Projectmanager-Industrialisierung--d-m-w-_JR10430741-1</t>
+          <t>https://voiceline.jobs.personio.de/job/2382820</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Airbus</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Projectmanager Industrialisierung (d/m/w)</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>10</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Augsburg Area</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Augsburg-Area/Projectmanager-Industrialisierung--d-m-w-_JR10430741-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>Isar Aerospace</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
         <is>
           <t>MES Delivery Manager / Project Manager (m/f/d)</t>
         </is>
       </c>
-      <c r="E14" t="n">
+      <c r="E15" t="n">
         <v>8</v>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>Parsdorf, Bavaria, Germany</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4989582101</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Thu Oct 15 02:00:00 UTC 2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Hensoldt</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>IT-Projektmanager Mission Support Systems P-8A (w/m/d)</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>...equisition ID: 2215 Location: Fürstenfeldbruck, DE, 82256 Company: ESG Elekt...</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-IT-Projektmanager-Mission-Support-Systems-P-8A-%28wmd%29-82256/1361630855/</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Thu Oct 15 02:00:00 UTC 2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Hensoldt</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Projektleiter TLB und Informationssicherheit P-8A (m/w/d)</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>...equisition ID: 4852 Location: Fürstenfeldbruck, DE, 82256 Wurster Nordseeküs...</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Projektleiter-TLB-und-Informationssicherheit-P-8A-%28mwd%29-82256/1361632455/</t>
         </is>
       </c>
     </row>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -571,35 +571,35 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Helsing</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
         <is>
           <t>(Senior) Programme Manager - Military Exercises</t>
         </is>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="E5" t="n">
         <v>8</v>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/5004102101?gh_jid=5004102101</t>
         </is>
@@ -951,72 +951,107 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Thu Oct 15 02:00:00 UTC 2026</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>Hensoldt</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
         <is>
           <t>IT-Projektmanager Mission Support Systems P-8A (w/m/d)</t>
         </is>
       </c>
-      <c r="E16" s="2" t="n">
+      <c r="E16" t="n">
         <v>7</v>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>...equisition ID: 2215 Location: Fürstenfeldbruck, DE, 82256 Company: ESG Elekt...</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-IT-Projektmanager-Mission-Support-Systems-P-8A-%28wmd%29-82256/1361630855/</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>Thu Oct 15 02:00:00 UTC 2026</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>Hensoldt</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
         <is>
           <t>Projektleiter TLB und Informationssicherheit P-8A (m/w/d)</t>
         </is>
       </c>
-      <c r="E17" s="2" t="n">
+      <c r="E17" t="n">
         <v>6</v>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>...equisition ID: 4852 Location: Fürstenfeldbruck, DE, 82256 Wurster Nordseeküs...</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Projektleiter-TLB-und-Informationssicherheit-P-8A-%28mwd%29-82256/1361632455/</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Thu Oct 15 02:00:00 UTC 2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Hensoldt</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Project Lead Police Helicopters (w/m/d)</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>...equisition ID: 5556 Location: Fürstenfeldbruck, DE, 82256 Company: ESG Elekt...</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Project-Lead-Police-Helicopters-%28wmd%29-82256/1361623855/</t>
         </is>
       </c>
     </row>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -1021,35 +1021,35 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>Thu Oct 15 02:00:00 UTC 2026</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>Hensoldt</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
         <is>
           <t>Project Lead Police Helicopters (w/m/d)</t>
         </is>
       </c>
-      <c r="E18" s="2" t="n">
+      <c r="E18" t="n">
         <v>4</v>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>...equisition ID: 5556 Location: Fürstenfeldbruck, DE, 82256 Company: ESG Elekt...</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Project-Lead-Police-Helicopters-%28wmd%29-82256/1361623855/</t>
         </is>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -811,49 +811,49 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Proxima Fusion</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Site Development Program Manager</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>3</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://jobs.ashbyhq.com/proxima-fusion/db5bc40c-aa3e-4735-94e7-096a556dd55d</t>
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Entrix</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Junior Portfolio Manager (d/f/m)</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>https://entrix.jobs.personio.com/job/2663715</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>VoiceLine</t>
+          <t>Proxima Fusion</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Senior Project Manager Customer Implementations (m/w/d) München Vollzeit Festanstellung</t>
+          <t>Site Development Program Manager</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -871,24 +871,24 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>München, Bayern, DE</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://voiceline.jobs.personio.de/job/2382820</t>
+          <t>https://jobs.ashbyhq.com/proxima-fusion/db5bc40c-aa3e-4735-94e7-096a556dd55d</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Airbus</t>
+          <t>VoiceLine</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -898,32 +898,32 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Projectmanager Industrialisierung (d/m/w)</t>
+          <t>Senior Project Manager Customer Implementations (m/w/d) München Vollzeit Festanstellung</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Augsburg Area</t>
+          <t>München, Bayern, DE</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Augsburg-Area/Projectmanager-Industrialisierung--d-m-w-_JR10430741-1</t>
+          <t>https://voiceline.jobs.personio.de/job/2382820</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Isar Aerospace</t>
+          <t>Airbus</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -933,32 +933,32 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>MES Delivery Manager / Project Manager (m/f/d)</t>
+          <t>Projectmanager Industrialisierung (d/m/w)</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Parsdorf, Bavaria, Germany</t>
+          <t>Augsburg Area</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4989582101</t>
+          <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Augsburg-Area/Projectmanager-Industrialisierung--d-m-w-_JR10430741-1</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Thu Oct 15 02:00:00 UTC 2026</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Hensoldt</t>
+          <t>Isar Aerospace</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -968,20 +968,20 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>IT-Projektmanager Mission Support Systems P-8A (w/m/d)</t>
+          <t>MES Delivery Manager / Project Manager (m/f/d)</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>...equisition ID: 2215 Location: Fürstenfeldbruck, DE, 82256 Company: ESG Elekt...</t>
+          <t>Parsdorf, Bavaria, Germany</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-IT-Projektmanager-Mission-Support-Systems-P-8A-%28wmd%29-82256/1361630855/</t>
+          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4989582101</t>
         </is>
       </c>
     </row>
@@ -1003,20 +1003,20 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Projektleiter TLB und Informationssicherheit P-8A (m/w/d)</t>
+          <t>IT-Projektmanager Mission Support Systems P-8A (w/m/d)</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>...equisition ID: 4852 Location: Fürstenfeldbruck, DE, 82256 Wurster Nordseeküs...</t>
+          <t>...equisition ID: 2215 Location: Fürstenfeldbruck, DE, 82256 Company: ESG Elekt...</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Projektleiter-TLB-und-Informationssicherheit-P-8A-%28mwd%29-82256/1361632455/</t>
+          <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-IT-Projektmanager-Mission-Support-Systems-P-8A-%28wmd%29-82256/1361630855/</t>
         </is>
       </c>
     </row>
@@ -1038,18 +1038,53 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>Projektleiter TLB und Informationssicherheit P-8A (m/w/d)</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>...equisition ID: 4852 Location: Fürstenfeldbruck, DE, 82256 Wurster Nordseeküs...</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Projektleiter-TLB-und-Informationssicherheit-P-8A-%28mwd%29-82256/1361632455/</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Thu Oct 15 02:00:00 UTC 2026</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Hensoldt</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
           <t>Project Lead Police Helicopters (w/m/d)</t>
         </is>
       </c>
-      <c r="E18" t="n">
+      <c r="E19" t="n">
         <v>4</v>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>...equisition ID: 5556 Location: Fürstenfeldbruck, DE, 82256 Company: ESG Elekt...</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Project-Lead-Police-Helicopters-%28wmd%29-82256/1361623855/</t>
         </is>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -811,49 +811,49 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Entrix</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Junior Portfolio Manager (d/f/m)</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>https://entrix.jobs.personio.com/job/2663715</t>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Proxima Fusion</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Site Development Program Manager</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>3</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/proxima-fusion/db5bc40c-aa3e-4735-94e7-096a556dd55d</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Proxima Fusion</t>
+          <t>VoiceLine</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Site Development Program Manager</t>
+          <t>Senior Project Manager Customer Implementations (m/w/d) München Vollzeit Festanstellung</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -871,24 +871,24 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>München, Bayern, DE</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/proxima-fusion/db5bc40c-aa3e-4735-94e7-096a556dd55d</t>
+          <t>https://voiceline.jobs.personio.de/job/2382820</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>VoiceLine</t>
+          <t>Airbus</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -898,32 +898,32 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Senior Project Manager Customer Implementations (m/w/d) München Vollzeit Festanstellung</t>
+          <t>Projectmanager Industrialisierung (d/m/w)</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>München, Bayern, DE</t>
+          <t>Augsburg Area</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://voiceline.jobs.personio.de/job/2382820</t>
+          <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Augsburg-Area/Projectmanager-Industrialisierung--d-m-w-_JR10430741-1</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Airbus</t>
+          <t>Isar Aerospace</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -933,32 +933,32 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Projectmanager Industrialisierung (d/m/w)</t>
+          <t>MES Delivery Manager / Project Manager (m/f/d)</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Augsburg Area</t>
+          <t>Parsdorf, Bavaria, Germany</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Augsburg-Area/Projectmanager-Industrialisierung--d-m-w-_JR10430741-1</t>
+          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4989582101</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>Thu Oct 15 02:00:00 UTC 2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Isar Aerospace</t>
+          <t>Hensoldt</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -968,20 +968,20 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>MES Delivery Manager / Project Manager (m/f/d)</t>
+          <t>IT-Projektmanager Mission Support Systems P-8A (w/m/d)</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Parsdorf, Bavaria, Germany</t>
+          <t>...equisition ID: 2215 Location: Fürstenfeldbruck, DE, 82256 Company: ESG Elekt...</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4989582101</t>
+          <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-IT-Projektmanager-Mission-Support-Systems-P-8A-%28wmd%29-82256/1361630855/</t>
         </is>
       </c>
     </row>
@@ -1003,20 +1003,20 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>IT-Projektmanager Mission Support Systems P-8A (w/m/d)</t>
+          <t>Projektleiter TLB und Informationssicherheit P-8A (m/w/d)</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>...equisition ID: 2215 Location: Fürstenfeldbruck, DE, 82256 Company: ESG Elekt...</t>
+          <t>...equisition ID: 4852 Location: Fürstenfeldbruck, DE, 82256 Wurster Nordseeküs...</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-IT-Projektmanager-Mission-Support-Systems-P-8A-%28wmd%29-82256/1361630855/</t>
+          <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Projektleiter-TLB-und-Informationssicherheit-P-8A-%28mwd%29-82256/1361632455/</t>
         </is>
       </c>
     </row>
@@ -1038,53 +1038,18 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Projektleiter TLB und Informationssicherheit P-8A (m/w/d)</t>
+          <t>Project Lead Police Helicopters (w/m/d)</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>...equisition ID: 4852 Location: Fürstenfeldbruck, DE, 82256 Wurster Nordseeküs...</t>
+          <t>...equisition ID: 5556 Location: Fürstenfeldbruck, DE, 82256 Company: ESG Elekt...</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
-        <is>
-          <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Projektleiter-TLB-und-Informationssicherheit-P-8A-%28mwd%29-82256/1361632455/</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Thu Oct 15 02:00:00 UTC 2026</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Hensoldt</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Project Lead Police Helicopters (w/m/d)</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>4</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>...equisition ID: 5556 Location: Fürstenfeldbruck, DE, 82256 Company: ESG Elekt...</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
         <is>
           <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Project-Lead-Police-Helicopters-%28wmd%29-82256/1361623855/</t>
         </is>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -743,12 +743,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>RobCo</t>
+          <t>Agile Robots</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -766,24 +766,24 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>Munich, Bavaria, Germany</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/robco/a3b35c55-7d10-48b2-a1eb-a45a0e5d436a</t>
+          <t>https://job-boards.eu.greenhouse.io/agilerobotsse/jobs/4996481101</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Agile Robots</t>
+          <t>Proxima Fusion</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -793,32 +793,32 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>(Senior) Technical Program Manager (m/f/d)</t>
+          <t>Site Development Program Manager</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Munich, Bavaria, Germany</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/agilerobotsse/jobs/4996481101</t>
+          <t>https://jobs.ashbyhq.com/proxima-fusion/db5bc40c-aa3e-4735-94e7-096a556dd55d</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Proxima Fusion</t>
+          <t>VoiceLine</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Site Development Program Manager</t>
+          <t>Senior Project Manager Customer Implementations (m/w/d) München Vollzeit Festanstellung</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -836,24 +836,24 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>München, Bayern, DE</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/proxima-fusion/db5bc40c-aa3e-4735-94e7-096a556dd55d</t>
+          <t>https://voiceline.jobs.personio.de/job/2382820</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>VoiceLine</t>
+          <t>Airbus</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -863,32 +863,32 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Senior Project Manager Customer Implementations (m/w/d) München Vollzeit Festanstellung</t>
+          <t>Projectmanager Industrialisierung (d/m/w)</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>München, Bayern, DE</t>
+          <t>Augsburg Area</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://voiceline.jobs.personio.de/job/2382820</t>
+          <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Augsburg-Area/Projectmanager-Industrialisierung--d-m-w-_JR10430741-1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Airbus</t>
+          <t>Isar Aerospace</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -898,32 +898,32 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Projectmanager Industrialisierung (d/m/w)</t>
+          <t>MES Delivery Manager / Project Manager (m/f/d)</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Augsburg Area</t>
+          <t>Parsdorf, Bavaria, Germany</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Augsburg-Area/Projectmanager-Industrialisierung--d-m-w-_JR10430741-1</t>
+          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4989582101</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>Thu Oct 15 02:00:00 UTC 2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Isar Aerospace</t>
+          <t>Hensoldt</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -933,20 +933,20 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>MES Delivery Manager / Project Manager (m/f/d)</t>
+          <t>IT-Projektmanager Mission Support Systems P-8A (w/m/d)</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Parsdorf, Bavaria, Germany</t>
+          <t>...equisition ID: 2215 Location: Fürstenfeldbruck, DE, 82256 Company: ESG Elekt...</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4989582101</t>
+          <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-IT-Projektmanager-Mission-Support-Systems-P-8A-%28wmd%29-82256/1361630855/</t>
         </is>
       </c>
     </row>
@@ -968,20 +968,20 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>IT-Projektmanager Mission Support Systems P-8A (w/m/d)</t>
+          <t>Projektleiter TLB und Informationssicherheit P-8A (m/w/d)</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>...equisition ID: 2215 Location: Fürstenfeldbruck, DE, 82256 Company: ESG Elekt...</t>
+          <t>...equisition ID: 4852 Location: Fürstenfeldbruck, DE, 82256 Wurster Nordseeküs...</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-IT-Projektmanager-Mission-Support-Systems-P-8A-%28wmd%29-82256/1361630855/</t>
+          <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Projektleiter-TLB-und-Informationssicherheit-P-8A-%28mwd%29-82256/1361632455/</t>
         </is>
       </c>
     </row>
@@ -1003,53 +1003,18 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Projektleiter TLB und Informationssicherheit P-8A (m/w/d)</t>
+          <t>Project Lead Police Helicopters (w/m/d)</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>...equisition ID: 4852 Location: Fürstenfeldbruck, DE, 82256 Wurster Nordseeküs...</t>
+          <t>...equisition ID: 5556 Location: Fürstenfeldbruck, DE, 82256 Company: ESG Elekt...</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
-        <is>
-          <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Projektleiter-TLB-und-Informationssicherheit-P-8A-%28mwd%29-82256/1361632455/</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Thu Oct 15 02:00:00 UTC 2026</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Hensoldt</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Project Lead Police Helicopters (w/m/d)</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>4</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>...equisition ID: 5556 Location: Fürstenfeldbruck, DE, 82256 Company: ESG Elekt...</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
         <is>
           <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Project-Lead-Police-Helicopters-%28wmd%29-82256/1361623855/</t>
         </is>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -671,37 +671,37 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Agile Robots</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Senior Project Manager (all genders)</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>5</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Munich, Bavaria, Germany</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://job-boards.eu.greenhouse.io/agilerobotsse/jobs/4990647101</t>
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Senior Programme Manager - International Business Development Air</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/5001597101?gh_jid=5001597101</t>
         </is>
       </c>
     </row>
@@ -713,7 +713,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>zooplus</t>
+          <t>Agile Robots</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -723,32 +723,32 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Programme Manager - Supply Chain Optimization (All Genders) Munich, Germany Vendor Management &amp; Supply Full-time</t>
+          <t>Senior Project Manager (all genders)</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Munich, Bavaria, de</t>
+          <t>Munich, Bavaria, Germany</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://careers.zooplus.com/jobs/programme-manager-supply-chain-optimization-all-genders-munich-bavaria-germany-5dfc2de1-feba-4717-b007-7c814d41b155</t>
+          <t>https://job-boards.eu.greenhouse.io/agilerobotsse/jobs/4990647101</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Agile Robots</t>
+          <t>zooplus</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>(Senior) Technical Program Manager (m/f/d)</t>
+          <t>Programme Manager - Supply Chain Optimization (All Genders) Munich, Germany Vendor Management &amp; Supply Full-time</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -766,24 +766,24 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Munich, Bavaria, Germany</t>
+          <t>Munich, Bavaria, de</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/agilerobotsse/jobs/4996481101</t>
+          <t>https://careers.zooplus.com/jobs/programme-manager-supply-chain-optimization-all-genders-munich-bavaria-germany-5dfc2de1-feba-4717-b007-7c814d41b155</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Proxima Fusion</t>
+          <t>Agile Robots</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -793,32 +793,32 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Site Development Program Manager</t>
+          <t>(Senior) Technical Program Manager (m/f/d)</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>Munich, Bavaria, Germany</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/proxima-fusion/db5bc40c-aa3e-4735-94e7-096a556dd55d</t>
+          <t>https://job-boards.eu.greenhouse.io/agilerobotsse/jobs/4996481101</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>VoiceLine</t>
+          <t>Proxima Fusion</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Senior Project Manager Customer Implementations (m/w/d) München Vollzeit Festanstellung</t>
+          <t>Site Development Program Manager</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -836,24 +836,24 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>München, Bayern, DE</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://voiceline.jobs.personio.de/job/2382820</t>
+          <t>https://jobs.ashbyhq.com/proxima-fusion/db5bc40c-aa3e-4735-94e7-096a556dd55d</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Airbus</t>
+          <t>VoiceLine</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -863,32 +863,32 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Projectmanager Industrialisierung (d/m/w)</t>
+          <t>Senior Project Manager Customer Implementations (m/w/d) München Vollzeit Festanstellung</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Augsburg Area</t>
+          <t>München, Bayern, DE</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Augsburg-Area/Projectmanager-Industrialisierung--d-m-w-_JR10430741-1</t>
+          <t>https://voiceline.jobs.personio.de/job/2382820</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Isar Aerospace</t>
+          <t>Airbus</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -898,32 +898,32 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>MES Delivery Manager / Project Manager (m/f/d)</t>
+          <t>Projectmanager Industrialisierung (d/m/w)</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Parsdorf, Bavaria, Germany</t>
+          <t>Augsburg Area</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4989582101</t>
+          <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Augsburg-Area/Projectmanager-Industrialisierung--d-m-w-_JR10430741-1</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Thu Oct 15 02:00:00 UTC 2026</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Hensoldt</t>
+          <t>Isar Aerospace</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -933,20 +933,20 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>IT-Projektmanager Mission Support Systems P-8A (w/m/d)</t>
+          <t>MES Delivery Manager / Project Manager (m/f/d)</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>...equisition ID: 2215 Location: Fürstenfeldbruck, DE, 82256 Company: ESG Elekt...</t>
+          <t>Parsdorf, Bavaria, Germany</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-IT-Projektmanager-Mission-Support-Systems-P-8A-%28wmd%29-82256/1361630855/</t>
+          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4989582101</t>
         </is>
       </c>
     </row>
@@ -968,20 +968,20 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Projektleiter TLB und Informationssicherheit P-8A (m/w/d)</t>
+          <t>IT-Projektmanager Mission Support Systems P-8A (w/m/d)</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>...equisition ID: 4852 Location: Fürstenfeldbruck, DE, 82256 Wurster Nordseeküs...</t>
+          <t>...equisition ID: 2215 Location: Fürstenfeldbruck, DE, 82256 Company: ESG Elekt...</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Projektleiter-TLB-und-Informationssicherheit-P-8A-%28mwd%29-82256/1361632455/</t>
+          <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-IT-Projektmanager-Mission-Support-Systems-P-8A-%28wmd%29-82256/1361630855/</t>
         </is>
       </c>
     </row>
@@ -1003,18 +1003,53 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t>Projektleiter TLB und Informationssicherheit P-8A (m/w/d)</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>...equisition ID: 4852 Location: Fürstenfeldbruck, DE, 82256 Wurster Nordseeküs...</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Projektleiter-TLB-und-Informationssicherheit-P-8A-%28mwd%29-82256/1361632455/</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Thu Oct 15 02:00:00 UTC 2026</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Hensoldt</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
           <t>Project Lead Police Helicopters (w/m/d)</t>
         </is>
       </c>
-      <c r="E17" t="n">
+      <c r="E18" t="n">
         <v>4</v>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>...equisition ID: 5556 Location: Fürstenfeldbruck, DE, 82256 Company: ESG Elekt...</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Project-Lead-Police-Helicopters-%28wmd%29-82256/1361623855/</t>
         </is>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -671,35 +671,35 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Helsing</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
         <is>
           <t>Senior Programme Manager - International Business Development Air</t>
         </is>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="E8" t="n">
         <v>6</v>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/5001597101?gh_jid=5001597101</t>
         </is>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -30,7 +30,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -41,6 +41,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="001F2937"/>
         <bgColor rgb="001F2937"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D1FAE5"/>
+        <bgColor rgb="00D1FAE5"/>
       </patternFill>
     </fill>
   </fills>
@@ -56,9 +62,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -424,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -485,6 +492,726 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(Senior) Programme Manager - Military Exercises</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/5004102101?gh_jid=5004102101</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Title: programme manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>ARX Robotics</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Project Manager - Infrastructure &amp; Expansion</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/arxroboticsgmbh/jobs/5005798101</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Title: project manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Senior Programme Manager - International Business Development Air</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/5001597101?gh_jid=5001597101</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Title: programme manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>BearingPoint</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>(Senior) Consultant / Architect ServiceNow Banking &amp; Insurance (m/w/d) Berlin, Düsseldorf, Frankfurt am Main, Hamburg, Leipzig, München, Stuttgart, Walldorf</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Berlin, DE; Düsseldorf, DE; Frankfurt am Main, DE; Hamburg, DE; Leipzig, DE; München, DE; Stuttgart, DE; Walldorf, DE</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bearingpoint.com/de-de/karriere/stellenangebote/angebot/?id=T7549597</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Related role</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>Responsibilities: delivery, transformation</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Agile Robots</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Senior Project Manager (all genders)</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Bavaria, Germany</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/agilerobotsse/jobs/4990647101</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Title: project manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Senior Business Transformation &amp; Process Optimisation Consultant - Aviation/Logistics</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/8015653003?gh_jid=8015653003</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Related role</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Responsibilities: delivery, stakeholders, transformation</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Senior Digital Transformation &amp; Process Optimisation Consultant - CPG/Retail</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/8016417003?gh_jid=8016417003</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Related role</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>Responsibilities: delivery, stakeholders, transformation</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Senior Management &amp; Technology Consultant - Aviation/Logistics</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/8015654003?gh_jid=8015654003</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Related role</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Responsibilities: delivery, stakeholders, transformation</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Senior Management &amp; Technology Consultant - CPG/Retail - CPG/Retail</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/8016657003?gh_jid=8016657003</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Related role</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>Responsibilities: delivery, stakeholders, transformation</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Senior Management &amp; Technology Consultant - Growth &amp; Scale Accounts</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/8026730003?gh_jid=8026730003</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Related role</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>Responsibilities: governance, stakeholders, transformation</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Senior Process Intelligence &amp; Supply Chain Transformation Consultant - Aviation/Logistics</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/8015655003?gh_jid=8015655003</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Related role</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>Responsibilities: delivery, stakeholders, transformation</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Senior Process Intelligence &amp; Supply Chain Transformation Consultant - CPG/Retail</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/8016658003?gh_jid=8016658003</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Related role</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>Responsibilities: delivery, stakeholders, transformation</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Senior Process Optimisation Consultant - Growth &amp; Scale Accounts</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/8026747003?gh_jid=8026747003</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Related role</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>Responsibilities: governance, stakeholders, transformation</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Agile Robots</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>(Senior) Technical Program Manager (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Bavaria, Germany</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/agilerobotsse/jobs/4996481101</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>Title: program manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Proxima Fusion</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Site Development Program Manager</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/proxima-fusion/db5bc40c-aa3e-4735-94e7-096a556dd55d</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>Title: program manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Isar Aerospace</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>MES Delivery Manager / Project Manager (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Parsdorf, Bavaria, Germany</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4989582101</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>Title: project manager</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -493,720 +493,720 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Helsing</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
         <is>
           <t>(Senior) Programme Manager - Military Exercises</t>
         </is>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" t="n">
         <v>8</v>
       </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/5004102101?gh_jid=5004102101</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>Direct role</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>Title: programme manager</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>ARX Robotics</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
         <is>
           <t>Project Manager - Infrastructure &amp; Expansion</t>
         </is>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E3" t="n">
         <v>6</v>
       </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
         <is>
           <t>https://job-boards.eu.greenhouse.io/arxroboticsgmbh/jobs/5005798101</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>Direct role</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>Title: project manager</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Helsing</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
         <is>
           <t>Senior Programme Manager - International Business Development Air</t>
         </is>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="E4" t="n">
         <v>6</v>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/5001597101?gh_jid=5001597101</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>Direct role</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>Title: programme manager</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>BearingPoint</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
         <is>
           <t>(Senior) Consultant / Architect ServiceNow Banking &amp; Insurance (m/w/d) Berlin, Düsseldorf, Frankfurt am Main, Hamburg, Leipzig, München, Stuttgart, Walldorf</t>
         </is>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="E5" t="n">
         <v>5</v>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>Berlin, DE; Düsseldorf, DE; Frankfurt am Main, DE; Hamburg, DE; Leipzig, DE; München, DE; Stuttgart, DE; Walldorf, DE</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>https://www.bearingpoint.com/de-de/karriere/stellenangebote/angebot/?id=T7549597</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>Related role</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>Responsibilities: delivery, transformation</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Agile Robots</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
         <is>
           <t>Senior Project Manager (all genders)</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="E6" t="n">
         <v>5</v>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>Munich, Bavaria, Germany</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>https://job-boards.eu.greenhouse.io/agilerobotsse/jobs/4990647101</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>Direct role</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>Title: project manager</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
         <is>
           <t>Senior Business Transformation &amp; Process Optimisation Consultant - Aviation/Logistics</t>
         </is>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="E7" t="n">
         <v>4</v>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/8015653003?gh_jid=8015653003</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>Related role</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>Responsibilities: delivery, stakeholders, transformation</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
         <is>
           <t>Senior Digital Transformation &amp; Process Optimisation Consultant - CPG/Retail</t>
         </is>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="E8" t="n">
         <v>4</v>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/8016417003?gh_jid=8016417003</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>Related role</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>Responsibilities: delivery, stakeholders, transformation</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
         <is>
           <t>Senior Management &amp; Technology Consultant - Aviation/Logistics</t>
         </is>
       </c>
-      <c r="E9" s="2" t="n">
+      <c r="E9" t="n">
         <v>4</v>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/8015654003?gh_jid=8015654003</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>Related role</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>Responsibilities: delivery, stakeholders, transformation</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
         <is>
           <t>Senior Management &amp; Technology Consultant - CPG/Retail - CPG/Retail</t>
         </is>
       </c>
-      <c r="E10" s="2" t="n">
+      <c r="E10" t="n">
         <v>4</v>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/8016657003?gh_jid=8016657003</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>Related role</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>Responsibilities: delivery, stakeholders, transformation</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
         <is>
           <t>Senior Management &amp; Technology Consultant - Growth &amp; Scale Accounts</t>
         </is>
       </c>
-      <c r="E11" s="2" t="n">
+      <c r="E11" t="n">
         <v>4</v>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/8026730003?gh_jid=8026730003</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>Related role</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>Responsibilities: governance, stakeholders, transformation</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
         <is>
           <t>Senior Process Intelligence &amp; Supply Chain Transformation Consultant - Aviation/Logistics</t>
         </is>
       </c>
-      <c r="E12" s="2" t="n">
+      <c r="E12" t="n">
         <v>4</v>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/8015655003?gh_jid=8015655003</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>Related role</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>Responsibilities: delivery, stakeholders, transformation</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>Senior Process Intelligence &amp; Supply Chain Transformation Consultant - CPG/Retail</t>
         </is>
       </c>
-      <c r="E13" s="2" t="n">
+      <c r="E13" t="n">
         <v>4</v>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/8016658003?gh_jid=8016658003</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>Related role</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>Responsibilities: delivery, stakeholders, transformation</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t>Senior Process Optimisation Consultant - Growth &amp; Scale Accounts</t>
         </is>
       </c>
-      <c r="E14" s="2" t="n">
+      <c r="E14" t="n">
         <v>4</v>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/8026747003?gh_jid=8026747003</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>Related role</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>Responsibilities: governance, stakeholders, transformation</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>Agile Robots</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
         <is>
           <t>(Senior) Technical Program Manager (m/f/d)</t>
         </is>
       </c>
-      <c r="E15" s="2" t="n">
+      <c r="E15" t="n">
         <v>4</v>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>Munich, Bavaria, Germany</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>https://job-boards.eu.greenhouse.io/agilerobotsse/jobs/4996481101</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>Direct role</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>Title: program manager</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>Proxima Fusion</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
         <is>
           <t>Site Development Program Manager</t>
         </is>
       </c>
-      <c r="E16" s="2" t="n">
+      <c r="E16" t="n">
         <v>3</v>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/proxima-fusion/db5bc40c-aa3e-4735-94e7-096a556dd55d</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>Direct role</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>Title: program manager</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>Isar Aerospace</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
         <is>
           <t>MES Delivery Manager / Project Manager (m/f/d)</t>
         </is>
       </c>
-      <c r="E17" s="2" t="n">
+      <c r="E17" t="n">
         <v>8</v>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>Parsdorf, Bavaria, Germany</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4989582101</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>Direct role</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>Title: project manager</t>
         </is>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -630,12 +630,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BearingPoint</t>
+          <t>Agile Robots</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -645,7 +645,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>(Senior) Consultant / Architect ServiceNow Banking &amp; Insurance (m/w/d) Berlin, Düsseldorf, Frankfurt am Main, Hamburg, Leipzig, München, Stuttgart, Walldorf</t>
+          <t>Senior Project Manager (all genders)</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -653,29 +653,29 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Berlin, DE; Düsseldorf, DE; Frankfurt am Main, DE; Hamburg, DE; Leipzig, DE; München, DE; Stuttgart, DE; Walldorf, DE</t>
+          <t>Munich, Bavaria, Germany</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.bearingpoint.com/de-de/karriere/stellenangebote/angebot/?id=T7549597</t>
+          <t>https://job-boards.eu.greenhouse.io/agilerobotsse/jobs/4990647101</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Related role</t>
+          <t>Direct role</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Responsibilities: delivery, transformation</t>
+          <t>Title: project manager</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -690,11 +690,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Senior Project Manager (all genders)</t>
+          <t>(Senior) Technical Program Manager (m/f/d)</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/agilerobotsse/jobs/4990647101</t>
+          <t>https://job-boards.eu.greenhouse.io/agilerobotsse/jobs/4996481101</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -713,19 +713,19 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Title: project manager</t>
+          <t>Title: program manager</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Celonis</t>
+          <t>Proxima Fusion</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -735,87 +735,87 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Senior Business Transformation &amp; Process Optimisation Consultant - Aviation/Logistics</t>
+          <t>Site Development Program Manager</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Munich, Germany</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/8015653003?gh_jid=8015653003</t>
+          <t>https://jobs.ashbyhq.com/proxima-fusion/db5bc40c-aa3e-4735-94e7-096a556dd55d</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Related role</t>
+          <t>Direct role</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Responsibilities: delivery, stakeholders, transformation</t>
+          <t>Title: program manager</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Celonis</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Senior Digital Transformation &amp; Process Optimisation Consultant - CPG/Retail</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>4</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Munich, Germany</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/8016417003?gh_jid=8016417003</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Related role</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Responsibilities: delivery, stakeholders, transformation</t>
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>appliedAI</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>AI Manager / Senior Project Lead (m/f/x)</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>München (81671)</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>https://appliedai.jobs.personio.de/job/2846436</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>Title: project lead</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Celonis</t>
+          <t>Isar Aerospace</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -825,388 +825,28 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Senior Management &amp; Technology Consultant - Aviation/Logistics</t>
+          <t>MES Delivery Manager / Project Manager (m/f/d)</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Munich, Germany</t>
+          <t>Parsdorf, Bavaria, Germany</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/8015654003?gh_jid=8015654003</t>
+          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4989582101</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Related role</t>
+          <t>Direct role</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
-        <is>
-          <t>Responsibilities: delivery, stakeholders, transformation</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Celonis</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Senior Management &amp; Technology Consultant - CPG/Retail - CPG/Retail</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>4</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Munich, Germany</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/8016657003?gh_jid=8016657003</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Related role</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Responsibilities: delivery, stakeholders, transformation</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Celonis</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Senior Management &amp; Technology Consultant - Growth &amp; Scale Accounts</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>4</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Munich, Germany</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/8026730003?gh_jid=8026730003</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Related role</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Responsibilities: governance, stakeholders, transformation</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Celonis</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Senior Process Intelligence &amp; Supply Chain Transformation Consultant - Aviation/Logistics</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>4</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Munich, Germany</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/8015655003?gh_jid=8015655003</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Related role</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Responsibilities: delivery, stakeholders, transformation</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Celonis</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Senior Process Intelligence &amp; Supply Chain Transformation Consultant - CPG/Retail</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>4</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Munich, Germany</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/8016658003?gh_jid=8016658003</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Related role</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Responsibilities: delivery, stakeholders, transformation</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Celonis</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Senior Process Optimisation Consultant - Growth &amp; Scale Accounts</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>4</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Munich, Germany</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/8026747003?gh_jid=8026747003</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Related role</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Responsibilities: governance, stakeholders, transformation</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Agile Robots</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>(Senior) Technical Program Manager (m/f/d)</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>4</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Munich, Bavaria, Germany</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://job-boards.eu.greenhouse.io/agilerobotsse/jobs/4996481101</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Direct role</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Title: program manager</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Proxima Fusion</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Site Development Program Manager</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>3</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://jobs.ashbyhq.com/proxima-fusion/db5bc40c-aa3e-4735-94e7-096a556dd55d</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Direct role</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>Title: program manager</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Isar Aerospace</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>MES Delivery Manager / Project Manager (m/f/d)</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>8</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Parsdorf, Bavaria, Germany</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4989582101</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Direct role</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
         <is>
           <t>Title: project manager</t>
         </is>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -763,90 +763,135 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>appliedAI</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
         <is>
           <t>AI Manager / Senior Project Lead (m/f/x)</t>
         </is>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="E8" t="n">
         <v>3</v>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>München (81671)</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>https://appliedai.jobs.personio.de/job/2846436</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>Direct role</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>Title: project lead</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Airbus</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Projectmanager Industrialisierung (d/m/w)</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Augsburg Area</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Augsburg-Area/Projectmanager-Industrialisierung--d-m-w-_JR10430741-1</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Title: project manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Isar Aerospace</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
         <is>
           <t>MES Delivery Manager / Project Manager (m/f/d)</t>
         </is>
       </c>
-      <c r="E9" t="n">
+      <c r="E10" t="n">
         <v>8</v>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>Parsdorf, Bavaria, Germany</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4989582101</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>Direct role</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>Title: project manager</t>
         </is>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -808,45 +808,45 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Airbus</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
         <is>
           <t>Projectmanager Industrialisierung (d/m/w)</t>
         </is>
       </c>
-      <c r="E9" s="2" t="n">
+      <c r="E9" t="n">
         <v>10</v>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>Augsburg Area</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Augsburg-Area/Projectmanager-Industrialisierung--d-m-w-_JR10430741-1</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>Direct role</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>Title: project manager</t>
         </is>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -852,51 +852,6 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Isar Aerospace</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>MES Delivery Manager / Project Manager (m/f/d)</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>8</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Parsdorf, Bavaria, Germany</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4989582101</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Direct role</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Title: project manager</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -493,360 +493,806 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>(Senior) Programme Manager - Military Exercises</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>8</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>https://helsing.ai/jobs/5004102101?gh_jid=5004102101</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr"/>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>SES</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Project Manager, IVV, Satellite Systems, IRIS2 Programme Office</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Munich (Unterföhring), DE +1 more…</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>https://careers.ses.com/job/Munich-%28Unterf%C3%B6hring%29-Project-Manager%2C-IVV%2C-Satellite-Systems%2C-IRIS2-Programme-Office/1396651333/</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>Direct role</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Title: programme manager</t>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Title: project manager</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>ARX Robotics</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Project Manager - Infrastructure &amp; Expansion</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>6</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>https://job-boards.eu.greenhouse.io/arxroboticsgmbh/jobs/5005798101</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Direct role</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Title: project manager</t>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Senior Business Transformation &amp; Process Optimisation Consultant - Aviation/Logistics</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/8015653003?gh_jid=8015653003</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Related role</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Responsibilities: delivery, stakeholders, transformation</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Senior Programme Manager - International Business Development Air</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>6</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>https://helsing.ai/jobs/5001597101?gh_jid=5001597101</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Direct role</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Title: programme manager</t>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Senior Management &amp; Technology Consultant - Aviation/Logistics</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/8015654003?gh_jid=8015654003</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Related role</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Responsibilities: delivery, stakeholders, transformation</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Agile Robots</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Senior Project Manager (all genders)</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>5</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Munich, Bavaria, Germany</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>https://job-boards.eu.greenhouse.io/agilerobotsse/jobs/4990647101</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Direct role</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Title: project manager</t>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Senior Management &amp; Technology Consultant - Growth &amp; Scale Accounts</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/8026730003?gh_jid=8026730003</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Related role</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>Responsibilities: delivery, governance, stakeholders, transformation</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Agile Robots</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>(Senior) Technical Program Manager (m/f/d)</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>4</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Munich, Bavaria, Germany</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://job-boards.eu.greenhouse.io/agilerobotsse/jobs/4996481101</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Direct role</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Title: program manager</t>
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Senior Process Intelligence &amp; Supply Chain Transformation Consultant - Aviation/Logistics</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/8015655003?gh_jid=8015655003</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Related role</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Responsibilities: delivery, stakeholders, transformation</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Proxima Fusion</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Site Development Program Manager</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>3</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://jobs.ashbyhq.com/proxima-fusion/db5bc40c-aa3e-4735-94e7-096a556dd55d</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Direct role</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Title: program manager</t>
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Senior Process Optimisation Consultant - Growth &amp; Scale Accounts</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/8026747003?gh_jid=8026747003</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Related role</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Responsibilities: delivery, governance, stakeholders, transformation</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>(Senior) Programme Manager - Military Exercises</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/5004102101?gh_jid=5004102101</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Title: programme manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Senior Digital Transformation &amp; Process Optimisation Consultant - CPG/Retail</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/8016417003?gh_jid=8016417003</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Related role</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Responsibilities: delivery, stakeholders, transformation</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Senior Management &amp; Technology Consultant - CPG/Retail - CPG/Retail</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/8016657003?gh_jid=8016657003</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Related role</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>Responsibilities: delivery, stakeholders, transformation</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Senior Process Intelligence &amp; Supply Chain Transformation Consultant - CPG/Retail</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/8016658003?gh_jid=8016658003</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Related role</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>Responsibilities: delivery, stakeholders, transformation</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ARX Robotics</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Project Manager - Infrastructure &amp; Expansion</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/arxroboticsgmbh/jobs/5005798101</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Title: project manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Senior Programme Manager - International Business Development Air</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/5001597101?gh_jid=5001597101</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Title: programme manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Agile Robots</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Senior Project Manager (all genders)</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>5</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Munich, Bavaria, Germany</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/agilerobotsse/jobs/4990647101</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Title: project manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Agile Robots</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>(Senior) Technical Program Manager (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>4</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Munich, Bavaria, Germany</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/agilerobotsse/jobs/4996481101</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Title: program manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Proxima Fusion</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Site Development Program Manager</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>3</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/proxima-fusion/db5bc40c-aa3e-4735-94e7-096a556dd55d</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Title: program manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>appliedAI</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
         <is>
           <t>AI Manager / Senior Project Lead (m/f/x)</t>
         </is>
       </c>
-      <c r="E8" t="n">
+      <c r="E17" t="n">
         <v>3</v>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>München (81671)</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>https://appliedai.jobs.personio.de/job/2846436</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>Direct role</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>Title: project lead</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Avelios Medical</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Senior Technical Program Manager (all genders) </t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/avelios-medical/6a0ad925-ab31-4125-a1a1-c4de7ce1b5a6</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>Title: program manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>Airbus</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
         <is>
           <t>Projectmanager Industrialisierung (d/m/w)</t>
         </is>
       </c>
-      <c r="E9" t="n">
+      <c r="E19" t="n">
         <v>10</v>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>Augsburg Area</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Augsburg-Area/Projectmanager-Industrialisierung--d-m-w-_JR10430741-1</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>Direct role</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>Title: project manager</t>
         </is>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -493,266 +493,265 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr"/>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>SES</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
         <is>
           <t>Project Manager, IVV, Satellite Systems, IRIS2 Programme Office</t>
         </is>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" t="n">
         <v>4</v>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Munich (Unterföhring), DE +1 more…</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>https://careers.ses.com/job/Munich-%28Unterf%C3%B6hring%29-Project-Manager%2C-IVV%2C-Satellite-Systems%2C-IRIS2-Programme-Office/1396651333/</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>Direct role</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>Title: project manager</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
         <is>
           <t>Senior Business Transformation &amp; Process Optimisation Consultant - Aviation/Logistics</t>
         </is>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E3" t="n">
         <v>10</v>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/8015653003?gh_jid=8015653003</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>Related role</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>Responsibilities: delivery, stakeholders, transformation</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
         <is>
           <t>Senior Management &amp; Technology Consultant - Aviation/Logistics</t>
         </is>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="E4" t="n">
         <v>10</v>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/8015654003?gh_jid=8015654003</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>Related role</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>Responsibilities: delivery, stakeholders, transformation</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
         <is>
           <t>Senior Management &amp; Technology Consultant - Growth &amp; Scale Accounts</t>
         </is>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="E5" t="n">
         <v>10</v>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/8026730003?gh_jid=8026730003</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>Related role</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>Responsibilities: delivery, governance, stakeholders, transformation</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
         <is>
           <t>Senior Process Intelligence &amp; Supply Chain Transformation Consultant - Aviation/Logistics</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="E6" t="n">
         <v>10</v>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/8015655003?gh_jid=8015655003</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>Related role</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>Responsibilities: delivery, stakeholders, transformation</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
         <is>
           <t>Senior Process Optimisation Consultant - Growth &amp; Scale Accounts</t>
         </is>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="E7" t="n">
         <v>10</v>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/8026747003?gh_jid=8026747003</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>Related role</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>Responsibilities: delivery, governance, stakeholders, transformation</t>
         </is>
@@ -804,135 +803,135 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
         <is>
           <t>Senior Digital Transformation &amp; Process Optimisation Consultant - CPG/Retail</t>
         </is>
       </c>
-      <c r="E9" s="2" t="n">
+      <c r="E9" t="n">
         <v>8</v>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/8016417003?gh_jid=8016417003</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>Related role</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>Responsibilities: delivery, stakeholders, transformation</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
         <is>
           <t>Senior Management &amp; Technology Consultant - CPG/Retail - CPG/Retail</t>
         </is>
       </c>
-      <c r="E10" s="2" t="n">
+      <c r="E10" t="n">
         <v>8</v>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/8016657003?gh_jid=8016657003</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>Related role</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>Responsibilities: delivery, stakeholders, transformation</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
         <is>
           <t>Senior Process Intelligence &amp; Supply Chain Transformation Consultant - CPG/Retail</t>
         </is>
       </c>
-      <c r="E11" s="2" t="n">
+      <c r="E11" t="n">
         <v>8</v>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/8016658003?gh_jid=8016658003</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>Related role</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>Responsibilities: delivery, stakeholders, transformation</t>
         </is>
@@ -1209,45 +1208,45 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>Avelios Medical</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
         <is>
           <t xml:space="preserve">Senior Technical Program Manager (all genders) </t>
         </is>
       </c>
-      <c r="E18" s="2" t="n">
+      <c r="E18" t="n">
         <v>3</v>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/avelios-medical/6a0ad925-ab31-4125-a1a1-c4de7ce1b5a6</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>Direct role</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>Title: program manager</t>
         </is>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1028,54 +1028,54 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Agile Robots</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Senior Project Manager (all genders)</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>5</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Munich, Bavaria, Germany</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://job-boards.eu.greenhouse.io/agilerobotsse/jobs/4990647101</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Nvidia Munich</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Senior Technical Program Manager - Nemotron</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Germany, Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>https://nvidia.wd5.myworkdayjobs.com/NVIDIAExternalCareerSite/job/Germany-Munich/Senior-Technical-Program-Manager---Nemotron_JR2028331</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>Direct role</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Title: project manager</t>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>Title: program manager</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1090,11 +1090,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>(Senior) Technical Program Manager (m/f/d)</t>
+          <t>Senior Project Manager (all genders)</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/agilerobotsse/jobs/4996481101</t>
+          <t>https://job-boards.eu.greenhouse.io/agilerobotsse/jobs/4990647101</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1113,64 +1113,64 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Title: program manager</t>
+          <t>Title: project manager</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Proxima Fusion</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Site Development Program Manager</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>3</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://jobs.ashbyhq.com/proxima-fusion/db5bc40c-aa3e-4735-94e7-096a556dd55d</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Agile Robots</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Project Coordinator – Site &amp; KPI (m/f/d) Fixed-term 18 months</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Bavaria, Germany</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/agilerobotsse/jobs/5013124101</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>Direct role</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>Title: program manager</t>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>Title: project coordinator</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>appliedAI</t>
+          <t>Agile Robots</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1180,20 +1180,20 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>AI Manager / Senior Project Lead (m/f/x)</t>
+          <t>(Senior) Technical Program Manager (m/f/d)</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>München (81671)</t>
+          <t>Munich, Bavaria, Germany</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://appliedai.jobs.personio.de/job/2846436</t>
+          <t>https://job-boards.eu.greenhouse.io/agilerobotsse/jobs/4996481101</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1203,95 +1203,230 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Title: project lead</t>
+          <t>Title: program manager</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Avelios Medical</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Senior Technical Program Manager (all genders) </t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>3</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://jobs.ashbyhq.com/avelios-medical/6a0ad925-ab31-4125-a1a1-c4de7ce1b5a6</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Agile Robots</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Project Coordinator – New Tasks &amp; QC (m/f/d) Fixed-term 18 months</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Bavaria, Germany</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/agilerobotsse/jobs/5013108101</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>Direct role</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>Title: program manager</t>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>Title: project coordinator</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Proxima Fusion</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Site Development Program Manager</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>3</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/proxima-fusion/db5bc40c-aa3e-4735-94e7-096a556dd55d</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Title: program manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>appliedAI</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>AI Manager / Senior Project Lead (m/f/x)</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>3</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>München (81671)</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://appliedai.jobs.personio.de/job/2846436</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Title: project lead</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Avelios Medical</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Senior Technical Program Manager (all genders) </t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>3</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/avelios-medical/6a0ad925-ab31-4125-a1a1-c4de7ce1b5a6</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Title: program manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>Airbus</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
         <is>
           <t>Projectmanager Industrialisierung (d/m/w)</t>
         </is>
       </c>
-      <c r="E19" t="n">
+      <c r="E22" t="n">
         <v>10</v>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>Augsburg Area</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Augsburg-Area/Projectmanager-Industrialisierung--d-m-w-_JR10430741-1</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>Direct role</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>Title: project manager</t>
         </is>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1028,45 +1028,45 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Nvidia Munich</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t>Senior Technical Program Manager - Nemotron</t>
         </is>
       </c>
-      <c r="E14" s="2" t="n">
+      <c r="E14" t="n">
         <v>6</v>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>Germany, Munich, Germany</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>https://nvidia.wd5.myworkdayjobs.com/NVIDIAExternalCareerSite/job/Germany-Munich/Senior-Technical-Program-Manager---Nemotron_JR2028331</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>Direct role</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>Title: program manager</t>
         </is>
@@ -1118,45 +1118,45 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>Agile Robots</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
         <is>
           <t>Project Coordinator – Site &amp; KPI (m/f/d) Fixed-term 18 months</t>
         </is>
       </c>
-      <c r="E16" s="2" t="n">
+      <c r="E16" t="n">
         <v>5</v>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>Munich, Bavaria, Germany</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>https://job-boards.eu.greenhouse.io/agilerobotsse/jobs/5013124101</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>Direct role</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>Title: project coordinator</t>
         </is>
@@ -1165,7 +1165,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>(Senior) Technical Program Manager (m/f/d)</t>
+          <t>Project Coordinator – New Tasks &amp; QC (m/f/d) Fixed-term 18 months</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/agilerobotsse/jobs/4996481101</t>
+          <t>https://job-boards.eu.greenhouse.io/agilerobotsse/jobs/5013108101</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1203,64 +1203,64 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
+          <t>Title: project coordinator</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Proxima Fusion</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Site Development Program Manager</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>3</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/proxima-fusion/db5bc40c-aa3e-4735-94e7-096a556dd55d</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
           <t>Title: program manager</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>Agile Robots</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>Project Coordinator – New Tasks &amp; QC (m/f/d) Fixed-term 18 months</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>Munich, Bavaria, Germany</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>https://job-boards.eu.greenhouse.io/agilerobotsse/jobs/5013108101</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>Direct role</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>Title: project coordinator</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Proxima Fusion</t>
+          <t>appliedAI</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Site Development Program Manager</t>
+          <t>AI Manager / Senior Project Lead (m/f/x)</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -1278,12 +1278,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>München (81671)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/proxima-fusion/db5bc40c-aa3e-4735-94e7-096a556dd55d</t>
+          <t>https://appliedai.jobs.personio.de/job/2846436</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1293,19 +1293,19 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Title: program manager</t>
+          <t>Title: project lead</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>appliedAI</t>
+          <t>Avelios Medical</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>AI Manager / Senior Project Lead (m/f/x)</t>
+          <t xml:space="preserve">Senior Technical Program Manager (all genders) </t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>München (81671)</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://appliedai.jobs.personio.de/job/2846436</t>
+          <t>https://jobs.ashbyhq.com/avelios-medical/6a0ad925-ab31-4125-a1a1-c4de7ce1b5a6</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1338,97 +1338,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Title: project lead</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Avelios Medical</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Senior Technical Program Manager (all genders) </t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>3</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://jobs.ashbyhq.com/avelios-medical/6a0ad925-ab31-4125-a1a1-c4de7ce1b5a6</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Direct role</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
           <t>Title: program manager</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Airbus</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Projectmanager Industrialisierung (d/m/w)</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>10</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Augsburg Area</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Augsburg-Area/Projectmanager-Industrialisierung--d-m-w-_JR10430741-1</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Direct role</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>Title: project manager</t>
         </is>
       </c>
     </row>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -493,87 +493,87 @@
       </c>
     </row>
     <row r="2">
-      <c r="B2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Blackwave</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Senior Technical Project Manager (m/w/d) Aerospace Composites</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Taufkirchen</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>https://blackwave.jobs.personio.de/job/2860163</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Title: project manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" t="inlineStr">
         <is>
           <t>SES</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
         <is>
           <t>Project Manager, IVV, Satellite Systems, IRIS2 Programme Office</t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="E3" t="n">
         <v>4</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Munich (Unterföhring), DE +1 more…</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>https://careers.ses.com/job/Munich-%28Unterf%C3%B6hring%29-Project-Manager%2C-IVV%2C-Satellite-Systems%2C-IRIS2-Programme-Office/1396651333/</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>Direct role</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>Title: project manager</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Celonis</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Senior Business Transformation &amp; Process Optimisation Consultant - Aviation/Logistics</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>10</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Munich, Germany</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/8015653003?gh_jid=8015653003</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Related role</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Responsibilities: delivery, stakeholders, transformation</t>
         </is>
       </c>
     </row>
@@ -595,7 +595,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Senior Management &amp; Technology Consultant - Aviation/Logistics</t>
+          <t>Senior Business Transformation &amp; Process Optimisation Consultant - Aviation/Logistics</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -608,7 +608,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/8015654003?gh_jid=8015654003</t>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/8015653003?gh_jid=8015653003</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -625,7 +625,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Senior Management &amp; Technology Consultant - Growth &amp; Scale Accounts</t>
+          <t>Senior Management &amp; Technology Consultant - Aviation/Logistics</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -653,7 +653,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/8026730003?gh_jid=8026730003</t>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/8015654003?gh_jid=8015654003</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -663,14 +663,14 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Responsibilities: delivery, governance, stakeholders, transformation</t>
+          <t>Responsibilities: delivery, stakeholders, transformation</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Senior Process Intelligence &amp; Supply Chain Transformation Consultant - Aviation/Logistics</t>
+          <t>Senior Management &amp; Technology Consultant - Growth &amp; Scale Accounts</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -698,7 +698,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/8015655003?gh_jid=8015655003</t>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/8026730003?gh_jid=8026730003</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -708,14 +708,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Responsibilities: delivery, stakeholders, transformation</t>
+          <t>Responsibilities: delivery, governance, stakeholders, transformation</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Senior Process Optimisation Consultant - Growth &amp; Scale Accounts</t>
+          <t>Senior Process Intelligence &amp; Supply Chain Transformation Consultant - Aviation/Logistics</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -743,7 +743,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/8026747003?gh_jid=8026747003</t>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/8015655003?gh_jid=8015655003</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -753,19 +753,19 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Responsibilities: delivery, governance, stakeholders, transformation</t>
+          <t>Responsibilities: delivery, stakeholders, transformation</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Helsing</t>
+          <t>Celonis</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -775,87 +775,87 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>(Senior) Programme Manager - Military Exercises</t>
+          <t>Senior Process Optimisation Consultant - Growth &amp; Scale Accounts</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>Munich, Germany</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://helsing.ai/jobs/5004102101?gh_jid=5004102101</t>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/8026747003?gh_jid=8026747003</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
+          <t>Related role</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Responsibilities: delivery, governance, stakeholders, transformation</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Airbus</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>SATCOMBw Projektleiter PMS Software (m/w/d)</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>München Area</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Mnchen-Area/SATCOMBw-Projektleiter-PMS-Software--m-w-d-_JR10448226-1</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
           <t>Direct role</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Title: programme manager</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Celonis</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Senior Digital Transformation &amp; Process Optimisation Consultant - CPG/Retail</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>8</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Munich, Germany</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/8016417003?gh_jid=8016417003</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Related role</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Responsibilities: delivery, stakeholders, transformation</t>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Title: projektleiter</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Celonis</t>
+          <t>Helsing</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Senior Management &amp; Technology Consultant - CPG/Retail - CPG/Retail</t>
+          <t>(Senior) Programme Manager - Military Exercises</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -873,22 +873,22 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Munich, Germany</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/8016657003?gh_jid=8016657003</t>
+          <t>https://helsing.ai/jobs/5004102101?gh_jid=5004102101</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Related role</t>
+          <t>Direct role</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Responsibilities: delivery, stakeholders, transformation</t>
+          <t>Title: programme manager</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Senior Process Intelligence &amp; Supply Chain Transformation Consultant - CPG/Retail</t>
+          <t>Senior Digital Transformation &amp; Process Optimisation Consultant - CPG/Retail</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -923,7 +923,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/8016658003?gh_jid=8016658003</t>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/8016417003?gh_jid=8016417003</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -940,12 +940,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ARX Robotics</t>
+          <t>Celonis</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -955,42 +955,42 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Project Manager - Infrastructure &amp; Expansion</t>
+          <t>Senior Management &amp; Technology Consultant - CPG/Retail - CPG/Retail</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>Munich, Germany</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/arxroboticsgmbh/jobs/5005798101</t>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/8016657003?gh_jid=8016657003</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Direct role</t>
+          <t>Related role</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Title: project manager</t>
+          <t>Responsibilities: delivery, stakeholders, transformation</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Helsing</t>
+          <t>Celonis</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1000,132 +1000,132 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Senior Programme Manager - International Business Development Air</t>
+          <t>Senior Process Intelligence &amp; Supply Chain Transformation Consultant - CPG/Retail</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>Munich, Germany</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://helsing.ai/jobs/5001597101?gh_jid=5001597101</t>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/8016658003?gh_jid=8016658003</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
+          <t>Related role</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Responsibilities: delivery, stakeholders, transformation</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Agile Robots</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Technical Project Manager (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Bavaria, Germany</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/agilerobotsse/jobs/5015409101</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
           <t>Direct role</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Title: programme manager</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Nvidia Munich</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Senior Technical Program Manager - Nemotron</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>6</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Germany, Munich, Germany</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://nvidia.wd5.myworkdayjobs.com/NVIDIAExternalCareerSite/job/Germany-Munich/Senior-Technical-Program-Manager---Nemotron_JR2028331</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Direct role</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Title: program manager</t>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>Title: project manager</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Agile Robots</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Senior Project Manager (all genders)</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>5</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Munich, Bavaria, Germany</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://job-boards.eu.greenhouse.io/agilerobotsse/jobs/4990647101</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Direct role</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Title: project manager</t>
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Proxima Fusion</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Risk and Change Manager - Alpha Delivery PMO </t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/proxima-fusion/a797ff9e-a28f-4630-91d1-5e585edc1cbb</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Related role</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>Responsibilities: governance, transformation</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Agile Robots</t>
+          <t>ARX Robotics</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1135,20 +1135,20 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Project Coordinator – Site &amp; KPI (m/f/d) Fixed-term 18 months</t>
+          <t>Project Manager - Infrastructure &amp; Expansion</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Munich, Bavaria, Germany</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/agilerobotsse/jobs/5013124101</t>
+          <t>https://job-boards.eu.greenhouse.io/arxroboticsgmbh/jobs/5005798101</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1158,19 +1158,19 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Title: project coordinator</t>
+          <t>Title: project manager</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Agile Robots</t>
+          <t>Helsing</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1180,20 +1180,20 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Project Coordinator – New Tasks &amp; QC (m/f/d) Fixed-term 18 months</t>
+          <t>Senior Programme Manager - International Business Development Air</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Munich, Bavaria, Germany</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/agilerobotsse/jobs/5013108101</t>
+          <t>https://helsing.ai/jobs/5001597101?gh_jid=5001597101</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1203,19 +1203,19 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Title: project coordinator</t>
+          <t>Title: programme manager</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Proxima Fusion</t>
+          <t>Nvidia Munich</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1225,20 +1225,20 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Site Development Program Manager</t>
+          <t>Senior Technical Program Manager - Nemotron</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>Germany, Munich, Germany</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/proxima-fusion/db5bc40c-aa3e-4735-94e7-096a556dd55d</t>
+          <t>https://nvidia.wd5.myworkdayjobs.com/NVIDIAExternalCareerSite/job/Germany-Munich/Senior-Technical-Program-Manager---Nemotron_JR2028331</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1255,12 +1255,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>appliedAI</t>
+          <t>Agile Robots</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1270,20 +1270,20 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>AI Manager / Senior Project Lead (m/f/x)</t>
+          <t>Senior Project Manager (all genders)</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>München (81671)</t>
+          <t>Munich, Bavaria, Germany</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://appliedai.jobs.personio.de/job/2846436</t>
+          <t>https://job-boards.eu.greenhouse.io/agilerobotsse/jobs/4990647101</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1293,50 +1293,230 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Title: project lead</t>
+          <t>Title: project manager</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Agile Robots</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Project Coordinator – Site &amp; KPI (m/f/d) Fixed-term 18 months</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>5</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Munich, Bavaria, Germany</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/agilerobotsse/jobs/5013124101</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Title: project coordinator</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Agile Robots</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Project Coordinator – New Tasks &amp; QC (m/f/d) Fixed-term 18 months</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>4</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Munich, Bavaria, Germany</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/agilerobotsse/jobs/5013108101</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Title: project coordinator</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Proxima Fusion</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Site Development Program Manager</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>3</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/proxima-fusion/db5bc40c-aa3e-4735-94e7-096a556dd55d</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Title: program manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>appliedAI</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>AI Manager / Senior Project Lead (m/f/x)</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>3</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>München (81671)</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://appliedai.jobs.personio.de/job/2846436</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Title: project lead</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>Avelios Medical</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
         <is>
           <t xml:space="preserve">Senior Technical Program Manager (all genders) </t>
         </is>
       </c>
-      <c r="E20" t="n">
+      <c r="E24" t="n">
         <v>3</v>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/avelios-medical/6a0ad925-ab31-4125-a1a1-c4de7ce1b5a6</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>Direct role</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>Title: program manager</t>
         </is>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -493,45 +493,45 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Blackwave</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
         <is>
           <t>Senior Technical Project Manager (m/w/d) Aerospace Composites</t>
         </is>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" t="n">
         <v>10</v>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Taufkirchen</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>https://blackwave.jobs.personio.de/job/2860163</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>Direct role</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>Title: project manager</t>
         </is>
@@ -803,45 +803,45 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Airbus</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
         <is>
           <t>SATCOMBw Projektleiter PMS Software (m/w/d)</t>
         </is>
       </c>
-      <c r="E9" s="2" t="n">
+      <c r="E9" t="n">
         <v>10</v>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>München Area</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Mnchen-Area/SATCOMBw-Projektleiter-PMS-Software--m-w-d-_JR10448226-1</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>Direct role</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>Title: projektleiter</t>
         </is>
@@ -1028,90 +1028,90 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Agile Robots</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t>Technical Project Manager (m/f/d)</t>
         </is>
       </c>
-      <c r="E14" s="2" t="n">
+      <c r="E14" t="n">
         <v>8</v>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>Munich, Bavaria, Germany</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>https://job-boards.eu.greenhouse.io/agilerobotsse/jobs/5015409101</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>Direct role</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>Title: project manager</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>Proxima Fusion</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
         <is>
           <t xml:space="preserve">Risk and Change Manager - Alpha Delivery PMO </t>
         </is>
       </c>
-      <c r="E15" s="2" t="n">
+      <c r="E15" t="n">
         <v>7</v>
       </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/proxima-fusion/a797ff9e-a28f-4630-91d1-5e585edc1cbb</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>Related role</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>Responsibilities: governance, transformation</t>
         </is>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -580,7 +580,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -595,7 +595,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Senior Business Transformation &amp; Process Optimisation Consultant - Aviation/Logistics</t>
+          <t>Senior Management &amp; Technology Consultant - Growth &amp; Scale Accounts</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -608,7 +608,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/8015653003?gh_jid=8015653003</t>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/8026730003?gh_jid=8026730003</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -618,14 +618,14 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Responsibilities: delivery, stakeholders, transformation</t>
+          <t>Responsibilities: delivery, governance, stakeholders, transformation</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Senior Management &amp; Technology Consultant - Aviation/Logistics</t>
+          <t>Senior Process Optimisation Consultant - Growth &amp; Scale Accounts</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -653,7 +653,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/8015654003?gh_jid=8015654003</t>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/8026747003?gh_jid=8026747003</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -663,19 +663,19 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Responsibilities: delivery, stakeholders, transformation</t>
+          <t>Responsibilities: delivery, governance, stakeholders, transformation</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Celonis</t>
+          <t>Airbus</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Senior Management &amp; Technology Consultant - Growth &amp; Scale Accounts</t>
+          <t>SATCOMBw Projektleiter PMS Software (m/w/d)</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -693,34 +693,34 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Munich, Germany</t>
+          <t>München Area</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/8026730003?gh_jid=8026730003</t>
+          <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Mnchen-Area/SATCOMBw-Projektleiter-PMS-Software--m-w-d-_JR10448226-1</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Related role</t>
+          <t>Direct role</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Responsibilities: delivery, governance, stakeholders, transformation</t>
+          <t>Title: projektleiter</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Celonis</t>
+          <t>Helsing</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -730,37 +730,37 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Senior Process Intelligence &amp; Supply Chain Transformation Consultant - Aviation/Logistics</t>
+          <t>(Senior) Programme Manager - Military Exercises</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Munich, Germany</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/8015655003?gh_jid=8015655003</t>
+          <t>https://helsing.ai/jobs/5004102101?gh_jid=5004102101</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Related role</t>
+          <t>Direct role</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Responsibilities: delivery, stakeholders, transformation</t>
+          <t>Title: programme manager</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -775,11 +775,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Senior Process Optimisation Consultant - Growth &amp; Scale Accounts</t>
+          <t>Senior Digital Transformation &amp; Process Optimisation Consultant - CPG/Retail</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/8026747003?gh_jid=8026747003</t>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/8016417003?gh_jid=8016417003</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -798,19 +798,19 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Responsibilities: delivery, governance, stakeholders, transformation</t>
+          <t>Responsibilities: delivery, stakeholders, transformation</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Airbus</t>
+          <t>Celonis</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -820,42 +820,42 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>SATCOMBw Projektleiter PMS Software (m/w/d)</t>
+          <t>Senior Management &amp; Technology Consultant - CPG/Retail - CPG/Retail</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>München Area</t>
+          <t>Munich, Germany</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Mnchen-Area/SATCOMBw-Projektleiter-PMS-Software--m-w-d-_JR10448226-1</t>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/8016657003?gh_jid=8016657003</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Direct role</t>
+          <t>Related role</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Title: projektleiter</t>
+          <t>Responsibilities: delivery, stakeholders, transformation</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Helsing</t>
+          <t>Celonis</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>(Senior) Programme Manager - Military Exercises</t>
+          <t>Senior Process Intelligence &amp; Supply Chain Transformation Consultant - CPG/Retail</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -873,34 +873,34 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>Munich, Germany</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://helsing.ai/jobs/5004102101?gh_jid=5004102101</t>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/8016658003?gh_jid=8016658003</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Direct role</t>
+          <t>Related role</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Title: programme manager</t>
+          <t>Responsibilities: delivery, stakeholders, transformation</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Celonis</t>
+          <t>Agile Robots</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -910,7 +910,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Senior Digital Transformation &amp; Process Optimisation Consultant - CPG/Retail</t>
+          <t>Technical Project Manager (m/f/d)</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -918,34 +918,34 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Munich, Germany</t>
+          <t>Munich, Bavaria, Germany</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/8016417003?gh_jid=8016417003</t>
+          <t>https://job-boards.eu.greenhouse.io/agilerobotsse/jobs/5015409101</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Related role</t>
+          <t>Direct role</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Responsibilities: delivery, stakeholders, transformation</t>
+          <t>Title: project manager</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Celonis</t>
+          <t>Proxima Fusion</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -955,20 +955,20 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Senior Management &amp; Technology Consultant - CPG/Retail - CPG/Retail</t>
+          <t xml:space="preserve">Risk and Change Manager - Alpha Delivery PMO </t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Munich, Germany</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/8016657003?gh_jid=8016657003</t>
+          <t>https://jobs.ashbyhq.com/proxima-fusion/a797ff9e-a28f-4630-91d1-5e585edc1cbb</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -978,19 +978,19 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Responsibilities: delivery, stakeholders, transformation</t>
+          <t>Responsibilities: governance, transformation</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Celonis</t>
+          <t>ARX Robotics</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1000,42 +1000,42 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Senior Process Intelligence &amp; Supply Chain Transformation Consultant - CPG/Retail</t>
+          <t>Project Manager - Infrastructure &amp; Expansion</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Munich, Germany</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/8016658003?gh_jid=8016658003</t>
+          <t>https://job-boards.eu.greenhouse.io/arxroboticsgmbh/jobs/5005798101</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Related role</t>
+          <t>Direct role</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Responsibilities: delivery, stakeholders, transformation</t>
+          <t>Title: project manager</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Agile Robots</t>
+          <t>Helsing</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1045,20 +1045,20 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Technical Project Manager (m/f/d)</t>
+          <t>Senior Programme Manager - International Business Development Air</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Munich, Bavaria, Germany</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/agilerobotsse/jobs/5015409101</t>
+          <t>https://helsing.ai/jobs/5001597101?gh_jid=5001597101</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1068,19 +1068,19 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Title: project manager</t>
+          <t>Title: programme manager</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Proxima Fusion</t>
+          <t>Nvidia Munich</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1090,42 +1090,42 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Risk and Change Manager - Alpha Delivery PMO </t>
+          <t>Senior Technical Program Manager - Nemotron</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>Germany, Munich, Germany</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/proxima-fusion/a797ff9e-a28f-4630-91d1-5e585edc1cbb</t>
+          <t>https://nvidia.wd5.myworkdayjobs.com/NVIDIAExternalCareerSite/job/Germany-Munich/Senior-Technical-Program-Manager---Nemotron_JR2028331</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Related role</t>
+          <t>Direct role</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Responsibilities: governance, transformation</t>
+          <t>Title: program manager</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ARX Robotics</t>
+          <t>Agile Robots</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1135,20 +1135,20 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Project Manager - Infrastructure &amp; Expansion</t>
+          <t>Senior Project Manager (all genders)</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>Munich, Bavaria, Germany</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/arxroboticsgmbh/jobs/5005798101</t>
+          <t>https://job-boards.eu.greenhouse.io/agilerobotsse/jobs/4990647101</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1165,12 +1165,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Helsing</t>
+          <t>Agile Robots</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1180,20 +1180,20 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Senior Programme Manager - International Business Development Air</t>
+          <t>Project Coordinator – Site &amp; KPI (m/f/d) Fixed-term 18 months</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>Munich, Bavaria, Germany</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://helsing.ai/jobs/5001597101?gh_jid=5001597101</t>
+          <t>https://job-boards.eu.greenhouse.io/agilerobotsse/jobs/5013124101</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Title: programme manager</t>
+          <t>Title: project coordinator</t>
         </is>
       </c>
     </row>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Nvidia Munich</t>
+          <t>Agile Robots</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1225,20 +1225,20 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Senior Technical Program Manager - Nemotron</t>
+          <t>Project Coordinator – New Tasks &amp; QC (m/f/d) Fixed-term 18 months</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Germany, Munich, Germany</t>
+          <t>Munich, Bavaria, Germany</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://nvidia.wd5.myworkdayjobs.com/NVIDIAExternalCareerSite/job/Germany-Munich/Senior-Technical-Program-Manager---Nemotron_JR2028331</t>
+          <t>https://job-boards.eu.greenhouse.io/agilerobotsse/jobs/5013108101</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1248,19 +1248,19 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Title: program manager</t>
+          <t>Title: project coordinator</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Agile Robots</t>
+          <t>Proxima Fusion</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1270,20 +1270,20 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Senior Project Manager (all genders)</t>
+          <t>Site Development Program Manager</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Munich, Bavaria, Germany</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/agilerobotsse/jobs/4990647101</t>
+          <t>https://jobs.ashbyhq.com/proxima-fusion/db5bc40c-aa3e-4735-94e7-096a556dd55d</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1293,19 +1293,19 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Title: project manager</t>
+          <t>Title: program manager</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Agile Robots</t>
+          <t>appliedAI</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1315,20 +1315,20 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Project Coordinator – Site &amp; KPI (m/f/d) Fixed-term 18 months</t>
+          <t>AI Manager / Senior Project Lead (m/f/x)</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Munich, Bavaria, Germany</t>
+          <t>München (81671)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/agilerobotsse/jobs/5013124101</t>
+          <t>https://appliedai.jobs.personio.de/job/2846436</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1338,187 +1338,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Title: project coordinator</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Agile Robots</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Project Coordinator – New Tasks &amp; QC (m/f/d) Fixed-term 18 months</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>4</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Munich, Bavaria, Germany</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://job-boards.eu.greenhouse.io/agilerobotsse/jobs/5013108101</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Direct role</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>Title: project coordinator</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Proxima Fusion</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Site Development Program Manager</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>3</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://jobs.ashbyhq.com/proxima-fusion/db5bc40c-aa3e-4735-94e7-096a556dd55d</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Direct role</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>Title: program manager</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>appliedAI</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>AI Manager / Senior Project Lead (m/f/x)</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>3</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>München (81671)</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://appliedai.jobs.personio.de/job/2846436</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Direct role</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
           <t>Title: project lead</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Avelios Medical</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Senior Technical Program Manager (all genders) </t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>3</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://jobs.ashbyhq.com/avelios-medical/6a0ad925-ab31-4125-a1a1-c4de7ce1b5a6</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Direct role</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>Title: program manager</t>
         </is>
       </c>
     </row>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -713,59 +713,59 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Helsing</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>(Senior) Programme Manager - Military Exercises</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>8</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://helsing.ai/jobs/5004102101?gh_jid=5004102101</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Airbus</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>VIE (d/f/m) - HR Project Manager - H/F</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>München Area</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Mnchen-Area/VIE--d-f-m----HR-Project-Manager---H-F_JR10451106</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Direct role</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Title: programme manager</t>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Title: project manager</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Celonis</t>
+          <t>Helsing</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Senior Digital Transformation &amp; Process Optimisation Consultant - CPG/Retail</t>
+          <t>(Senior) Programme Manager - Military Exercises</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -783,22 +783,22 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Munich, Germany</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/8016417003?gh_jid=8016417003</t>
+          <t>https://helsing.ai/jobs/5004102101?gh_jid=5004102101</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Related role</t>
+          <t>Direct role</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Responsibilities: delivery, stakeholders, transformation</t>
+          <t>Title: programme manager</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Senior Management &amp; Technology Consultant - CPG/Retail - CPG/Retail</t>
+          <t>Senior Digital Transformation &amp; Process Optimisation Consultant - CPG/Retail</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -833,7 +833,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/8016657003?gh_jid=8016657003</t>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/8016417003?gh_jid=8016417003</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Senior Process Intelligence &amp; Supply Chain Transformation Consultant - CPG/Retail</t>
+          <t>Senior Management &amp; Technology Consultant - CPG/Retail - CPG/Retail</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -878,7 +878,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/8016658003?gh_jid=8016658003</t>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/8016657003?gh_jid=8016657003</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -895,12 +895,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Agile Robots</t>
+          <t>Celonis</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -910,7 +910,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Technical Project Manager (m/f/d)</t>
+          <t>Senior Process Intelligence &amp; Supply Chain Transformation Consultant - CPG/Retail</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -918,22 +918,22 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Munich, Bavaria, Germany</t>
+          <t>Munich, Germany</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/agilerobotsse/jobs/5015409101</t>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/8016658003?gh_jid=8016658003</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Direct role</t>
+          <t>Related role</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Title: project manager</t>
+          <t>Responsibilities: delivery, stakeholders, transformation</t>
         </is>
       </c>
     </row>
@@ -945,7 +945,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Proxima Fusion</t>
+          <t>Agile Robots</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -955,42 +955,42 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Risk and Change Manager - Alpha Delivery PMO </t>
+          <t>Technical Project Manager (m/f/d)</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>Munich, Bavaria, Germany</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/proxima-fusion/a797ff9e-a28f-4630-91d1-5e585edc1cbb</t>
+          <t>https://job-boards.eu.greenhouse.io/agilerobotsse/jobs/5015409101</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Related role</t>
+          <t>Direct role</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Responsibilities: governance, transformation</t>
+          <t>Title: project manager</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ARX Robotics</t>
+          <t>Proxima Fusion</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1000,11 +1000,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Project Manager - Infrastructure &amp; Expansion</t>
+          <t xml:space="preserve">Risk and Change Manager - Alpha Delivery PMO </t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1013,29 +1013,29 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/arxroboticsgmbh/jobs/5005798101</t>
+          <t>https://jobs.ashbyhq.com/proxima-fusion/a797ff9e-a28f-4630-91d1-5e585edc1cbb</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Direct role</t>
+          <t>Related role</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Title: project manager</t>
+          <t>Responsibilities: governance, transformation</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Helsing</t>
+          <t>ARX Robotics</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1045,7 +1045,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Senior Programme Manager - International Business Development Air</t>
+          <t>Project Manager - Infrastructure &amp; Expansion</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://helsing.ai/jobs/5001597101?gh_jid=5001597101</t>
+          <t>https://job-boards.eu.greenhouse.io/arxroboticsgmbh/jobs/5005798101</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1068,19 +1068,19 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Title: programme manager</t>
+          <t>Title: project manager</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Nvidia Munich</t>
+          <t>Helsing</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Senior Technical Program Manager - Nemotron</t>
+          <t>Senior Programme Manager - International Business Development Air</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Germany, Munich, Germany</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://nvidia.wd5.myworkdayjobs.com/NVIDIAExternalCareerSite/job/Germany-Munich/Senior-Technical-Program-Manager---Nemotron_JR2028331</t>
+          <t>https://helsing.ai/jobs/5001597101?gh_jid=5001597101</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1113,19 +1113,19 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Title: program manager</t>
+          <t>Title: programme manager</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Agile Robots</t>
+          <t>Nvidia Munich</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1135,20 +1135,20 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Senior Project Manager (all genders)</t>
+          <t>Senior Technical Program Manager - Nemotron</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Munich, Bavaria, Germany</t>
+          <t>Germany, Munich, Germany</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/agilerobotsse/jobs/4990647101</t>
+          <t>https://nvidia.wd5.myworkdayjobs.com/NVIDIAExternalCareerSite/job/Germany-Munich/Senior-Technical-Program-Manager---Nemotron_JR2028331</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1158,14 +1158,14 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Title: project manager</t>
+          <t>Title: program manager</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Project Coordinator – Site &amp; KPI (m/f/d) Fixed-term 18 months</t>
+          <t>Senior Project Manager (all genders)</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/agilerobotsse/jobs/5013124101</t>
+          <t>https://job-boards.eu.greenhouse.io/agilerobotsse/jobs/4990647101</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Title: project coordinator</t>
+          <t>Title: project manager</t>
         </is>
       </c>
     </row>
@@ -1225,11 +1225,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Project Coordinator – New Tasks &amp; QC (m/f/d) Fixed-term 18 months</t>
+          <t>Project Coordinator – Site &amp; KPI (m/f/d) Fixed-term 18 months</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/agilerobotsse/jobs/5013108101</t>
+          <t>https://job-boards.eu.greenhouse.io/agilerobotsse/jobs/5013124101</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1255,12 +1255,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Proxima Fusion</t>
+          <t>Agile Robots</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1270,20 +1270,20 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Site Development Program Manager</t>
+          <t>Project Coordinator – New Tasks &amp; QC (m/f/d) Fixed-term 18 months</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>Munich, Bavaria, Germany</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/proxima-fusion/db5bc40c-aa3e-4735-94e7-096a556dd55d</t>
+          <t>https://job-boards.eu.greenhouse.io/agilerobotsse/jobs/5013108101</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1293,19 +1293,19 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Title: program manager</t>
+          <t>Title: project coordinator</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>appliedAI</t>
+          <t>Proxima Fusion</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>AI Manager / Senior Project Lead (m/f/x)</t>
+          <t>Site Development Program Manager</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -1323,20 +1323,65 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/proxima-fusion/db5bc40c-aa3e-4735-94e7-096a556dd55d</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Title: program manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>appliedAI</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>AI Manager / Senior Project Lead (m/f/x)</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>3</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
           <t>München (81671)</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>https://appliedai.jobs.personio.de/job/2846436</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>Direct role</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>Title: project lead</t>
         </is>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -713,45 +713,45 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Airbus</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
         <is>
           <t>VIE (d/f/m) - HR Project Manager - H/F</t>
         </is>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="E7" t="n">
         <v>10</v>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>München Area</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Mnchen-Area/VIE--d-f-m----HR-Project-Manager---H-F_JR10451106</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>Direct role</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
         <is>
           <t>Title: project manager</t>
         </is>
@@ -805,12 +805,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Celonis</t>
+          <t>Agile Robots</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Senior Digital Transformation &amp; Process Optimisation Consultant - CPG/Retail</t>
+          <t>Technical Project Manager (m/f/d)</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -828,34 +828,34 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Munich, Germany</t>
+          <t>Munich, Bavaria, Germany</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/8016417003?gh_jid=8016417003</t>
+          <t>https://job-boards.eu.greenhouse.io/agilerobotsse/jobs/5015409101</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Related role</t>
+          <t>Direct role</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Responsibilities: delivery, stakeholders, transformation</t>
+          <t>Title: project manager</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Celonis</t>
+          <t>Proxima Fusion</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -865,20 +865,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Senior Management &amp; Technology Consultant - CPG/Retail - CPG/Retail</t>
+          <t xml:space="preserve">Risk and Change Manager - Alpha Delivery PMO </t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Munich, Germany</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/8016657003?gh_jid=8016657003</t>
+          <t>https://jobs.ashbyhq.com/proxima-fusion/a797ff9e-a28f-4630-91d1-5e585edc1cbb</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -888,19 +888,19 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Responsibilities: delivery, stakeholders, transformation</t>
+          <t>Responsibilities: governance, transformation</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Celonis</t>
+          <t>ARX Robotics</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -910,42 +910,42 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Senior Process Intelligence &amp; Supply Chain Transformation Consultant - CPG/Retail</t>
+          <t>Project Manager - Infrastructure &amp; Expansion</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Munich, Germany</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/8016658003?gh_jid=8016658003</t>
+          <t>https://job-boards.eu.greenhouse.io/arxroboticsgmbh/jobs/5005798101</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Related role</t>
+          <t>Direct role</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Responsibilities: delivery, stakeholders, transformation</t>
+          <t>Title: project manager</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Agile Robots</t>
+          <t>Helsing</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -955,20 +955,20 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Technical Project Manager (m/f/d)</t>
+          <t>Senior Programme Manager - International Business Development Air</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Munich, Bavaria, Germany</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/agilerobotsse/jobs/5015409101</t>
+          <t>https://helsing.ai/jobs/5001597101?gh_jid=5001597101</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -978,19 +978,19 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Title: project manager</t>
+          <t>Title: programme manager</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Proxima Fusion</t>
+          <t>Nvidia Munich</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1000,42 +1000,42 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Risk and Change Manager - Alpha Delivery PMO </t>
+          <t>Senior Technical Program Manager - Nemotron</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>Germany, Munich, Germany</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/proxima-fusion/a797ff9e-a28f-4630-91d1-5e585edc1cbb</t>
+          <t>https://nvidia.wd5.myworkdayjobs.com/NVIDIAExternalCareerSite/job/Germany-Munich/Senior-Technical-Program-Manager---Nemotron_JR2028331</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Related role</t>
+          <t>Direct role</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Responsibilities: governance, transformation</t>
+          <t>Title: program manager</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ARX Robotics</t>
+          <t>Agile Robots</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1045,20 +1045,20 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Project Manager - Infrastructure &amp; Expansion</t>
+          <t>Senior Project Manager (all genders)</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>Munich, Bavaria, Germany</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/arxroboticsgmbh/jobs/5005798101</t>
+          <t>https://job-boards.eu.greenhouse.io/agilerobotsse/jobs/4990647101</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1075,12 +1075,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Helsing</t>
+          <t>Agile Robots</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1090,20 +1090,20 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Senior Programme Manager - International Business Development Air</t>
+          <t>Project Coordinator – Site &amp; KPI (m/f/d) Fixed-term 18 months</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>Munich, Bavaria, Germany</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://helsing.ai/jobs/5001597101?gh_jid=5001597101</t>
+          <t>https://job-boards.eu.greenhouse.io/agilerobotsse/jobs/5013124101</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Title: programme manager</t>
+          <t>Title: project coordinator</t>
         </is>
       </c>
     </row>
@@ -1125,7 +1125,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Nvidia Munich</t>
+          <t>Agile Robots</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1135,20 +1135,20 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Senior Technical Program Manager - Nemotron</t>
+          <t>Project Coordinator – New Tasks &amp; QC (m/f/d) Fixed-term 18 months</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Germany, Munich, Germany</t>
+          <t>Munich, Bavaria, Germany</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://nvidia.wd5.myworkdayjobs.com/NVIDIAExternalCareerSite/job/Germany-Munich/Senior-Technical-Program-Manager---Nemotron_JR2028331</t>
+          <t>https://job-boards.eu.greenhouse.io/agilerobotsse/jobs/5013108101</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1158,19 +1158,19 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Title: program manager</t>
+          <t>Title: project coordinator</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Agile Robots</t>
+          <t>Proxima Fusion</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1180,20 +1180,20 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Senior Project Manager (all genders)</t>
+          <t>Site Development Program Manager</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Munich, Bavaria, Germany</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/agilerobotsse/jobs/4990647101</t>
+          <t>https://jobs.ashbyhq.com/proxima-fusion/db5bc40c-aa3e-4735-94e7-096a556dd55d</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1203,19 +1203,19 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Title: project manager</t>
+          <t>Title: program manager</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Agile Robots</t>
+          <t>appliedAI</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1225,20 +1225,20 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Project Coordinator – Site &amp; KPI (m/f/d) Fixed-term 18 months</t>
+          <t>AI Manager / Senior Project Lead (m/f/x)</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Munich, Bavaria, Germany</t>
+          <t>München (81671)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/agilerobotsse/jobs/5013124101</t>
+          <t>https://appliedai.jobs.personio.de/job/2846436</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1247,141 +1247,6 @@
         </is>
       </c>
       <c r="I18" t="inlineStr">
-        <is>
-          <t>Title: project coordinator</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Agile Robots</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Project Coordinator – New Tasks &amp; QC (m/f/d) Fixed-term 18 months</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>4</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Munich, Bavaria, Germany</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://job-boards.eu.greenhouse.io/agilerobotsse/jobs/5013108101</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Direct role</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>Title: project coordinator</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Proxima Fusion</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Site Development Program Manager</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>3</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://jobs.ashbyhq.com/proxima-fusion/db5bc40c-aa3e-4735-94e7-096a556dd55d</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Direct role</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>Title: program manager</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>appliedAI</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>AI Manager / Senior Project Lead (m/f/x)</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>3</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>München (81671)</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://appliedai.jobs.personio.de/job/2846436</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Direct role</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
         <is>
           <t>Title: project lead</t>
         </is>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -893,59 +893,59 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>ARX Robotics</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Project Manager - Infrastructure &amp; Expansion</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>6</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://job-boards.eu.greenhouse.io/arxroboticsgmbh/jobs/5005798101</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Direct role</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Title: project manager</t>
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Orbem</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Staff Technical Program Manager (f/m/d)</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/orbem/4d8b273c-27f1-44d5-9072-0c003b7f2103</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>Title: program manager</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Helsing</t>
+          <t>ARX Robotics</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Senior Programme Manager - International Business Development Air</t>
+          <t>Project Manager - Infrastructure &amp; Expansion</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -968,7 +968,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://helsing.ai/jobs/5001597101?gh_jid=5001597101</t>
+          <t>https://job-boards.eu.greenhouse.io/arxroboticsgmbh/jobs/5005798101</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -978,19 +978,19 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Title: programme manager</t>
+          <t>Title: project manager</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Nvidia Munich</t>
+          <t>Helsing</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1000,7 +1000,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Senior Technical Program Manager - Nemotron</t>
+          <t>Senior Programme Manager - International Business Development Air</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Germany, Munich, Germany</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://nvidia.wd5.myworkdayjobs.com/NVIDIAExternalCareerSite/job/Germany-Munich/Senior-Technical-Program-Manager---Nemotron_JR2028331</t>
+          <t>https://helsing.ai/jobs/5001597101?gh_jid=5001597101</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1023,19 +1023,19 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Title: program manager</t>
+          <t>Title: programme manager</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Agile Robots</t>
+          <t>Nvidia Munich</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1045,20 +1045,20 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Senior Project Manager (all genders)</t>
+          <t>Senior Technical Program Manager - Nemotron</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Munich, Bavaria, Germany</t>
+          <t>Germany, Munich, Germany</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/agilerobotsse/jobs/4990647101</t>
+          <t>https://nvidia.wd5.myworkdayjobs.com/NVIDIAExternalCareerSite/job/Germany-Munich/Senior-Technical-Program-Manager---Nemotron_JR2028331</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1068,14 +1068,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Title: project manager</t>
+          <t>Title: program manager</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Project Coordinator – Site &amp; KPI (m/f/d) Fixed-term 18 months</t>
+          <t>Senior Project Manager (all genders)</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/agilerobotsse/jobs/5013124101</t>
+          <t>https://job-boards.eu.greenhouse.io/agilerobotsse/jobs/4990647101</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Title: project coordinator</t>
+          <t>Title: project manager</t>
         </is>
       </c>
     </row>
@@ -1135,11 +1135,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Project Coordinator – New Tasks &amp; QC (m/f/d) Fixed-term 18 months</t>
+          <t>Project Coordinator – Site &amp; KPI (m/f/d) Fixed-term 18 months</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/agilerobotsse/jobs/5013108101</t>
+          <t>https://job-boards.eu.greenhouse.io/agilerobotsse/jobs/5013124101</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1165,12 +1165,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Proxima Fusion</t>
+          <t>Agile Robots</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1180,20 +1180,20 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Site Development Program Manager</t>
+          <t>Project Coordinator – New Tasks &amp; QC (m/f/d) Fixed-term 18 months</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>Munich, Bavaria, Germany</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/proxima-fusion/db5bc40c-aa3e-4735-94e7-096a556dd55d</t>
+          <t>https://job-boards.eu.greenhouse.io/agilerobotsse/jobs/5013108101</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1203,19 +1203,19 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Title: program manager</t>
+          <t>Title: project coordinator</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>appliedAI</t>
+          <t>Proxima Fusion</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>AI Manager / Senior Project Lead (m/f/x)</t>
+          <t>Site Development Program Manager</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -1233,20 +1233,65 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/proxima-fusion/db5bc40c-aa3e-4735-94e7-096a556dd55d</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Title: program manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>appliedAI</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>AI Manager / Senior Project Lead (m/f/x)</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>3</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
           <t>München (81671)</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>https://appliedai.jobs.personio.de/job/2846436</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Direct role</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
         <is>
           <t>Title: project lead</t>
         </is>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -893,45 +893,45 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>2026-10-30</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Orbem</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
         <is>
           <t>Staff Technical Program Manager (f/m/d)</t>
         </is>
       </c>
-      <c r="E11" s="2" t="n">
+      <c r="E11" t="n">
         <v>7</v>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/orbem/4d8b273c-27f1-44d5-9072-0c003b7f2103</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>Direct role</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
         <is>
           <t>Title: program manager</t>
         </is>
@@ -1075,7 +1075,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Senior Project Manager (all genders)</t>
+          <t>Project Coordinator – Site &amp; KPI (m/f/d) Fixed-term 18 months</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/agilerobotsse/jobs/4990647101</t>
+          <t>https://job-boards.eu.greenhouse.io/agilerobotsse/jobs/5013124101</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Title: project manager</t>
+          <t>Title: project coordinator</t>
         </is>
       </c>
     </row>
@@ -1135,11 +1135,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Project Coordinator – Site &amp; KPI (m/f/d) Fixed-term 18 months</t>
+          <t>Project Coordinator – New Tasks &amp; QC (m/f/d) Fixed-term 18 months</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/agilerobotsse/jobs/5013124101</t>
+          <t>https://job-boards.eu.greenhouse.io/agilerobotsse/jobs/5013108101</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1165,12 +1165,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Agile Robots</t>
+          <t>Proxima Fusion</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1180,20 +1180,20 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Project Coordinator – New Tasks &amp; QC (m/f/d) Fixed-term 18 months</t>
+          <t>Site Development Program Manager</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Munich, Bavaria, Germany</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/agilerobotsse/jobs/5013108101</t>
+          <t>https://jobs.ashbyhq.com/proxima-fusion/db5bc40c-aa3e-4735-94e7-096a556dd55d</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1203,19 +1203,19 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Title: project coordinator</t>
+          <t>Title: program manager</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Proxima Fusion</t>
+          <t>appliedAI</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Site Development Program Manager</t>
+          <t>AI Manager / Senior Project Lead (m/f/x)</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>München (81671)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/proxima-fusion/db5bc40c-aa3e-4735-94e7-096a556dd55d</t>
+          <t>https://appliedai.jobs.personio.de/job/2846436</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1247,51 +1247,6 @@
         </is>
       </c>
       <c r="I18" t="inlineStr">
-        <is>
-          <t>Title: program manager</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>appliedAI</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>AI Manager / Senior Project Lead (m/f/x)</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>3</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>München (81671)</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://appliedai.jobs.personio.de/job/2846436</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Direct role</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
         <is>
           <t>Title: project lead</t>
         </is>
